--- a/主要指数介绍.xlsx
+++ b/主要指数介绍.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="210">
   <si>
     <t>指数简称</t>
   </si>
@@ -239,7 +239,7 @@
     <t>上证科创板50成份指数</t>
   </si>
   <si>
-    <t>科创板上市超6个月（或满足特定市值条件的较短时间）的证券</t>
+    <t>排除被实施退市风险警示和有重大违法、经营异常或市场表现严重异常的，上市满12个月，或上市满3个月且市值排前5，或上市以来日均总市值排前3、上市满1个月且经专家委员会通过。</t>
   </si>
   <si>
     <t>流动性与规模：先剔除过去一年日均成交额后10%，再按日均总市值选前50名</t>
@@ -257,10 +257,10 @@
     <t>上证科创板100指数</t>
   </si>
   <si>
-    <t>科创板上市超过6个月的非风险警示证券</t>
+    <t>科创板上市超过12个月的非退市风险警示证券</t>
   </si>
   <si>
-    <t>规模与流动性：先保留成交额前90%，再剔除科创50样本及总市值前40名，最后按日均总市值选前100名</t>
+    <t>规模与流动性：先保留成交额前90%，再剔除科创50样本及过去一年日均总市值前40名，最后按日均总市值选前100名</t>
   </si>
   <si>
     <t xml:space="preserve">科创200 </t>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>上证科创板200指数</t>
+  </si>
+  <si>
+    <t>科创板上市超过12个月的非风险警示证券</t>
   </si>
   <si>
     <t>规模与流动性：先保留成交额前90%，再剔除科创50、科创100样本及总市值前130名，最后按日均总市值选前200名</t>
@@ -3613,7 +3616,7 @@
         <v>0.085889248583001</v>
       </c>
     </row>
-    <row r="10" ht="40.5" spans="1:69">
+    <row r="10" ht="94.5" spans="1:69">
       <c r="A10" s="1" t="s">
         <v>67</v>
       </c>
@@ -3877,10 +3880,10 @@
         <v>200</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>32</v>
@@ -3978,25 +3981,25 @@
     </row>
     <row r="13" ht="40.5" spans="1:69">
       <c r="A13" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I13" s="38" t="s">
         <v>51</v>
@@ -4103,7 +4106,7 @@
     </row>
     <row r="14" ht="27" spans="1:69">
       <c r="A14" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B14" s="1">
         <v>899050</v>
@@ -4112,10 +4115,10 @@
         <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>32</v>
@@ -4124,7 +4127,7 @@
         <v>0.1</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J14" s="1">
         <v>1000</v>
@@ -4161,31 +4164,31 @@
     </row>
     <row r="15" s="1" customFormat="1" ht="27" spans="1:69">
       <c r="A15" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B15" s="1">
         <v>399673</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D15" s="1">
         <v>50</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J15" s="1">
         <v>1000</v>
@@ -4332,22 +4335,22 @@
     </row>
     <row r="16" s="1" customFormat="1" ht="27" spans="1:69">
       <c r="A16" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B16" s="1">
         <v>399006</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D16" s="1">
         <v>100</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>32</v>
@@ -4356,7 +4359,7 @@
         <v>0.2</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J16" s="1">
         <v>1000</v>
@@ -4503,31 +4506,31 @@
     </row>
     <row r="17" s="1" customFormat="1" ht="27" spans="1:69">
       <c r="A17" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B17" s="1">
         <v>399019</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D17" s="1">
         <v>200</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J17" s="1">
         <v>1000</v>
@@ -4663,28 +4666,28 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:69">
       <c r="A18" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B18" s="1">
         <v>399102</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J18" s="1">
         <v>1000</v>
@@ -4856,22 +4859,22 @@
     </row>
     <row r="20" ht="40.5" hidden="1" spans="1:69">
       <c r="A20" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D20" s="18">
         <v>24</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>32</v>
@@ -5057,28 +5060,28 @@
     </row>
     <row r="21" ht="40.5" hidden="1" spans="1:69">
       <c r="A21" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D21" s="18">
         <v>99</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>34</v>
@@ -5258,28 +5261,28 @@
     </row>
     <row r="22" ht="40.5" hidden="1" spans="1:69">
       <c r="A22" s="17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D22" s="18">
         <v>192</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G22" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>34</v>
@@ -5459,22 +5462,22 @@
     </row>
     <row r="23" ht="40.5" hidden="1" spans="1:69">
       <c r="A23" s="17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D23" s="18">
         <v>57</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>32</v>
@@ -5660,22 +5663,22 @@
     </row>
     <row r="24" ht="40.5" hidden="1" spans="1:69">
       <c r="A24" s="17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D24" s="18">
         <v>38</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>32</v>
@@ -5861,22 +5864,22 @@
     </row>
     <row r="25" ht="40.5" hidden="1" spans="1:69">
       <c r="A25" s="17" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D25" s="18">
         <v>76</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>32</v>
@@ -6062,22 +6065,22 @@
     </row>
     <row r="26" ht="40.5" hidden="1" spans="1:69">
       <c r="A26" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D26" s="18">
         <v>88</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>32</v>
@@ -6263,22 +6266,22 @@
     </row>
     <row r="27" ht="40.5" hidden="1" spans="1:69">
       <c r="A27" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B27" s="18">
         <v>399965</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D27" s="18">
         <v>11</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>32</v>
@@ -6462,28 +6465,28 @@
     </row>
     <row r="28" ht="40.5" hidden="1" spans="1:69">
       <c r="A28" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B28" s="39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D28" s="18">
         <v>132</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>34</v>
@@ -6663,22 +6666,22 @@
     </row>
     <row r="29" ht="40.5" hidden="1" spans="1:69">
       <c r="A29" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B29" s="39" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D29" s="18">
         <v>47</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>32</v>
@@ -6864,22 +6867,22 @@
     </row>
     <row r="30" ht="40.5" hidden="1" spans="1:69">
       <c r="A30" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B30" s="39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D30" s="18">
         <v>36</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>32</v>
@@ -7098,31 +7101,31 @@
     </row>
     <row r="32" ht="94.5" hidden="1" spans="1:69">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D32" s="1">
         <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J32" s="1">
         <v>1000</v>
@@ -7302,31 +7305,31 @@
     </row>
     <row r="33" ht="94.5" hidden="1" spans="1:69">
       <c r="A33" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B33" s="1">
         <v>932308</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D33" s="1">
         <v>200</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H33" s="22" t="s">
         <v>40</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J33" s="1">
         <v>1000</v>
@@ -7459,25 +7462,25 @@
     </row>
     <row r="34" ht="54" hidden="1" spans="1:69">
       <c r="A34" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B34" s="1">
         <v>932154</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D34" s="1">
         <v>50</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H34" s="22" t="s">
         <v>40</v>
@@ -7616,31 +7619,31 @@
     </row>
     <row r="35" ht="121.5" hidden="1" spans="1:69">
       <c r="A35" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D35" s="1">
         <v>50</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G35" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J35" s="1">
         <v>1000</v>
@@ -7813,28 +7816,28 @@
     </row>
     <row r="36" ht="94.5" hidden="1" spans="1:69">
       <c r="A36" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B36" s="1">
         <v>930740</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D36" s="1">
         <v>50</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>34</v>
@@ -8017,28 +8020,28 @@
     </row>
     <row r="37" ht="148.5" hidden="1" spans="1:69">
       <c r="A37" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B37" s="1">
         <v>931847</v>
       </c>
       <c r="C37" s="25" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D37" s="1">
         <v>50</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>34</v>
@@ -8174,28 +8177,28 @@
     </row>
     <row r="38" ht="148.5" hidden="1" spans="1:69">
       <c r="A38" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B38" s="1">
         <v>931849</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D38" s="1">
         <v>100</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>34</v>
@@ -8331,25 +8334,25 @@
     </row>
     <row r="39" ht="40.5" hidden="1" spans="1:69">
       <c r="A39" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B39" s="1">
         <v>930955</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D39" s="1">
         <v>100</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G39" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>72</v>
@@ -8525,28 +8528,28 @@
     </row>
     <row r="40" ht="135" hidden="1" spans="1:69">
       <c r="A40" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B40" s="1">
         <v>932422</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D40" s="1">
         <v>50</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>34</v>
@@ -8707,31 +8710,31 @@
     </row>
     <row r="42" s="2" customFormat="1" ht="189" hidden="1" spans="1:69">
       <c r="A42" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B42" s="2">
         <v>932365</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D42" s="2">
         <v>100</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G42" s="28" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H42" s="28" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J42" s="2">
         <v>1000</v>
@@ -8875,31 +8878,31 @@
     </row>
     <row r="43" ht="216" hidden="1" spans="1:69">
       <c r="A43" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B43" s="1">
         <v>932366</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D43" s="1">
         <v>50</v>
       </c>
       <c r="E43" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H43" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J43" s="1">
         <v>1000</v>
@@ -9024,31 +9027,31 @@
     </row>
     <row r="44" ht="189" hidden="1" spans="1:69">
       <c r="A44" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B44" s="34">
         <v>932367</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D44" s="1">
         <v>50</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G44" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J44" s="1">
         <v>1000</v>
@@ -9173,31 +9176,31 @@
     </row>
     <row r="45" ht="202.5" hidden="1" spans="1:69">
       <c r="A45" s="35" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B45" s="1">
         <v>932369</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D45" s="1">
         <v>100</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G45" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J45" s="1">
         <v>1000</v>
@@ -9322,31 +9325,31 @@
     </row>
     <row r="46" ht="189" spans="1:69">
       <c r="A46" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B46" s="1">
         <v>931082</v>
       </c>
       <c r="C46" s="25" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D46" s="1">
         <v>50</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G46" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J46" s="1">
         <v>1000</v>

--- a/主要指数介绍.xlsx
+++ b/主要指数介绍.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20152" windowHeight="8955"/>
+    <workbookView windowWidth="20752" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="主要指数介绍" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="215">
   <si>
     <t>指数简称</t>
   </si>
@@ -716,6 +716,21 @@
 盈利质量由高到低排名位于样本空间前 80%，其中盈利质量=(过去一年经营活动产生的现金流量净额-过去一年营业利润)/总资产；
 （2）将待选样本按照自由现金流率由高到低排名，选取排名前50 的证券作为指数样本，其中自由现金流率=自由现金流/企业价值</t>
   </si>
+  <si>
+    <t>中证全指</t>
+  </si>
+  <si>
+    <t>000985</t>
+  </si>
+  <si>
+    <t>中证全指指数</t>
+  </si>
+  <si>
+    <t>A 股非风险警示证券；上市时间超过一年的科创板证券和上市时间超过两年的北交所证券；上市时间超过一个季度，除非该证券自上市以来日均总市值排在前 30 位</t>
+  </si>
+  <si>
+    <t>每季度调整一次(实施时间分别为 6 月和 12 月的第二个星期五的下一交易日)</t>
+  </si>
 </sst>
 </file>
 
@@ -1371,7 +1386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1478,6 +1493,15 @@
     </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2295,7 +2319,7 @@
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="41" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -2499,7 +2523,7 @@
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="41" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -2703,7 +2727,7 @@
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="41" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -3218,7 +3242,7 @@
       <c r="A8" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="41" t="s">
         <v>57</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -3416,7 +3440,7 @@
       <c r="A9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="41" t="s">
         <v>62</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -3620,7 +3644,7 @@
       <c r="A10" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="41" t="s">
         <v>68</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -3742,7 +3766,7 @@
       <c r="A11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="41" t="s">
         <v>74</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -3870,7 +3894,7 @@
       <c r="A12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="41" t="s">
         <v>79</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -3983,7 +4007,7 @@
       <c r="A13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="41" t="s">
         <v>84</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -4001,7 +4025,7 @@
       <c r="H13" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I13" s="38" t="s">
+      <c r="I13" s="41" t="s">
         <v>51</v>
       </c>
       <c r="J13" s="1">
@@ -4861,7 +4885,7 @@
       <c r="A20" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="42" t="s">
         <v>110</v>
       </c>
       <c r="C20" s="18" t="s">
@@ -5062,7 +5086,7 @@
       <c r="A21" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="39" t="s">
+      <c r="B21" s="42" t="s">
         <v>115</v>
       </c>
       <c r="C21" s="18" t="s">
@@ -5263,7 +5287,7 @@
       <c r="A22" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="39" t="s">
+      <c r="B22" s="42" t="s">
         <v>118</v>
       </c>
       <c r="C22" s="18" t="s">
@@ -5464,7 +5488,7 @@
       <c r="A23" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="42" t="s">
         <v>121</v>
       </c>
       <c r="C23" s="18" t="s">
@@ -5665,7 +5689,7 @@
       <c r="A24" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="42" t="s">
         <v>124</v>
       </c>
       <c r="C24" s="18" t="s">
@@ -5866,7 +5890,7 @@
       <c r="A25" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="42" t="s">
         <v>127</v>
       </c>
       <c r="C25" s="18" t="s">
@@ -6067,7 +6091,7 @@
       <c r="A26" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="42" t="s">
         <v>130</v>
       </c>
       <c r="C26" s="18" t="s">
@@ -6389,7 +6413,7 @@
       <c r="AR27" s="11">
         <v>0.2647</v>
       </c>
-      <c r="AS27" s="40" t="s">
+      <c r="AS27" s="43" t="s">
         <v>51</v>
       </c>
       <c r="AT27" s="11">
@@ -6467,7 +6491,7 @@
       <c r="A28" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="42" t="s">
         <v>135</v>
       </c>
       <c r="C28" s="18" t="s">
@@ -6668,7 +6692,7 @@
       <c r="A29" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="42" t="s">
         <v>138</v>
       </c>
       <c r="C29" s="18" t="s">
@@ -6869,7 +6893,7 @@
       <c r="A30" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="42" t="s">
         <v>141</v>
       </c>
       <c r="C30" s="18" t="s">
@@ -7103,7 +7127,7 @@
       <c r="A32" t="s">
         <v>143</v>
       </c>
-      <c r="B32" s="38" t="s">
+      <c r="B32" s="41" t="s">
         <v>144</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -7456,7 +7480,7 @@
       <c r="BP33" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BQ33" s="41" t="s">
+      <c r="BQ33" s="44" t="s">
         <v>51</v>
       </c>
     </row>
@@ -7613,7 +7637,7 @@
       <c r="BP34" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BQ34" s="41" t="s">
+      <c r="BQ34" s="44" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8171,7 +8195,7 @@
       <c r="BP37" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BQ37" s="41" t="s">
+      <c r="BQ37" s="44" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8325,7 +8349,7 @@
       <c r="BO38" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BP38" s="41" t="s">
+      <c r="BP38" s="44" t="s">
         <v>51</v>
       </c>
       <c r="BQ38" s="14" t="s">
@@ -8676,7 +8700,7 @@
       <c r="BO40" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BP40" s="41" t="s">
+      <c r="BP40" s="44" t="s">
         <v>51</v>
       </c>
       <c r="BQ40" s="14" t="s">
@@ -9487,20 +9511,207 @@
       <c r="AG47" s="36"/>
       <c r="AH47" s="36"/>
     </row>
-    <row r="48" spans="1:69">
-      <c r="K48" s="10"/>
-      <c r="W48" s="36"/>
-      <c r="X48" s="36"/>
-      <c r="Y48" s="36"/>
-      <c r="Z48" s="36"/>
-      <c r="AA48" s="36"/>
-      <c r="AB48" s="36"/>
-      <c r="AC48" s="36"/>
-      <c r="AD48" s="36"/>
-      <c r="AE48" s="36"/>
-      <c r="AF48" s="36"/>
-      <c r="AG48" s="36"/>
+    <row r="48" ht="81" spans="1:69">
+      <c r="A48" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B48" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="C48" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="D48" s="1">
+        <v>5166</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K48" s="38">
+        <v>38352</v>
+      </c>
+      <c r="L48" s="3">
+        <v>40757</v>
+      </c>
+      <c r="M48" s="39">
+        <v>-0.1099</v>
+      </c>
+      <c r="N48" s="39">
+        <v>1.1217</v>
+      </c>
+      <c r="O48" s="39">
+        <v>1.7088</v>
+      </c>
+      <c r="P48" s="39">
+        <v>-0.6406</v>
+      </c>
+      <c r="Q48" s="39">
+        <v>1.0646</v>
+      </c>
+      <c r="R48" s="39">
+        <v>-0.0377</v>
+      </c>
+      <c r="S48" s="39">
+        <v>-0.2801</v>
+      </c>
+      <c r="T48" s="39">
+        <v>0.0458</v>
+      </c>
+      <c r="U48" s="39">
+        <v>0.0521</v>
+      </c>
+      <c r="V48" s="39">
+        <v>0.4582</v>
+      </c>
+      <c r="W48" s="39">
+        <v>0.3256</v>
+      </c>
+      <c r="X48" s="39">
+        <v>-0.1441</v>
+      </c>
+      <c r="Y48" s="39">
+        <v>0.0234</v>
+      </c>
+      <c r="Z48" s="39">
+        <v>-0.2994</v>
+      </c>
+      <c r="AA48" s="39">
+        <v>0.3111</v>
+      </c>
+      <c r="AB48" s="39">
+        <v>0.2492</v>
+      </c>
+      <c r="AC48" s="39">
+        <v>0.0619</v>
+      </c>
+      <c r="AD48" s="39">
+        <v>-0.2032</v>
+      </c>
+      <c r="AE48" s="39">
+        <v>-0.0704</v>
+      </c>
+      <c r="AF48" s="39">
+        <v>0.0743</v>
+      </c>
+      <c r="AG48" s="39">
+        <v>0.246</v>
+      </c>
       <c r="AH48" s="36"/>
+      <c r="AI48" s="4">
+        <f>SUM(M48:AG48)/21</f>
+        <v>0.188442857142857</v>
+      </c>
+      <c r="AK48" s="39">
+        <v>0.2203</v>
+      </c>
+      <c r="AL48" s="39">
+        <v>0.2223</v>
+      </c>
+      <c r="AM48" s="39">
+        <v>0.369</v>
+      </c>
+      <c r="AN48" s="39">
+        <v>0.4887</v>
+      </c>
+      <c r="AO48" s="39">
+        <v>0.3225</v>
+      </c>
+      <c r="AP48" s="39">
+        <v>0.2493</v>
+      </c>
+      <c r="AQ48" s="39">
+        <v>0.2123</v>
+      </c>
+      <c r="AR48" s="39">
+        <v>0.2109</v>
+      </c>
+      <c r="AS48" s="39">
+        <v>0.2098</v>
+      </c>
+      <c r="AT48" s="39">
+        <v>0.1755</v>
+      </c>
+      <c r="AU48" s="39">
+        <v>0.4001</v>
+      </c>
+      <c r="AV48" s="39">
+        <v>0.2549</v>
+      </c>
+      <c r="AW48" s="39">
+        <v>0.1115</v>
+      </c>
+      <c r="AX48" s="39">
+        <v>0.2135</v>
+      </c>
+      <c r="AY48" s="39">
+        <v>0.2063</v>
+      </c>
+      <c r="AZ48" s="39">
+        <v>0.2339</v>
+      </c>
+      <c r="BA48" s="39">
+        <v>0.1601</v>
+      </c>
+      <c r="BB48" s="39">
+        <v>0.2051</v>
+      </c>
+      <c r="BC48" s="39">
+        <v>0.1277</v>
+      </c>
+      <c r="BD48" s="39">
+        <v>0.2502</v>
+      </c>
+      <c r="BE48" s="39">
+        <v>0.1769</v>
+      </c>
+      <c r="BG48" s="10">
+        <v>0.246</v>
+      </c>
+      <c r="BH48" s="10">
+        <v>0.0756</v>
+      </c>
+      <c r="BI48" s="10">
+        <v>0.0104</v>
+      </c>
+      <c r="BJ48" s="10">
+        <v>0.081</v>
+      </c>
+      <c r="BK48" s="10">
+        <v>0.0239</v>
+      </c>
+      <c r="BL48" s="10">
+        <v>0.0313</v>
+      </c>
+      <c r="BM48" s="10">
+        <v>0.0607</v>
+      </c>
+      <c r="BN48" s="10">
+        <v>0.0327</v>
+      </c>
+      <c r="BO48" s="10">
+        <v>0.0712</v>
+      </c>
+      <c r="BP48" s="10">
+        <v>0.062</v>
+      </c>
+      <c r="BQ48" s="10">
+        <v>0.0884</v>
+      </c>
     </row>
     <row r="49" spans="11:34">
       <c r="K49" s="10"/>
@@ -12326,51 +12537,51 @@
       <c r="AH248" s="36"/>
     </row>
     <row r="249" spans="23:34">
-      <c r="W249" s="37" t="e">
+      <c r="W249" s="40" t="e">
         <f t="shared" ref="W249:AG249" si="1">(F249-F3)/F3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="X249" s="37" t="e">
+      <c r="X249" s="40" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Y249" s="37" t="e">
+      <c r="Y249" s="40" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Z249" s="37" t="e">
+      <c r="Z249" s="40" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="AA249" s="37">
+      <c r="AA249" s="40">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="AB249" s="37">
+      <c r="AB249" s="40">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="AC249" s="37">
+      <c r="AC249" s="40">
         <f t="shared" si="1"/>
         <v>-1</v>
       </c>
-      <c r="AD249" s="37" t="e">
+      <c r="AD249" s="40" t="e">
         <f>(W249-W9)/W9</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE249" s="37" t="e">
+      <c r="AE249" s="40" t="e">
         <f>(X249-#REF!)/#REF!</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AF249" s="37" t="e">
+      <c r="AF249" s="40" t="e">
         <f>(Y249-#REF!)/#REF!</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG249" s="37" t="e">
+      <c r="AG249" s="40" t="e">
         <f>(Z249-#REF!)/#REF!</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH249" s="37"/>
+      <c r="AH249" s="40"/>
     </row>
     <row r="250" spans="23:34">
       <c r="W250" s="36"/>
@@ -15775,51 +15986,51 @@
       <c r="AH492" s="36"/>
     </row>
     <row r="493" spans="23:34">
-      <c r="W493" s="37" t="e">
+      <c r="W493" s="40" t="e">
         <f t="shared" ref="W493:AG493" si="2">(F493-F249)/F249</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X493" s="37" t="e">
+      <c r="X493" s="40" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y493" s="37" t="e">
+      <c r="Y493" s="40" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z493" s="37" t="e">
+      <c r="Z493" s="40" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA493" s="37" t="e">
+      <c r="AA493" s="40" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB493" s="37" t="e">
+      <c r="AB493" s="40" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC493" s="37" t="e">
+      <c r="AC493" s="40" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD493" s="37" t="e">
+      <c r="AD493" s="40" t="e">
         <f>(W493-W249)/W249</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE493" s="37" t="e">
+      <c r="AE493" s="40" t="e">
         <f>(X493-X249)/X249</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF493" s="37" t="e">
+      <c r="AF493" s="40" t="e">
         <f>(Y493-Y249)/Y249</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG493" s="37" t="e">
+      <c r="AG493" s="40" t="e">
         <f>(Z493-Z249)/Z249</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH493" s="37"/>
+      <c r="AH493" s="40"/>
     </row>
     <row r="494" spans="23:34">
       <c r="W494" s="36"/>
@@ -19210,51 +19421,51 @@
       <c r="AH735" s="36"/>
     </row>
     <row r="736" spans="23:34">
-      <c r="W736" s="37" t="e">
+      <c r="W736" s="40" t="e">
         <f t="shared" ref="W736:AG736" si="3">(F736-F493)/F493</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X736" s="37" t="e">
+      <c r="X736" s="40" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y736" s="37" t="e">
+      <c r="Y736" s="40" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z736" s="37" t="e">
+      <c r="Z736" s="40" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA736" s="37" t="e">
+      <c r="AA736" s="40" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB736" s="37" t="e">
+      <c r="AB736" s="40" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC736" s="37" t="e">
+      <c r="AC736" s="40" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD736" s="37" t="e">
+      <c r="AD736" s="40" t="e">
         <f>(W736-W493)/W493</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE736" s="37" t="e">
+      <c r="AE736" s="40" t="e">
         <f>(X736-X493)/X493</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF736" s="37" t="e">
+      <c r="AF736" s="40" t="e">
         <f>(Y736-Y493)/Y493</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG736" s="37" t="e">
+      <c r="AG736" s="40" t="e">
         <f>(Z736-Z493)/Z493</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH736" s="37"/>
+      <c r="AH736" s="40"/>
     </row>
     <row r="737" spans="23:34">
       <c r="W737" s="36"/>
@@ -22659,51 +22870,51 @@
       <c r="AH979" s="36"/>
     </row>
     <row r="980" spans="23:34">
-      <c r="W980" s="37" t="e">
+      <c r="W980" s="40" t="e">
         <f t="shared" ref="W980:AG980" si="4">(F980-F736)/F736</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X980" s="37" t="e">
+      <c r="X980" s="40" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y980" s="37" t="e">
+      <c r="Y980" s="40" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z980" s="37" t="e">
+      <c r="Z980" s="40" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA980" s="37" t="e">
+      <c r="AA980" s="40" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB980" s="37" t="e">
+      <c r="AB980" s="40" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC980" s="37" t="e">
+      <c r="AC980" s="40" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD980" s="37" t="e">
+      <c r="AD980" s="40" t="e">
         <f>(W980-W736)/W736</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE980" s="37" t="e">
+      <c r="AE980" s="40" t="e">
         <f>(X980-X736)/X736</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF980" s="37" t="e">
+      <c r="AF980" s="40" t="e">
         <f>(Y980-Y736)/Y736</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG980" s="37" t="e">
+      <c r="AG980" s="40" t="e">
         <f>(Z980-Z736)/Z736</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH980" s="37"/>
+      <c r="AH980" s="40"/>
     </row>
     <row r="981" spans="23:34">
       <c r="W981" s="36"/>
@@ -26094,51 +26305,51 @@
       <c r="AH1222" s="36"/>
     </row>
     <row r="1223" spans="23:34">
-      <c r="W1223" s="37" t="e">
+      <c r="W1223" s="40" t="e">
         <f t="shared" ref="W1223:AG1223" si="5">(F1223-F980)/F980</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X1223" s="37" t="e">
+      <c r="X1223" s="40" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y1223" s="37" t="e">
+      <c r="Y1223" s="40" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z1223" s="37" t="e">
+      <c r="Z1223" s="40" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA1223" s="37" t="e">
+      <c r="AA1223" s="40" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB1223" s="37" t="e">
+      <c r="AB1223" s="40" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC1223" s="37" t="e">
+      <c r="AC1223" s="40" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD1223" s="37" t="e">
+      <c r="AD1223" s="40" t="e">
         <f>(W1223-W980)/W980</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE1223" s="37" t="e">
+      <c r="AE1223" s="40" t="e">
         <f>(X1223-X980)/X980</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF1223" s="37" t="e">
+      <c r="AF1223" s="40" t="e">
         <f>(Y1223-Y980)/Y980</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG1223" s="37" t="e">
+      <c r="AG1223" s="40" t="e">
         <f>(Z1223-Z980)/Z980</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH1223" s="37"/>
+      <c r="AH1223" s="40"/>
     </row>
     <row r="1224" spans="23:34">
       <c r="W1224" s="36"/>
@@ -29529,51 +29740,51 @@
       <c r="AH1465" s="36"/>
     </row>
     <row r="1466" spans="23:34">
-      <c r="W1466" s="37" t="e">
+      <c r="W1466" s="40" t="e">
         <f t="shared" ref="W1466:AG1466" si="6">(F1466-F1223)/F1223</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X1466" s="37" t="e">
+      <c r="X1466" s="40" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y1466" s="37" t="e">
+      <c r="Y1466" s="40" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z1466" s="37" t="e">
+      <c r="Z1466" s="40" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA1466" s="37" t="e">
+      <c r="AA1466" s="40" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB1466" s="37" t="e">
+      <c r="AB1466" s="40" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC1466" s="37" t="e">
+      <c r="AC1466" s="40" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD1466" s="37" t="e">
+      <c r="AD1466" s="40" t="e">
         <f>(W1466-W1223)/W1223</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE1466" s="37" t="e">
+      <c r="AE1466" s="40" t="e">
         <f>(X1466-X1223)/X1223</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF1466" s="37" t="e">
+      <c r="AF1466" s="40" t="e">
         <f>(Y1466-Y1223)/Y1223</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG1466" s="37" t="e">
+      <c r="AG1466" s="40" t="e">
         <f>(Z1466-Z1223)/Z1223</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH1466" s="37"/>
+      <c r="AH1466" s="40"/>
     </row>
     <row r="1467" spans="23:34">
       <c r="W1467" s="36"/>
@@ -32950,51 +33161,51 @@
       <c r="AH1707" s="36"/>
     </row>
     <row r="1708" spans="23:34">
-      <c r="W1708" s="37" t="e">
+      <c r="W1708" s="40" t="e">
         <f t="shared" ref="W1708:AG1708" si="7">(F1708-F1466)/F1466</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X1708" s="37" t="e">
+      <c r="X1708" s="40" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y1708" s="37" t="e">
+      <c r="Y1708" s="40" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z1708" s="37" t="e">
+      <c r="Z1708" s="40" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA1708" s="37" t="e">
+      <c r="AA1708" s="40" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB1708" s="37" t="e">
+      <c r="AB1708" s="40" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC1708" s="37" t="e">
+      <c r="AC1708" s="40" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD1708" s="37" t="e">
+      <c r="AD1708" s="40" t="e">
         <f>(W1708-W1466)/W1466</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE1708" s="37" t="e">
+      <c r="AE1708" s="40" t="e">
         <f>(X1708-X1466)/X1466</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF1708" s="37" t="e">
+      <c r="AF1708" s="40" t="e">
         <f>(Y1708-Y1466)/Y1466</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG1708" s="37" t="e">
+      <c r="AG1708" s="40" t="e">
         <f>(Z1708-Z1466)/Z1466</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH1708" s="37"/>
+      <c r="AH1708" s="40"/>
     </row>
     <row r="1709" spans="23:34">
       <c r="W1709" s="36"/>
@@ -36371,51 +36582,51 @@
       <c r="AH1949" s="36"/>
     </row>
     <row r="1950" spans="23:34">
-      <c r="W1950" s="37" t="e">
+      <c r="W1950" s="40" t="e">
         <f t="shared" ref="W1950:AG1950" si="8">(F1950-F1708)/F1708</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X1950" s="37" t="e">
+      <c r="X1950" s="40" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y1950" s="37" t="e">
+      <c r="Y1950" s="40" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z1950" s="37" t="e">
+      <c r="Z1950" s="40" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA1950" s="37" t="e">
+      <c r="AA1950" s="40" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB1950" s="37" t="e">
+      <c r="AB1950" s="40" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC1950" s="37" t="e">
+      <c r="AC1950" s="40" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD1950" s="37" t="e">
+      <c r="AD1950" s="40" t="e">
         <f>(W1950-W1708)/W1708</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE1950" s="37" t="e">
+      <c r="AE1950" s="40" t="e">
         <f>(X1950-X1708)/X1708</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF1950" s="37" t="e">
+      <c r="AF1950" s="40" t="e">
         <f>(Y1950-Y1708)/Y1708</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG1950" s="37" t="e">
+      <c r="AG1950" s="40" t="e">
         <f>(Z1950-Z1708)/Z1708</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH1950" s="37"/>
+      <c r="AH1950" s="40"/>
     </row>
     <row r="1951" spans="23:34">
       <c r="W1951" s="36"/>
@@ -39764,51 +39975,51 @@
       <c r="AH2189" s="36"/>
     </row>
     <row r="2190" spans="23:34">
-      <c r="W2190" s="37" t="e">
+      <c r="W2190" s="40" t="e">
         <f t="shared" ref="W2190:AG2190" si="9">(F2190-F1950)/F1950</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X2190" s="37" t="e">
+      <c r="X2190" s="40" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y2190" s="37" t="e">
+      <c r="Y2190" s="40" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z2190" s="37" t="e">
+      <c r="Z2190" s="40" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA2190" s="37" t="e">
+      <c r="AA2190" s="40" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB2190" s="37" t="e">
+      <c r="AB2190" s="40" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC2190" s="37" t="e">
+      <c r="AC2190" s="40" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD2190" s="37" t="e">
+      <c r="AD2190" s="40" t="e">
         <f>(W2190-W1950)/W1950</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE2190" s="37" t="e">
+      <c r="AE2190" s="40" t="e">
         <f>(X2190-X1950)/X1950</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF2190" s="37" t="e">
+      <c r="AF2190" s="40" t="e">
         <f>(Y2190-Y1950)/Y1950</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG2190" s="37" t="e">
+      <c r="AG2190" s="40" t="e">
         <f>(Z2190-Z1950)/Z1950</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH2190" s="37"/>
+      <c r="AH2190" s="40"/>
     </row>
     <row r="2191" spans="23:34">
       <c r="W2191" s="36"/>
@@ -43171,51 +43382,51 @@
       <c r="AH2430" s="36"/>
     </row>
     <row r="2431" spans="23:34">
-      <c r="W2431" s="37" t="e">
+      <c r="W2431" s="40" t="e">
         <f t="shared" ref="W2431:AG2431" si="10">(F2431-F2190)/F2190</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X2431" s="37" t="e">
+      <c r="X2431" s="40" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y2431" s="37" t="e">
+      <c r="Y2431" s="40" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z2431" s="37" t="e">
+      <c r="Z2431" s="40" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA2431" s="37" t="e">
+      <c r="AA2431" s="40" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB2431" s="37" t="e">
+      <c r="AB2431" s="40" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC2431" s="37" t="e">
+      <c r="AC2431" s="40" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD2431" s="37" t="e">
+      <c r="AD2431" s="40" t="e">
         <f>(W2431-W2190)/W2190</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE2431" s="37" t="e">
+      <c r="AE2431" s="40" t="e">
         <f>(X2431-X2190)/X2190</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF2431" s="37" t="e">
+      <c r="AF2431" s="40" t="e">
         <f>(Y2431-Y2190)/Y2190</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG2431" s="37" t="e">
+      <c r="AG2431" s="40" t="e">
         <f>(Z2431-Z2190)/Z2190</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH2431" s="37"/>
+      <c r="AH2431" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/主要指数介绍.xlsx
+++ b/主要指数介绍.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="266">
   <si>
     <t>指数简称</t>
   </si>
@@ -584,6 +584,9 @@
   </si>
   <si>
     <t>中证500红利低波动指数</t>
+  </si>
+  <si>
+    <t>（1）过去三年连续现金分红；过去三年平均股利支付率大于 0 且小于 1；过去 12 个季度 ROE 标准差在样本空间内由低到高排名前 80%。（2）对剩余证券，按照过去三年平均现金股息率由高到低排名，选取排名前 50% 的证券作为待选样本；（3）对于待选样本，按照过去一年波动率（日收益率的标准差）升序排名，选取排名靠前的 50 只证券作为指数样本。</t>
   </si>
   <si>
     <t>单个样本权重不超过 10%，单个一级行业权重不超过 30%</t>
@@ -2217,7 +2220,7 @@
     <col min="3" max="3" width="25.4247787610619" style="4" customWidth="1"/>
     <col min="4" max="4" width="8.36283185840708" style="4" customWidth="1"/>
     <col min="5" max="5" width="45.070796460177" style="4" customWidth="1"/>
-    <col min="6" max="6" width="52.9646017699115" style="4" customWidth="1"/>
+    <col min="6" max="6" width="57.6902654867257" style="4" customWidth="1"/>
     <col min="7" max="7" width="28.5309734513274" style="4" customWidth="1"/>
     <col min="8" max="8" width="31.7964601769912" style="4" customWidth="1"/>
     <col min="9" max="9" width="34.646017699115" style="4" customWidth="1"/>
@@ -7736,7 +7739,7 @@
         <v>0.0983390163708719</v>
       </c>
     </row>
-    <row r="40" ht="67.5" spans="1:71">
+    <row r="40" ht="94.5" spans="1:71">
       <c r="A40" s="4" t="s">
         <v>178</v>
       </c>
@@ -7753,13 +7756,13 @@
         <v>124</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>138</v>
       </c>
       <c r="H40" s="36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>36</v>
@@ -7897,13 +7900,13 @@
     </row>
     <row r="41" ht="67.5" spans="1:71">
       <c r="A41" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B41" s="4">
         <v>931849</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D41" s="4">
         <v>100</v>
@@ -7912,13 +7915,13 @@
         <v>127</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>138</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>36</v>
@@ -8054,13 +8057,13 @@
     </row>
     <row r="42" ht="67.5" spans="1:71">
       <c r="A42" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B42" s="4">
         <v>932422</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D42" s="4">
         <v>50</v>
@@ -8075,7 +8078,7 @@
         <v>138</v>
       </c>
       <c r="H42" s="36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>36</v>
@@ -8211,22 +8214,22 @@
     </row>
     <row r="43" ht="94.5" spans="1:71">
       <c r="A43" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B43" s="4">
         <v>930992</v>
       </c>
       <c r="C43" s="34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D43" s="4">
         <v>100</v>
       </c>
       <c r="E43" s="36" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F43" s="36" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>138</v>
@@ -8235,7 +8238,7 @@
         <v>90</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J43" s="4">
         <v>3000</v>
@@ -8329,28 +8332,28 @@
     </row>
     <row r="45" ht="54" spans="1:71">
       <c r="A45" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B45" s="4">
         <v>932315</v>
       </c>
       <c r="C45" s="34" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D45" s="4">
         <v>50</v>
       </c>
       <c r="E45" s="36" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H45" s="36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>36</v>
@@ -8404,13 +8407,13 @@
     </row>
     <row r="46" ht="54" spans="1:71">
       <c r="A46" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B46" s="4">
         <v>932316</v>
       </c>
       <c r="C46" s="34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D46" s="4">
         <v>50</v>
@@ -8419,13 +8422,13 @@
         <v>120</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H46" s="36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>36</v>
@@ -8479,13 +8482,13 @@
     </row>
     <row r="47" ht="54" spans="1:71">
       <c r="A47" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B47" s="4">
         <v>932317</v>
       </c>
       <c r="C47" s="34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D47" s="4">
         <v>50</v>
@@ -8494,13 +8497,13 @@
         <v>124</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H47" s="36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>36</v>
@@ -8554,13 +8557,13 @@
     </row>
     <row r="48" ht="54" spans="1:71">
       <c r="A48" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B48" s="4">
         <v>932319</v>
       </c>
       <c r="C48" s="44" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D48" s="4">
         <v>100</v>
@@ -8569,13 +8572,13 @@
         <v>127</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H48" s="36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>36</v>
@@ -8629,13 +8632,13 @@
     </row>
     <row r="49" ht="54" spans="1:71">
       <c r="A49" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B49" s="4">
         <v>932476</v>
       </c>
       <c r="C49" s="34" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D49" s="4">
         <v>50</v>
@@ -8644,13 +8647,13 @@
         <v>131</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H49" s="36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>36</v>
@@ -8747,22 +8750,22 @@
     </row>
     <row r="51" ht="67.5" spans="1:71">
       <c r="A51" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B51" s="50" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C51" s="34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D51" s="4">
         <v>50</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>138</v>
@@ -8771,7 +8774,7 @@
         <v>116</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J51" s="4">
         <v>1000</v>
@@ -8822,22 +8825,22 @@
     </row>
     <row r="52" ht="81" spans="1:71">
       <c r="A52" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B52" s="50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C52" s="34" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D52" s="4">
         <v>100</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>138</v>
@@ -8897,22 +8900,22 @@
     </row>
     <row r="53" ht="54" spans="1:71">
       <c r="A53" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B53" s="4">
         <v>931233</v>
       </c>
       <c r="C53" s="34" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D53" s="4">
         <v>50</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>138</v>
@@ -8921,7 +8924,7 @@
         <v>116</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J53" s="4">
         <v>1000</v>
@@ -8972,22 +8975,22 @@
     </row>
     <row r="54" ht="54" spans="1:71">
       <c r="A54" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C54" s="34" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D54" s="4">
         <v>50</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>138</v>
@@ -8996,7 +8999,7 @@
         <v>116</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J54" s="4">
         <v>1000</v>
@@ -9090,22 +9093,22 @@
     </row>
     <row r="56" ht="40.5" spans="1:71">
       <c r="A56" s="45" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B56" s="52" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C56" s="45" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D56" s="45">
         <v>24</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>34</v>
@@ -9293,22 +9296,22 @@
     </row>
     <row r="57" ht="40.5" spans="1:71">
       <c r="A57" s="45" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B57" s="52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C57" s="45" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D57" s="45">
         <v>99</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>34</v>
@@ -9496,22 +9499,22 @@
     </row>
     <row r="58" ht="40.5" spans="1:71">
       <c r="A58" s="45" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B58" s="52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C58" s="45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D58" s="45">
         <v>192</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>34</v>
@@ -9699,22 +9702,22 @@
     </row>
     <row r="59" ht="40.5" spans="1:71">
       <c r="A59" s="45" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B59" s="52" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C59" s="45" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D59" s="45">
         <v>57</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>34</v>
@@ -9902,22 +9905,22 @@
     </row>
     <row r="60" ht="40.5" spans="1:71">
       <c r="A60" s="45" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B60" s="52" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C60" s="45" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D60" s="45">
         <v>38</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>34</v>
@@ -10105,22 +10108,22 @@
     </row>
     <row r="61" ht="40.5" spans="1:71">
       <c r="A61" s="45" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B61" s="52" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C61" s="45" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D61" s="45">
         <v>76</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>34</v>
@@ -10308,22 +10311,22 @@
     </row>
     <row r="62" ht="40.5" spans="1:71">
       <c r="A62" s="45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B62" s="52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C62" s="45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D62" s="45">
         <v>88</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>34</v>
@@ -10511,22 +10514,22 @@
     </row>
     <row r="63" ht="40.5" spans="1:71">
       <c r="A63" s="45" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B63" s="45">
         <v>399965</v>
       </c>
       <c r="C63" s="45" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D63" s="45">
         <v>11</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>34</v>
@@ -10712,22 +10715,22 @@
     </row>
     <row r="64" ht="40.5" spans="1:71">
       <c r="A64" s="45" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B64" s="52" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C64" s="45" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D64" s="45">
         <v>132</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>34</v>
@@ -10915,22 +10918,22 @@
     </row>
     <row r="65" ht="40.5" spans="1:71">
       <c r="A65" s="45" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B65" s="52" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C65" s="45" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D65" s="45">
         <v>47</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>34</v>
@@ -11118,22 +11121,22 @@
     </row>
     <row r="66" ht="40.5" spans="1:71">
       <c r="A66" s="45" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B66" s="52" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C66" s="45" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D66" s="45">
         <v>36</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>34</v>
@@ -11364,19 +11367,19 @@
     </row>
     <row r="68" ht="54" spans="1:71">
       <c r="A68" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B68" s="50" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C68" s="34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D68" s="4">
         <v>5166</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>89</v>
@@ -11388,7 +11391,7 @@
         <v>90</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J68" s="4">
         <v>1000</v>

--- a/主要指数介绍.xlsx
+++ b/主要指数介绍.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="322">
   <si>
     <t>指数简称</t>
   </si>
@@ -893,6 +893,46 @@
     <t>所有样本权重相等</t>
   </si>
   <si>
+    <t xml:space="preserve">中证煤炭   </t>
+  </si>
+  <si>
+    <t>中证煤炭指数</t>
+  </si>
+  <si>
+    <t>同中证全指样本空间</t>
+  </si>
+  <si>
+    <t>（1）选取属于煤炭行业的证券（2）如果证券数量少于或等于 50 只，则全部证券作为指数样本；如果证券数量多于 50 只，则分别按照证券过去一年的日均成交金额、日均总市值由高到低排名，剔除成交金额排名后 10%、以及累积总市值占比达到 98% 以后的证券，并且保持剔除后证券数量不少于 50 只，将剩余全部证券作为指数样本。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">单个样本权重不超过 10%
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中证钢铁   </t>
+  </si>
+  <si>
+    <t>中证钢铁指数</t>
+  </si>
+  <si>
+    <t>（1）选取属于钢铁行业的证券（2）如果证券数量少于或等于 50 只，则全部证券作为指数样本；如果证券数量多于 50 只，则分别按照证券过去一年的日均成交金额、日均总市值由高到低排名，剔除成交金额排名后 10%、以及累积总市值占比达到 98% 以后的证券，并且保持剔除后证券数量不少于 50 只，将剩余全部证券作为指数样本。</t>
+  </si>
+  <si>
+    <t>CS稀金属</t>
+  </si>
+  <si>
+    <t>中证稀有金属主题指数</t>
+  </si>
+  <si>
+    <t>同中证全指指数的样本空间，过去一年日均成交金额排名位于样本空间前 90%</t>
+  </si>
+  <si>
+    <t>（1）样本空间内满足可投资性条件、业务涉及稀有金属采选冶加的证券为待选证券；（2）按过去一年日均总市值由高到低排序，取前 50 只为样本，不足 50 只则全部纳入。</t>
+  </si>
+  <si>
+    <t>单个样本权重不超过 15%，前五大样本合计权重不超过 60%</t>
+  </si>
+  <si>
     <t>中证环保</t>
   </si>
   <si>
@@ -935,9 +975,6 @@
     <t xml:space="preserve">中证白酒   </t>
   </si>
   <si>
-    <t xml:space="preserve">中证煤炭   </t>
-  </si>
-  <si>
     <t xml:space="preserve">家用电器   </t>
   </si>
   <si>
@@ -947,16 +984,10 @@
     <t xml:space="preserve">中证软件   </t>
   </si>
   <si>
-    <t xml:space="preserve">中证钢铁   </t>
-  </si>
-  <si>
     <t xml:space="preserve">中证旅游   </t>
   </si>
   <si>
     <t xml:space="preserve">港股科技  </t>
-  </si>
-  <si>
-    <t>CS稀金属</t>
   </si>
   <si>
     <t>港股通高股息</t>
@@ -1022,7 +1053,7 @@
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="177" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1068,6 +1099,19 @@
       <color rgb="FF040C35"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -1541,137 +1585,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1807,7 +1851,31 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
@@ -1818,9 +1886,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2365,7 +2430,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BQ2454"/>
+  <dimension ref="A1:BQ2458"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.141592920354" style="4" customWidth="1"/>
@@ -2625,7 +2690,7 @@
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -2829,7 +2894,7 @@
       <c r="A4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="51" t="s">
+      <c r="B4" s="58" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -3033,7 +3098,7 @@
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="B5" s="58" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -3598,7 +3663,7 @@
       <c r="A9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="58" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -3796,7 +3861,7 @@
       <c r="A10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="51" t="s">
+      <c r="B10" s="58" t="s">
         <v>62</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -4059,7 +4124,7 @@
       <c r="A12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="51" t="s">
+      <c r="B12" s="58" t="s">
         <v>68</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -4181,7 +4246,7 @@
       <c r="A13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="58" t="s">
         <v>74</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -4309,7 +4374,7 @@
       <c r="A14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="58" t="s">
         <v>79</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -4422,7 +4487,7 @@
       <c r="A15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="58" t="s">
         <v>84</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -4440,7 +4505,7 @@
       <c r="H15" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I15" s="51" t="s">
+      <c r="I15" s="58" t="s">
         <v>51</v>
       </c>
       <c r="J15" s="4">
@@ -6167,7 +6232,7 @@
       <c r="A30" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="58" t="s">
         <v>132</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -6520,7 +6585,7 @@
       <c r="BP31" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="BQ31" s="52" t="s">
+      <c r="BQ31" s="59" t="s">
         <v>51</v>
       </c>
     </row>
@@ -6528,7 +6593,7 @@
       <c r="A32" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="58" t="s">
         <v>145</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -6732,7 +6797,7 @@
       <c r="A33" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="51" t="s">
+      <c r="B33" s="58" t="s">
         <v>150</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -7084,19 +7149,19 @@
       <c r="BL34" s="15">
         <v>0.0603036102934573</v>
       </c>
-      <c r="BM34" s="52" t="s">
+      <c r="BM34" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="BN34" s="52" t="s">
+      <c r="BN34" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="BO34" s="52" t="s">
+      <c r="BO34" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="BP34" s="52" t="s">
+      <c r="BP34" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="BQ34" s="52" t="s">
+      <c r="BQ34" s="59" t="s">
         <v>51</v>
       </c>
     </row>
@@ -7253,7 +7318,7 @@
       <c r="BP35" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="BQ35" s="52" t="s">
+      <c r="BQ35" s="59" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8008,7 +8073,7 @@
       <c r="BP40" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="BQ40" s="52" t="s">
+      <c r="BQ40" s="59" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8162,7 +8227,7 @@
       <c r="BO41" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="BP41" s="52" t="s">
+      <c r="BP41" s="59" t="s">
         <v>51</v>
       </c>
       <c r="BQ41" s="17" t="s">
@@ -8319,7 +8384,7 @@
       <c r="BO42" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="BP42" s="52" t="s">
+      <c r="BP42" s="59" t="s">
         <v>51</v>
       </c>
       <c r="BQ42" s="17" t="s">
@@ -8455,19 +8520,19 @@
       <c r="BL43" s="14">
         <v>0.0406</v>
       </c>
-      <c r="BM43" s="53" t="s">
+      <c r="BM43" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BN43" s="53" t="s">
+      <c r="BN43" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BO43" s="53" t="s">
+      <c r="BO43" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BP43" s="53" t="s">
+      <c r="BP43" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BQ43" s="53" t="s">
+      <c r="BQ43" s="60" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8647,19 +8712,19 @@
       <c r="BL45" s="15">
         <v>0.113823071174797</v>
       </c>
-      <c r="BM45" s="53" t="s">
+      <c r="BM45" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BN45" s="53" t="s">
+      <c r="BN45" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BO45" s="53" t="s">
+      <c r="BO45" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BP45" s="53" t="s">
+      <c r="BP45" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BQ45" s="53" t="s">
+      <c r="BQ45" s="60" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8796,19 +8861,19 @@
       <c r="BL46" s="15">
         <v>0.0852474573735877</v>
       </c>
-      <c r="BM46" s="53" t="s">
+      <c r="BM46" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BN46" s="53" t="s">
+      <c r="BN46" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BO46" s="53" t="s">
+      <c r="BO46" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BP46" s="53" t="s">
+      <c r="BP46" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BQ46" s="53" t="s">
+      <c r="BQ46" s="60" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8945,19 +9010,19 @@
       <c r="BL47" s="15">
         <v>0.09350422314173</v>
       </c>
-      <c r="BM47" s="53" t="s">
+      <c r="BM47" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BN47" s="53" t="s">
+      <c r="BN47" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BO47" s="53" t="s">
+      <c r="BO47" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BP47" s="53" t="s">
+      <c r="BP47" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BQ47" s="53" t="s">
+      <c r="BQ47" s="60" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9094,19 +9159,19 @@
       <c r="BL48" s="15">
         <v>0.0923653113940854</v>
       </c>
-      <c r="BM48" s="53" t="s">
+      <c r="BM48" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BN48" s="53" t="s">
+      <c r="BN48" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BO48" s="53" t="s">
+      <c r="BO48" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BP48" s="53" t="s">
+      <c r="BP48" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BQ48" s="53" t="s">
+      <c r="BQ48" s="60" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9243,19 +9308,19 @@
       <c r="BL49" s="15">
         <v>0.078742377357387</v>
       </c>
-      <c r="BM49" s="53" t="s">
+      <c r="BM49" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BN49" s="53" t="s">
+      <c r="BN49" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BO49" s="53" t="s">
+      <c r="BO49" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BP49" s="53" t="s">
+      <c r="BP49" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BQ49" s="53" t="s">
+      <c r="BQ49" s="60" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9306,7 +9371,7 @@
       <c r="A51" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B51" s="51" t="s">
+      <c r="B51" s="58" t="s">
         <v>206</v>
       </c>
       <c r="C51" s="31" t="s">
@@ -9474,10 +9539,10 @@
       <c r="BO51" s="14">
         <v>0.0756</v>
       </c>
-      <c r="BP51" s="53" t="s">
+      <c r="BP51" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BQ51" s="53" t="s">
+      <c r="BQ51" s="60" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9485,7 +9550,7 @@
       <c r="A52" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B52" s="51" t="s">
+      <c r="B52" s="58" t="s">
         <v>211</v>
       </c>
       <c r="C52" s="31" t="s">
@@ -9674,7 +9739,7 @@
       <c r="BP52" s="14">
         <v>0.0756</v>
       </c>
-      <c r="BQ52" s="53" t="s">
+      <c r="BQ52" s="60" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9807,16 +9872,16 @@
       <c r="BL53" s="14">
         <v>0.0104</v>
       </c>
-      <c r="BM53" s="53" t="s">
+      <c r="BM53" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BN53" s="53" t="s">
+      <c r="BN53" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BO53" s="53" t="s">
+      <c r="BO53" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="BP53" s="53" t="s">
+      <c r="BP53" s="60" t="s">
         <v>51</v>
       </c>
       <c r="BQ53" s="17"/>
@@ -10063,7 +10128,7 @@
       <c r="A56" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="B56" s="54" t="s">
+      <c r="B56" s="61" t="s">
         <v>225</v>
       </c>
       <c r="C56" s="39" t="s">
@@ -10267,7 +10332,7 @@
       <c r="A57" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="B57" s="54" t="s">
+      <c r="B57" s="61" t="s">
         <v>230</v>
       </c>
       <c r="C57" s="39" t="s">
@@ -10471,7 +10536,7 @@
       <c r="A58" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="B58" s="54" t="s">
+      <c r="B58" s="61" t="s">
         <v>233</v>
       </c>
       <c r="C58" s="39" t="s">
@@ -10675,7 +10740,7 @@
       <c r="A59" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="B59" s="54" t="s">
+      <c r="B59" s="61" t="s">
         <v>236</v>
       </c>
       <c r="C59" s="39" t="s">
@@ -10879,7 +10944,7 @@
       <c r="A60" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="B60" s="54" t="s">
+      <c r="B60" s="61" t="s">
         <v>239</v>
       </c>
       <c r="C60" s="39" t="s">
@@ -11083,7 +11148,7 @@
       <c r="A61" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="B61" s="54" t="s">
+      <c r="B61" s="61" t="s">
         <v>242</v>
       </c>
       <c r="C61" s="39" t="s">
@@ -11287,7 +11352,7 @@
       <c r="A62" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="B62" s="54" t="s">
+      <c r="B62" s="61" t="s">
         <v>245</v>
       </c>
       <c r="C62" s="39" t="s">
@@ -11615,7 +11680,7 @@
       <c r="AR63" s="14">
         <v>0.2647</v>
       </c>
-      <c r="AS63" s="51" t="s">
+      <c r="AS63" s="58" t="s">
         <v>51</v>
       </c>
       <c r="AT63" s="14">
@@ -11693,7 +11758,7 @@
       <c r="A64" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="B64" s="54" t="s">
+      <c r="B64" s="61" t="s">
         <v>250</v>
       </c>
       <c r="C64" s="39" t="s">
@@ -11897,7 +11962,7 @@
       <c r="A65" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="B65" s="54" t="s">
+      <c r="B65" s="61" t="s">
         <v>253</v>
       </c>
       <c r="C65" s="39" t="s">
@@ -12101,7 +12166,7 @@
       <c r="A66" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="B66" s="54" t="s">
+      <c r="B66" s="61" t="s">
         <v>256</v>
       </c>
       <c r="C66" s="39" t="s">
@@ -12348,7 +12413,7 @@
       <c r="A68" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="B68" s="51" t="s">
+      <c r="B68" s="58" t="s">
         <v>259</v>
       </c>
       <c r="C68" s="31" t="s">
@@ -12565,7 +12630,7 @@
       <c r="A70" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="B70" s="55" t="s">
+      <c r="B70" s="62" t="s">
         <v>264</v>
       </c>
       <c r="C70" s="43" t="s">
@@ -12767,7 +12832,7 @@
       <c r="A71" s="42" t="s">
         <v>268</v>
       </c>
-      <c r="B71" s="55" t="s">
+      <c r="B71" s="62" t="s">
         <v>269</v>
       </c>
       <c r="C71" s="43" t="s">
@@ -12965,73 +13030,525 @@
         <v>0.0955</v>
       </c>
     </row>
-    <row r="72" spans="1:69">
+    <row r="72" ht="81" spans="1:69">
       <c r="A72" s="42" t="s">
         <v>273</v>
       </c>
-      <c r="B72" s="55" t="s">
+      <c r="B72" s="42">
+        <v>399998</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="K72" s="13"/>
-      <c r="W72" s="41"/>
-      <c r="X72" s="41"/>
-      <c r="Y72" s="41"/>
-      <c r="Z72" s="41"/>
-      <c r="AA72" s="41"/>
-      <c r="AB72" s="41"/>
-      <c r="AC72" s="41"/>
-      <c r="AD72" s="41"/>
-      <c r="AE72" s="41"/>
-      <c r="AF72" s="41"/>
-      <c r="AG72" s="41"/>
+      <c r="D72" s="4">
+        <v>30</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J72" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K72" s="45">
+        <v>39813</v>
+      </c>
+      <c r="L72" s="6">
+        <v>42048</v>
+      </c>
+      <c r="Q72" s="46">
+        <v>2.0243</v>
+      </c>
+      <c r="R72" s="46">
+        <v>-0.012</v>
+      </c>
+      <c r="S72" s="46">
+        <v>-0.2969</v>
+      </c>
+      <c r="T72" s="46">
+        <v>-0.0729</v>
+      </c>
+      <c r="U72" s="46">
+        <v>-0.4135</v>
+      </c>
+      <c r="V72" s="46">
+        <v>0.2818</v>
+      </c>
+      <c r="W72" s="46">
+        <v>0.0492</v>
+      </c>
+      <c r="X72" s="46">
+        <v>0.0269</v>
+      </c>
+      <c r="Y72" s="46">
+        <v>0.12</v>
+      </c>
+      <c r="Z72" s="46">
+        <v>-0.3486</v>
+      </c>
+      <c r="AA72" s="46">
+        <v>0.1086</v>
+      </c>
+      <c r="AB72" s="46">
+        <v>0.0742</v>
+      </c>
+      <c r="AC72" s="46">
+        <v>0.4281</v>
+      </c>
+      <c r="AD72" s="46">
+        <v>0.102</v>
+      </c>
+      <c r="AE72" s="46">
+        <v>0.0326</v>
+      </c>
+      <c r="AF72" s="46">
+        <v>-0.0296</v>
+      </c>
+      <c r="AG72" s="46">
+        <v>-0.0877</v>
+      </c>
       <c r="AH72" s="41"/>
-    </row>
-    <row r="73" spans="1:69">
+      <c r="AI72" s="7">
+        <f>SUM(Q72:AG72)/17</f>
+        <v>0.116852941176471</v>
+      </c>
+      <c r="AO72" s="46">
+        <v>0.5125</v>
+      </c>
+      <c r="AP72" s="46">
+        <v>0.4012</v>
+      </c>
+      <c r="AQ72" s="46">
+        <v>0.3151</v>
+      </c>
+      <c r="AR72" s="46">
+        <v>0.312</v>
+      </c>
+      <c r="AS72" s="46">
+        <v>0.2909</v>
+      </c>
+      <c r="AT72" s="46">
+        <v>0.2698</v>
+      </c>
+      <c r="AU72" s="46">
+        <v>0.4882</v>
+      </c>
+      <c r="AV72" s="46">
+        <v>0.347</v>
+      </c>
+      <c r="AW72" s="46">
+        <v>0.2453</v>
+      </c>
+      <c r="AX72" s="46">
+        <v>0.2717</v>
+      </c>
+      <c r="AY72" s="46">
+        <v>0.2417</v>
+      </c>
+      <c r="AZ72" s="46">
+        <v>0.299</v>
+      </c>
+      <c r="BA72" s="46">
+        <v>0.422</v>
+      </c>
+      <c r="BB72" s="46">
+        <v>0.3698</v>
+      </c>
+      <c r="BC72" s="46">
+        <v>0.1906</v>
+      </c>
+      <c r="BD72" s="46">
+        <v>0.2702</v>
+      </c>
+      <c r="BE72" s="46">
+        <v>0.2152</v>
+      </c>
+      <c r="BG72" s="47">
+        <v>-0.0876612559921522</v>
+      </c>
+      <c r="BH72" s="47">
+        <v>-0.0294923264089031</v>
+      </c>
+      <c r="BI72" s="47">
+        <v>0.075428131221329</v>
+      </c>
+      <c r="BJ72" s="47">
+        <v>0.0799281177142273</v>
+      </c>
+      <c r="BK72" s="47">
+        <v>0.0250782339861382</v>
+      </c>
+      <c r="BL72" s="47">
+        <v>0.0274148186713365</v>
+      </c>
+      <c r="BM72" s="47">
+        <v>0.000945672848502443</v>
+      </c>
+      <c r="BN72" s="47">
+        <v>-0.027332824660263</v>
+      </c>
+      <c r="BO72" s="47">
+        <v>0.040743502432081</v>
+      </c>
+      <c r="BP72" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="BQ72" s="48" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" ht="81" spans="1:69">
       <c r="A73" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="B73" s="42">
+        <v>930606</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D73" s="4">
+        <v>49</v>
+      </c>
+      <c r="E73" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="B73" s="55" t="s">
-        <v>276</v>
-      </c>
-      <c r="K73" s="13"/>
-      <c r="W73" s="41"/>
-      <c r="X73" s="41"/>
-      <c r="Y73" s="41"/>
-      <c r="Z73" s="41"/>
-      <c r="AA73" s="41"/>
-      <c r="AB73" s="41"/>
-      <c r="AC73" s="41"/>
-      <c r="AD73" s="41"/>
-      <c r="AE73" s="41"/>
-      <c r="AF73" s="41"/>
-      <c r="AG73" s="41"/>
+      <c r="F73" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J73" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K73" s="45">
+        <v>39813</v>
+      </c>
+      <c r="L73" s="6">
+        <v>42094</v>
+      </c>
+      <c r="Q73" s="46">
+        <v>0.9878</v>
+      </c>
+      <c r="R73" s="46">
+        <v>-0.3105</v>
+      </c>
+      <c r="S73" s="46">
+        <v>-0.2642</v>
+      </c>
+      <c r="T73" s="46">
+        <v>-0.0536</v>
+      </c>
+      <c r="U73" s="46">
+        <v>-0.2087</v>
+      </c>
+      <c r="V73" s="46">
+        <v>0.7128</v>
+      </c>
+      <c r="W73" s="46">
+        <v>0.0943</v>
+      </c>
+      <c r="X73" s="46">
+        <v>-0.0828</v>
+      </c>
+      <c r="Y73" s="46">
+        <v>0.0972</v>
+      </c>
+      <c r="Z73" s="46">
+        <v>-0.3265</v>
+      </c>
+      <c r="AA73" s="46">
+        <v>-0.0157</v>
+      </c>
+      <c r="AB73" s="46">
+        <v>0.0178</v>
+      </c>
+      <c r="AC73" s="46">
+        <v>0.3411</v>
+      </c>
+      <c r="AD73" s="46">
+        <v>-0.2449</v>
+      </c>
+      <c r="AE73" s="46">
+        <v>-0.0689</v>
+      </c>
+      <c r="AF73" s="46">
+        <v>0.008</v>
+      </c>
+      <c r="AG73" s="46">
+        <v>0.2751</v>
+      </c>
       <c r="AH73" s="41"/>
-    </row>
-    <row r="74" spans="1:69">
-      <c r="A74" s="42" t="s">
-        <v>277</v>
-      </c>
-      <c r="B74" s="42" t="s">
-        <v>278</v>
-      </c>
-      <c r="K74" s="13"/>
-      <c r="W74" s="41"/>
-      <c r="X74" s="41"/>
-      <c r="Y74" s="41"/>
-      <c r="Z74" s="41"/>
-      <c r="AA74" s="41"/>
-      <c r="AB74" s="41"/>
-      <c r="AC74" s="41"/>
-      <c r="AD74" s="41"/>
-      <c r="AE74" s="41"/>
-      <c r="AF74" s="41"/>
-      <c r="AG74" s="41"/>
+      <c r="AI73" s="7">
+        <f>SUM(Q73:AG73)/17</f>
+        <v>0.0563705882352941</v>
+      </c>
+      <c r="AO73" s="46">
+        <v>0.4175</v>
+      </c>
+      <c r="AP73" s="46">
+        <v>0.2817</v>
+      </c>
+      <c r="AQ73" s="46">
+        <v>0.2413</v>
+      </c>
+      <c r="AR73" s="46">
+        <v>0.22</v>
+      </c>
+      <c r="AS73" s="46">
+        <v>0.197</v>
+      </c>
+      <c r="AT73" s="46">
+        <v>0.2366</v>
+      </c>
+      <c r="AU73" s="46">
+        <v>0.433</v>
+      </c>
+      <c r="AV73" s="46">
+        <v>0.3204</v>
+      </c>
+      <c r="AW73" s="46">
+        <v>0.2199</v>
+      </c>
+      <c r="AX73" s="46">
+        <v>0.239</v>
+      </c>
+      <c r="AY73" s="46">
+        <v>0.2289</v>
+      </c>
+      <c r="AZ73" s="46">
+        <v>0.2497</v>
+      </c>
+      <c r="BA73" s="46">
+        <v>0.3533</v>
+      </c>
+      <c r="BB73" s="46">
+        <v>0.2477</v>
+      </c>
+      <c r="BC73" s="46">
+        <v>0.1547</v>
+      </c>
+      <c r="BD73" s="46">
+        <v>0.2545</v>
+      </c>
+      <c r="BE73" s="46">
+        <v>0.2109</v>
+      </c>
+      <c r="BG73" s="49">
+        <v>0.27512341422301</v>
+      </c>
+      <c r="BH73" s="49">
+        <v>0.0616982403006807</v>
+      </c>
+      <c r="BI73" s="49">
+        <v>0.0391906921963963</v>
+      </c>
+      <c r="BJ73" s="49">
+        <v>0.0281098648669311</v>
+      </c>
+      <c r="BK73" s="49">
+        <v>-0.0119723692464356</v>
+      </c>
+      <c r="BL73" s="49">
+        <v>-0.00947559580708957</v>
+      </c>
+      <c r="BM73" s="49">
+        <v>0.0154513499284832</v>
+      </c>
+      <c r="BN73" s="49">
+        <v>-0.0107810374242893</v>
+      </c>
+      <c r="BO73" s="49">
+        <v>0.00902100998653288</v>
+      </c>
+      <c r="BP73" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="BQ73" s="50" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="74" ht="40.5" spans="1:69">
+      <c r="A74" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="B74" s="42">
+        <v>930632</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D74" s="4">
+        <v>50</v>
+      </c>
+      <c r="E74" s="52" t="s">
+        <v>283</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J74" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K74" s="6">
+        <v>40908</v>
+      </c>
+      <c r="L74" s="6">
+        <v>42136</v>
+      </c>
+      <c r="T74" s="46">
+        <v>0.2845</v>
+      </c>
+      <c r="U74" s="46">
+        <v>-0.3169</v>
+      </c>
+      <c r="V74" s="46">
+        <v>0.364</v>
+      </c>
+      <c r="W74" s="46">
+        <v>0.0918</v>
+      </c>
+      <c r="X74" s="46">
+        <v>-0.1478</v>
+      </c>
+      <c r="Y74" s="46">
+        <v>0.3972</v>
+      </c>
+      <c r="Z74" s="46">
+        <v>-0.4247</v>
+      </c>
+      <c r="AA74" s="46">
+        <v>0.2623</v>
+      </c>
+      <c r="AB74" s="46">
+        <v>0.3642</v>
+      </c>
+      <c r="AC74" s="46">
+        <v>0.784</v>
+      </c>
+      <c r="AD74" s="46">
+        <v>-0.2596</v>
+      </c>
+      <c r="AE74" s="46">
+        <v>-0.2471</v>
+      </c>
+      <c r="AF74" s="46">
+        <v>-0.066</v>
+      </c>
+      <c r="AG74" s="46">
+        <v>0.8939</v>
+      </c>
       <c r="AH74" s="41"/>
+      <c r="AI74" s="7">
+        <f>SUM(T74:AG74)/14</f>
+        <v>0.141414285714286</v>
+      </c>
+      <c r="AR74" s="46">
+        <v>0.356</v>
+      </c>
+      <c r="AS74" s="46">
+        <v>0.3042</v>
+      </c>
+      <c r="AT74" s="46">
+        <v>0.2529</v>
+      </c>
+      <c r="AU74" s="46">
+        <v>0.5012</v>
+      </c>
+      <c r="AV74" s="46">
+        <v>0.3771</v>
+      </c>
+      <c r="AW74" s="46">
+        <v>0.3215</v>
+      </c>
+      <c r="AX74" s="46">
+        <v>0.323</v>
+      </c>
+      <c r="AY74" s="46">
+        <v>0.3101</v>
+      </c>
+      <c r="AZ74" s="46">
+        <v>0.377</v>
+      </c>
+      <c r="BA74" s="46">
+        <v>0.4622</v>
+      </c>
+      <c r="BB74" s="46">
+        <v>0.3643</v>
+      </c>
+      <c r="BC74" s="46">
+        <v>0.2226</v>
+      </c>
+      <c r="BD74" s="46">
+        <v>0.3429</v>
+      </c>
+      <c r="BE74" s="46">
+        <v>0.3035</v>
+      </c>
+      <c r="BG74" s="49">
+        <v>0.893872817833167</v>
+      </c>
+      <c r="BH74" s="49">
+        <v>0.100205205159584</v>
+      </c>
+      <c r="BI74" s="49">
+        <v>0.119569229540326</v>
+      </c>
+      <c r="BJ74" s="49">
+        <v>0.171535040660459</v>
+      </c>
+      <c r="BK74" s="49">
+        <v>0.103920760507768</v>
+      </c>
+      <c r="BL74" s="49">
+        <v>0.0771621992656473</v>
+      </c>
+      <c r="BM74" s="49">
+        <v>0.0591421027895198</v>
+      </c>
+      <c r="BN74" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="BO74" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="BP74" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="BQ74" s="50" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="75" spans="1:69">
-      <c r="A75" s="42"/>
+      <c r="A75" s="43"/>
       <c r="B75" s="42"/>
-      <c r="K75" s="13"/>
       <c r="W75" s="41"/>
       <c r="X75" s="41"/>
       <c r="Y75" s="41"/>
@@ -13047,10 +13564,10 @@
     </row>
     <row r="76" spans="1:69">
       <c r="A76" s="42" t="s">
-        <v>279</v>
-      </c>
-      <c r="B76" s="42">
-        <v>399812</v>
+        <v>286</v>
+      </c>
+      <c r="B76" s="62" t="s">
+        <v>287</v>
       </c>
       <c r="K76" s="13"/>
       <c r="W76" s="41"/>
@@ -13068,10 +13585,10 @@
     </row>
     <row r="77" spans="1:69">
       <c r="A77" s="42" t="s">
-        <v>280</v>
-      </c>
-      <c r="B77" s="42">
-        <v>399808</v>
+        <v>288</v>
+      </c>
+      <c r="B77" s="62" t="s">
+        <v>289</v>
       </c>
       <c r="K77" s="13"/>
       <c r="W77" s="41"/>
@@ -13089,10 +13606,10 @@
     </row>
     <row r="78" spans="1:69">
       <c r="A78" s="42" t="s">
-        <v>281</v>
-      </c>
-      <c r="B78" s="42">
-        <v>399967</v>
+        <v>290</v>
+      </c>
+      <c r="B78" s="42" t="s">
+        <v>291</v>
       </c>
       <c r="K78" s="13"/>
       <c r="W78" s="41"/>
@@ -13109,12 +13626,8 @@
       <c r="AH78" s="41"/>
     </row>
     <row r="79" spans="1:69">
-      <c r="A79" s="42" t="s">
-        <v>282</v>
-      </c>
-      <c r="B79" s="42">
-        <v>399971</v>
-      </c>
+      <c r="A79" s="42"/>
+      <c r="B79" s="42"/>
       <c r="K79" s="13"/>
       <c r="W79" s="41"/>
       <c r="X79" s="41"/>
@@ -13131,10 +13644,10 @@
     </row>
     <row r="80" spans="1:69">
       <c r="A80" s="42" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="B80" s="42">
-        <v>399973</v>
+        <v>399812</v>
       </c>
       <c r="K80" s="13"/>
       <c r="W80" s="41"/>
@@ -13151,8 +13664,12 @@
       <c r="AH80" s="41"/>
     </row>
     <row r="81" spans="1:34">
-      <c r="A81" s="42"/>
-      <c r="B81" s="42"/>
+      <c r="A81" s="42" t="s">
+        <v>293</v>
+      </c>
+      <c r="B81" s="42">
+        <v>399808</v>
+      </c>
       <c r="K81" s="13"/>
       <c r="W81" s="41"/>
       <c r="X81" s="41"/>
@@ -13169,10 +13686,10 @@
     </row>
     <row r="82" spans="1:34">
       <c r="A82" s="42" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B82" s="42">
-        <v>399986</v>
+        <v>399967</v>
       </c>
       <c r="K82" s="13"/>
       <c r="W82" s="41"/>
@@ -13190,10 +13707,10 @@
     </row>
     <row r="83" spans="1:34">
       <c r="A83" s="42" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B83" s="42">
-        <v>399975</v>
+        <v>399971</v>
       </c>
       <c r="K83" s="13"/>
       <c r="W83" s="41"/>
@@ -13211,10 +13728,10 @@
     </row>
     <row r="84" spans="1:34">
       <c r="A84" s="42" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B84" s="42">
-        <v>399997</v>
+        <v>399973</v>
       </c>
       <c r="K84" s="13"/>
       <c r="W84" s="41"/>
@@ -13231,12 +13748,8 @@
       <c r="AH84" s="41"/>
     </row>
     <row r="85" spans="1:34">
-      <c r="A85" s="42" t="s">
-        <v>287</v>
-      </c>
-      <c r="B85" s="42">
-        <v>399998</v>
-      </c>
+      <c r="A85" s="42"/>
+      <c r="B85" s="42"/>
       <c r="K85" s="13"/>
       <c r="W85" s="41"/>
       <c r="X85" s="41"/>
@@ -13253,10 +13766,10 @@
     </row>
     <row r="86" spans="1:34">
       <c r="A86" s="42" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B86" s="42">
-        <v>930697</v>
+        <v>399986</v>
       </c>
       <c r="K86" s="13"/>
       <c r="W86" s="41"/>
@@ -13273,8 +13786,12 @@
       <c r="AH86" s="41"/>
     </row>
     <row r="87" spans="1:34">
-      <c r="A87" s="42"/>
-      <c r="B87" s="42"/>
+      <c r="A87" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="B87" s="42">
+        <v>399975</v>
+      </c>
       <c r="K87" s="13"/>
       <c r="W87" s="41"/>
       <c r="X87" s="41"/>
@@ -13290,11 +13807,11 @@
       <c r="AH87" s="41"/>
     </row>
     <row r="88" spans="1:34">
-      <c r="A88" s="43" t="s">
-        <v>289</v>
-      </c>
-      <c r="B88" s="45">
-        <v>930607</v>
+      <c r="A88" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="B88" s="42">
+        <v>399997</v>
       </c>
       <c r="K88" s="13"/>
       <c r="W88" s="41"/>
@@ -13310,33 +13827,12 @@
       <c r="AG88" s="41"/>
       <c r="AH88" s="41"/>
     </row>
-    <row r="89" spans="1:34">
-      <c r="A89" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="B89" s="42">
-        <v>930601</v>
-      </c>
-      <c r="K89" s="13"/>
-      <c r="W89" s="41"/>
-      <c r="X89" s="41"/>
-      <c r="Y89" s="41"/>
-      <c r="Z89" s="41"/>
-      <c r="AA89" s="41"/>
-      <c r="AB89" s="41"/>
-      <c r="AC89" s="41"/>
-      <c r="AD89" s="41"/>
-      <c r="AE89" s="41"/>
-      <c r="AF89" s="41"/>
-      <c r="AG89" s="41"/>
-      <c r="AH89" s="41"/>
-    </row>
     <row r="90" spans="1:34">
       <c r="A90" s="42" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B90" s="42">
-        <v>930606</v>
+        <v>930697</v>
       </c>
       <c r="K90" s="13"/>
       <c r="W90" s="41"/>
@@ -13353,12 +13849,8 @@
       <c r="AH90" s="41"/>
     </row>
     <row r="91" spans="1:34">
-      <c r="A91" s="42" t="s">
-        <v>292</v>
-      </c>
-      <c r="B91" s="42">
-        <v>930633</v>
-      </c>
+      <c r="A91" s="42"/>
+      <c r="B91" s="42"/>
       <c r="K91" s="13"/>
       <c r="W91" s="41"/>
       <c r="X91" s="41"/>
@@ -13374,11 +13866,11 @@
       <c r="AH91" s="41"/>
     </row>
     <row r="92" spans="1:34">
-      <c r="A92" s="42" t="s">
-        <v>293</v>
-      </c>
-      <c r="B92" s="42">
-        <v>931574</v>
+      <c r="A92" s="43" t="s">
+        <v>301</v>
+      </c>
+      <c r="B92" s="53">
+        <v>930607</v>
       </c>
       <c r="K92" s="13"/>
       <c r="W92" s="41"/>
@@ -13395,7 +13887,15 @@
       <c r="AH92" s="41"/>
     </row>
     <row r="93" spans="1:34">
-      <c r="K93" s="13"/>
+      <c r="A93" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="B93" s="42">
+        <v>930601</v>
+      </c>
+      <c r="K93" s="54">
+        <v>38352</v>
+      </c>
       <c r="W93" s="41"/>
       <c r="X93" s="41"/>
       <c r="Y93" s="41"/>
@@ -13409,33 +13909,14 @@
       <c r="AG93" s="41"/>
       <c r="AH93" s="41"/>
     </row>
-    <row r="94" spans="1:34">
-      <c r="A94" s="43" t="s">
-        <v>294</v>
-      </c>
-      <c r="B94" s="42">
-        <v>931061</v>
-      </c>
-      <c r="W94" s="41"/>
-      <c r="X94" s="41"/>
-      <c r="Y94" s="41"/>
-      <c r="Z94" s="41"/>
-      <c r="AA94" s="41"/>
-      <c r="AB94" s="41"/>
-      <c r="AC94" s="41"/>
-      <c r="AD94" s="41"/>
-      <c r="AE94" s="41"/>
-      <c r="AF94" s="41"/>
-      <c r="AG94" s="41"/>
-      <c r="AH94" s="41"/>
-    </row>
     <row r="95" spans="1:34">
-      <c r="A95" s="43" t="s">
-        <v>295</v>
+      <c r="A95" s="42" t="s">
+        <v>303</v>
       </c>
       <c r="B95" s="42">
-        <v>930914</v>
-      </c>
+        <v>930633</v>
+      </c>
+      <c r="K95" s="13"/>
       <c r="W95" s="41"/>
       <c r="X95" s="41"/>
       <c r="Y95" s="41"/>
@@ -13450,15 +13931,13 @@
       <c r="AH95" s="41"/>
     </row>
     <row r="96" spans="1:34">
-      <c r="A96" s="43" t="s">
-        <v>296</v>
+      <c r="A96" s="42" t="s">
+        <v>304</v>
       </c>
       <c r="B96" s="42">
-        <v>930945</v>
-      </c>
-      <c r="K96" s="46">
-        <v>38352</v>
-      </c>
+        <v>931574</v>
+      </c>
+      <c r="K96" s="13"/>
       <c r="W96" s="41"/>
       <c r="X96" s="41"/>
       <c r="Y96" s="41"/>
@@ -13473,8 +13952,7 @@
       <c r="AH96" s="41"/>
     </row>
     <row r="97" spans="1:34">
-      <c r="A97" s="42"/>
-      <c r="B97" s="42"/>
+      <c r="K97" s="13"/>
       <c r="W97" s="41"/>
       <c r="X97" s="41"/>
       <c r="Y97" s="41"/>
@@ -13488,38 +13966,12 @@
       <c r="AG97" s="41"/>
       <c r="AH97" s="41"/>
     </row>
-    <row r="98" spans="1:34">
-      <c r="A98" s="43" t="s">
-        <v>297</v>
-      </c>
-      <c r="B98" s="42">
-        <v>930902</v>
-      </c>
-      <c r="K98" s="47">
-        <v>41274</v>
-      </c>
-      <c r="W98" s="41"/>
-      <c r="X98" s="41"/>
-      <c r="Y98" s="41"/>
-      <c r="Z98" s="41"/>
-      <c r="AA98" s="41"/>
-      <c r="AB98" s="41"/>
-      <c r="AC98" s="41"/>
-      <c r="AD98" s="41"/>
-      <c r="AE98" s="41"/>
-      <c r="AF98" s="41"/>
-      <c r="AG98" s="41"/>
-      <c r="AH98" s="41"/>
-    </row>
     <row r="99" spans="1:34">
-      <c r="A99" s="42" t="s">
-        <v>298</v>
+      <c r="A99" s="43" t="s">
+        <v>305</v>
       </c>
       <c r="B99" s="42">
-        <v>931071</v>
-      </c>
-      <c r="K99" s="47">
-        <v>42004</v>
+        <v>930914</v>
       </c>
       <c r="W99" s="41"/>
       <c r="X99" s="41"/>
@@ -13535,15 +13987,14 @@
       <c r="AH99" s="41"/>
     </row>
     <row r="100" spans="1:34">
-      <c r="A100" s="42" t="s">
-        <v>299</v>
-      </c>
-      <c r="B100" s="42"/>
-      <c r="C100" s="43" t="s">
-        <v>300</v>
-      </c>
-      <c r="K100" s="47">
-        <v>41089</v>
+      <c r="A100" s="43" t="s">
+        <v>306</v>
+      </c>
+      <c r="B100" s="42">
+        <v>930945</v>
+      </c>
+      <c r="K100" s="54">
+        <v>38352</v>
       </c>
       <c r="W100" s="41"/>
       <c r="X100" s="41"/>
@@ -13559,12 +14010,8 @@
       <c r="AH100" s="41"/>
     </row>
     <row r="101" spans="1:34">
-      <c r="A101" s="42" t="s">
-        <v>301</v>
-      </c>
-      <c r="B101" s="42">
-        <v>931582</v>
-      </c>
+      <c r="A101" s="42"/>
+      <c r="B101" s="42"/>
       <c r="W101" s="41"/>
       <c r="X101" s="41"/>
       <c r="Y101" s="41"/>
@@ -13579,13 +14026,13 @@
       <c r="AH101" s="41"/>
     </row>
     <row r="102" spans="1:34">
-      <c r="A102" s="42" t="s">
-        <v>302</v>
+      <c r="A102" s="43" t="s">
+        <v>307</v>
       </c>
       <c r="B102" s="42">
-        <v>931151</v>
-      </c>
-      <c r="K102" s="47">
+        <v>930902</v>
+      </c>
+      <c r="K102" s="55">
         <v>41274</v>
       </c>
       <c r="W102" s="41"/>
@@ -13602,8 +14049,15 @@
       <c r="AH102" s="41"/>
     </row>
     <row r="103" spans="1:34">
-      <c r="A103" s="42"/>
-      <c r="B103" s="42"/>
+      <c r="A103" s="42" t="s">
+        <v>308</v>
+      </c>
+      <c r="B103" s="42">
+        <v>931071</v>
+      </c>
+      <c r="K103" s="55">
+        <v>42004</v>
+      </c>
       <c r="W103" s="41"/>
       <c r="X103" s="41"/>
       <c r="Y103" s="41"/>
@@ -13619,13 +14073,14 @@
     </row>
     <row r="104" spans="1:34">
       <c r="A104" s="42" t="s">
-        <v>303</v>
-      </c>
-      <c r="B104" s="42">
-        <v>930641</v>
-      </c>
-      <c r="K104" s="46">
-        <v>38352</v>
+        <v>309</v>
+      </c>
+      <c r="B104" s="42"/>
+      <c r="C104" s="43" t="s">
+        <v>310</v>
+      </c>
+      <c r="K104" s="55">
+        <v>41089</v>
       </c>
       <c r="W104" s="41"/>
       <c r="X104" s="41"/>
@@ -13642,13 +14097,13 @@
     </row>
     <row r="105" spans="1:34">
       <c r="A105" s="42" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B105" s="42">
-        <v>931152</v>
-      </c>
-      <c r="K105" s="46">
-        <v>42004</v>
+        <v>931582</v>
+      </c>
+      <c r="K105" s="55">
+        <v>42734</v>
       </c>
       <c r="W105" s="41"/>
       <c r="X105" s="41"/>
@@ -13664,17 +14119,14 @@
       <c r="AH105" s="41"/>
     </row>
     <row r="106" spans="1:34">
-      <c r="A106" s="43" t="s">
-        <v>305</v>
+      <c r="A106" s="42" t="s">
+        <v>312</v>
       </c>
       <c r="B106" s="42">
-        <v>931153</v>
-      </c>
-      <c r="C106" s="48" t="s">
-        <v>306</v>
-      </c>
-      <c r="K106" s="46">
-        <v>41089</v>
+        <v>931151</v>
+      </c>
+      <c r="K106" s="55">
+        <v>41274</v>
       </c>
       <c r="W106" s="41"/>
       <c r="X106" s="41"/>
@@ -13690,22 +14142,30 @@
       <c r="AH106" s="41"/>
     </row>
     <row r="107" spans="1:34">
-      <c r="A107" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B107" s="51" t="s">
-        <v>308</v>
-      </c>
+      <c r="A107" s="42"/>
+      <c r="B107" s="42"/>
+      <c r="W107" s="41"/>
+      <c r="X107" s="41"/>
+      <c r="Y107" s="41"/>
+      <c r="Z107" s="41"/>
+      <c r="AA107" s="41"/>
+      <c r="AB107" s="41"/>
+      <c r="AC107" s="41"/>
+      <c r="AD107" s="41"/>
+      <c r="AE107" s="41"/>
+      <c r="AF107" s="41"/>
+      <c r="AG107" s="41"/>
+      <c r="AH107" s="41"/>
     </row>
     <row r="108" spans="1:34">
-      <c r="A108" s="49" t="s">
-        <v>309</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C108" s="49" t="s">
-        <v>311</v>
+      <c r="A108" s="42" t="s">
+        <v>313</v>
+      </c>
+      <c r="B108" s="42">
+        <v>930641</v>
+      </c>
+      <c r="K108" s="54">
+        <v>38352</v>
       </c>
       <c r="W108" s="41"/>
       <c r="X108" s="41"/>
@@ -13721,6 +14181,15 @@
       <c r="AH108" s="41"/>
     </row>
     <row r="109" spans="1:34">
+      <c r="A109" s="42" t="s">
+        <v>314</v>
+      </c>
+      <c r="B109" s="42">
+        <v>931152</v>
+      </c>
+      <c r="K109" s="54">
+        <v>42004</v>
+      </c>
       <c r="W109" s="41"/>
       <c r="X109" s="41"/>
       <c r="Y109" s="41"/>
@@ -13735,6 +14204,18 @@
       <c r="AH109" s="41"/>
     </row>
     <row r="110" spans="1:34">
+      <c r="A110" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="B110" s="42">
+        <v>931153</v>
+      </c>
+      <c r="C110" s="56" t="s">
+        <v>316</v>
+      </c>
+      <c r="K110" s="54">
+        <v>41089</v>
+      </c>
       <c r="W110" s="41"/>
       <c r="X110" s="41"/>
       <c r="Y110" s="41"/>
@@ -13749,20 +14230,26 @@
       <c r="AH110" s="41"/>
     </row>
     <row r="111" spans="1:34">
-      <c r="W111" s="41"/>
-      <c r="X111" s="41"/>
-      <c r="Y111" s="41"/>
-      <c r="Z111" s="41"/>
-      <c r="AA111" s="41"/>
-      <c r="AB111" s="41"/>
-      <c r="AC111" s="41"/>
-      <c r="AD111" s="41"/>
-      <c r="AE111" s="41"/>
-      <c r="AF111" s="41"/>
-      <c r="AG111" s="41"/>
-      <c r="AH111" s="41"/>
+      <c r="A111" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B111" s="58" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="112" spans="1:34">
+      <c r="A112" s="43" t="s">
+        <v>319</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C112" s="43" t="s">
+        <v>321</v>
+      </c>
+      <c r="K112" s="54">
+        <v>38352</v>
+      </c>
       <c r="W112" s="41"/>
       <c r="X112" s="41"/>
       <c r="Y112" s="41"/>
@@ -16003,51 +16490,18 @@
       <c r="AH271" s="41"/>
     </row>
     <row r="272" spans="23:34">
-      <c r="W272" s="50" t="e">
-        <f t="shared" ref="W272:AG272" si="1">(F272-F3)/F3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X272" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y272" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Z272" s="50" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AA272" s="50">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="AB272" s="50">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="AC272" s="50">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="AD272" s="50" t="e">
-        <f>(W272-W10)/W10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AE272" s="50" t="e">
-        <f>(X272-#REF!)/#REF!</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AF272" s="50" t="e">
-        <f>(Y272-#REF!)/#REF!</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AG272" s="50" t="e">
-        <f>(Z272-#REF!)/#REF!</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AH272" s="50"/>
+      <c r="W272" s="41"/>
+      <c r="X272" s="41"/>
+      <c r="Y272" s="41"/>
+      <c r="Z272" s="41"/>
+      <c r="AA272" s="41"/>
+      <c r="AB272" s="41"/>
+      <c r="AC272" s="41"/>
+      <c r="AD272" s="41"/>
+      <c r="AE272" s="41"/>
+      <c r="AF272" s="41"/>
+      <c r="AG272" s="41"/>
+      <c r="AH272" s="41"/>
     </row>
     <row r="273" spans="23:34">
       <c r="W273" s="41"/>
@@ -16092,18 +16546,51 @@
       <c r="AH275" s="41"/>
     </row>
     <row r="276" spans="23:34">
-      <c r="W276" s="41"/>
-      <c r="X276" s="41"/>
-      <c r="Y276" s="41"/>
-      <c r="Z276" s="41"/>
-      <c r="AA276" s="41"/>
-      <c r="AB276" s="41"/>
-      <c r="AC276" s="41"/>
-      <c r="AD276" s="41"/>
-      <c r="AE276" s="41"/>
-      <c r="AF276" s="41"/>
-      <c r="AG276" s="41"/>
-      <c r="AH276" s="41"/>
+      <c r="W276" s="57" t="e">
+        <f t="shared" ref="W276:AG276" si="1">(F276-F3)/F3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X276" s="57" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y276" s="57" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z276" s="57" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AA276" s="57">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="AB276" s="57">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="AC276" s="57">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="AD276" s="57" t="e">
+        <f>(W276-W10)/W10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AE276" s="57" t="e">
+        <f>(X276-#REF!)/#REF!</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AF276" s="57" t="e">
+        <f>(Y276-#REF!)/#REF!</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AG276" s="57" t="e">
+        <f>(Z276-#REF!)/#REF!</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AH276" s="57"/>
     </row>
     <row r="277" spans="23:34">
       <c r="W277" s="41"/>
@@ -19452,51 +19939,18 @@
       <c r="AH515" s="41"/>
     </row>
     <row r="516" spans="23:34">
-      <c r="W516" s="50" t="e">
-        <f t="shared" ref="W516:AG516" si="2">(F516-F272)/F272</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X516" s="50" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y516" s="50" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z516" s="50" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA516" s="50" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB516" s="50" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC516" s="50" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD516" s="50" t="e">
-        <f>(W516-W272)/W272</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE516" s="50" t="e">
-        <f>(X516-X272)/X272</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF516" s="50" t="e">
-        <f>(Y516-Y272)/Y272</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG516" s="50" t="e">
-        <f>(Z516-Z272)/Z272</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH516" s="50"/>
+      <c r="W516" s="41"/>
+      <c r="X516" s="41"/>
+      <c r="Y516" s="41"/>
+      <c r="Z516" s="41"/>
+      <c r="AA516" s="41"/>
+      <c r="AB516" s="41"/>
+      <c r="AC516" s="41"/>
+      <c r="AD516" s="41"/>
+      <c r="AE516" s="41"/>
+      <c r="AF516" s="41"/>
+      <c r="AG516" s="41"/>
+      <c r="AH516" s="41"/>
     </row>
     <row r="517" spans="23:34">
       <c r="W517" s="41"/>
@@ -19541,18 +19995,51 @@
       <c r="AH519" s="41"/>
     </row>
     <row r="520" spans="23:34">
-      <c r="W520" s="41"/>
-      <c r="X520" s="41"/>
-      <c r="Y520" s="41"/>
-      <c r="Z520" s="41"/>
-      <c r="AA520" s="41"/>
-      <c r="AB520" s="41"/>
-      <c r="AC520" s="41"/>
-      <c r="AD520" s="41"/>
-      <c r="AE520" s="41"/>
-      <c r="AF520" s="41"/>
-      <c r="AG520" s="41"/>
-      <c r="AH520" s="41"/>
+      <c r="W520" s="57" t="e">
+        <f t="shared" ref="W520:AG520" si="2">(F520-F276)/F276</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X520" s="57" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y520" s="57" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z520" s="57" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA520" s="57" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB520" s="57" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC520" s="57" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD520" s="57" t="e">
+        <f>(W520-W276)/W276</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE520" s="57" t="e">
+        <f>(X520-X276)/X276</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF520" s="57" t="e">
+        <f>(Y520-Y276)/Y276</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG520" s="57" t="e">
+        <f>(Z520-Z276)/Z276</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH520" s="57"/>
     </row>
     <row r="521" spans="23:34">
       <c r="W521" s="41"/>
@@ -22887,51 +23374,18 @@
       <c r="AH758" s="41"/>
     </row>
     <row r="759" spans="23:34">
-      <c r="W759" s="50" t="e">
-        <f t="shared" ref="W759:AG759" si="3">(F759-F516)/F516</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X759" s="50" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y759" s="50" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z759" s="50" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA759" s="50" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB759" s="50" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC759" s="50" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD759" s="50" t="e">
-        <f>(W759-W516)/W516</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE759" s="50" t="e">
-        <f>(X759-X516)/X516</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF759" s="50" t="e">
-        <f>(Y759-Y516)/Y516</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG759" s="50" t="e">
-        <f>(Z759-Z516)/Z516</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH759" s="50"/>
+      <c r="W759" s="41"/>
+      <c r="X759" s="41"/>
+      <c r="Y759" s="41"/>
+      <c r="Z759" s="41"/>
+      <c r="AA759" s="41"/>
+      <c r="AB759" s="41"/>
+      <c r="AC759" s="41"/>
+      <c r="AD759" s="41"/>
+      <c r="AE759" s="41"/>
+      <c r="AF759" s="41"/>
+      <c r="AG759" s="41"/>
+      <c r="AH759" s="41"/>
     </row>
     <row r="760" spans="23:34">
       <c r="W760" s="41"/>
@@ -22976,18 +23430,51 @@
       <c r="AH762" s="41"/>
     </row>
     <row r="763" spans="23:34">
-      <c r="W763" s="41"/>
-      <c r="X763" s="41"/>
-      <c r="Y763" s="41"/>
-      <c r="Z763" s="41"/>
-      <c r="AA763" s="41"/>
-      <c r="AB763" s="41"/>
-      <c r="AC763" s="41"/>
-      <c r="AD763" s="41"/>
-      <c r="AE763" s="41"/>
-      <c r="AF763" s="41"/>
-      <c r="AG763" s="41"/>
-      <c r="AH763" s="41"/>
+      <c r="W763" s="57" t="e">
+        <f t="shared" ref="W763:AG763" si="3">(F763-F520)/F520</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X763" s="57" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y763" s="57" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z763" s="57" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA763" s="57" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB763" s="57" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC763" s="57" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD763" s="57" t="e">
+        <f>(W763-W520)/W520</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE763" s="57" t="e">
+        <f>(X763-X520)/X520</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF763" s="57" t="e">
+        <f>(Y763-Y520)/Y520</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG763" s="57" t="e">
+        <f>(Z763-Z520)/Z520</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH763" s="57"/>
     </row>
     <row r="764" spans="23:34">
       <c r="W764" s="41"/>
@@ -26336,51 +26823,18 @@
       <c r="AH1002" s="41"/>
     </row>
     <row r="1003" spans="23:34">
-      <c r="W1003" s="50" t="e">
-        <f t="shared" ref="W1003:AG1003" si="4">(F1003-F759)/F759</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X1003" s="50" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y1003" s="50" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z1003" s="50" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA1003" s="50" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB1003" s="50" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC1003" s="50" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD1003" s="50" t="e">
-        <f>(W1003-W759)/W759</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE1003" s="50" t="e">
-        <f>(X1003-X759)/X759</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF1003" s="50" t="e">
-        <f>(Y1003-Y759)/Y759</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG1003" s="50" t="e">
-        <f>(Z1003-Z759)/Z759</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH1003" s="50"/>
+      <c r="W1003" s="41"/>
+      <c r="X1003" s="41"/>
+      <c r="Y1003" s="41"/>
+      <c r="Z1003" s="41"/>
+      <c r="AA1003" s="41"/>
+      <c r="AB1003" s="41"/>
+      <c r="AC1003" s="41"/>
+      <c r="AD1003" s="41"/>
+      <c r="AE1003" s="41"/>
+      <c r="AF1003" s="41"/>
+      <c r="AG1003" s="41"/>
+      <c r="AH1003" s="41"/>
     </row>
     <row r="1004" spans="23:34">
       <c r="W1004" s="41"/>
@@ -26425,18 +26879,51 @@
       <c r="AH1006" s="41"/>
     </row>
     <row r="1007" spans="23:34">
-      <c r="W1007" s="41"/>
-      <c r="X1007" s="41"/>
-      <c r="Y1007" s="41"/>
-      <c r="Z1007" s="41"/>
-      <c r="AA1007" s="41"/>
-      <c r="AB1007" s="41"/>
-      <c r="AC1007" s="41"/>
-      <c r="AD1007" s="41"/>
-      <c r="AE1007" s="41"/>
-      <c r="AF1007" s="41"/>
-      <c r="AG1007" s="41"/>
-      <c r="AH1007" s="41"/>
+      <c r="W1007" s="57" t="e">
+        <f t="shared" ref="W1007:AG1007" si="4">(F1007-F763)/F763</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X1007" s="57" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y1007" s="57" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z1007" s="57" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA1007" s="57" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB1007" s="57" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1007" s="57" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD1007" s="57" t="e">
+        <f>(W1007-W763)/W763</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE1007" s="57" t="e">
+        <f>(X1007-X763)/X763</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF1007" s="57" t="e">
+        <f>(Y1007-Y763)/Y763</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG1007" s="57" t="e">
+        <f>(Z1007-Z763)/Z763</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH1007" s="57"/>
     </row>
     <row r="1008" spans="23:34">
       <c r="W1008" s="41"/>
@@ -29771,51 +30258,18 @@
       <c r="AH1245" s="41"/>
     </row>
     <row r="1246" spans="23:34">
-      <c r="W1246" s="50" t="e">
-        <f t="shared" ref="W1246:AG1246" si="5">(F1246-F1003)/F1003</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X1246" s="50" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y1246" s="50" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z1246" s="50" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA1246" s="50" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB1246" s="50" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC1246" s="50" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD1246" s="50" t="e">
-        <f>(W1246-W1003)/W1003</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE1246" s="50" t="e">
-        <f>(X1246-X1003)/X1003</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF1246" s="50" t="e">
-        <f>(Y1246-Y1003)/Y1003</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG1246" s="50" t="e">
-        <f>(Z1246-Z1003)/Z1003</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH1246" s="50"/>
+      <c r="W1246" s="41"/>
+      <c r="X1246" s="41"/>
+      <c r="Y1246" s="41"/>
+      <c r="Z1246" s="41"/>
+      <c r="AA1246" s="41"/>
+      <c r="AB1246" s="41"/>
+      <c r="AC1246" s="41"/>
+      <c r="AD1246" s="41"/>
+      <c r="AE1246" s="41"/>
+      <c r="AF1246" s="41"/>
+      <c r="AG1246" s="41"/>
+      <c r="AH1246" s="41"/>
     </row>
     <row r="1247" spans="23:34">
       <c r="W1247" s="41"/>
@@ -29860,18 +30314,51 @@
       <c r="AH1249" s="41"/>
     </row>
     <row r="1250" spans="23:34">
-      <c r="W1250" s="41"/>
-      <c r="X1250" s="41"/>
-      <c r="Y1250" s="41"/>
-      <c r="Z1250" s="41"/>
-      <c r="AA1250" s="41"/>
-      <c r="AB1250" s="41"/>
-      <c r="AC1250" s="41"/>
-      <c r="AD1250" s="41"/>
-      <c r="AE1250" s="41"/>
-      <c r="AF1250" s="41"/>
-      <c r="AG1250" s="41"/>
-      <c r="AH1250" s="41"/>
+      <c r="W1250" s="57" t="e">
+        <f t="shared" ref="W1250:AG1250" si="5">(F1250-F1007)/F1007</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X1250" s="57" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y1250" s="57" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z1250" s="57" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA1250" s="57" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB1250" s="57" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1250" s="57" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD1250" s="57" t="e">
+        <f>(W1250-W1007)/W1007</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE1250" s="57" t="e">
+        <f>(X1250-X1007)/X1007</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF1250" s="57" t="e">
+        <f>(Y1250-Y1007)/Y1007</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG1250" s="57" t="e">
+        <f>(Z1250-Z1007)/Z1007</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH1250" s="57"/>
     </row>
     <row r="1251" spans="23:34">
       <c r="W1251" s="41"/>
@@ -33206,51 +33693,18 @@
       <c r="AH1488" s="41"/>
     </row>
     <row r="1489" spans="23:34">
-      <c r="W1489" s="50" t="e">
-        <f t="shared" ref="W1489:AG1489" si="6">(F1489-F1246)/F1246</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X1489" s="50" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y1489" s="50" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z1489" s="50" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA1489" s="50" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB1489" s="50" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC1489" s="50" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD1489" s="50" t="e">
-        <f>(W1489-W1246)/W1246</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE1489" s="50" t="e">
-        <f>(X1489-X1246)/X1246</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF1489" s="50" t="e">
-        <f>(Y1489-Y1246)/Y1246</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG1489" s="50" t="e">
-        <f>(Z1489-Z1246)/Z1246</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH1489" s="50"/>
+      <c r="W1489" s="41"/>
+      <c r="X1489" s="41"/>
+      <c r="Y1489" s="41"/>
+      <c r="Z1489" s="41"/>
+      <c r="AA1489" s="41"/>
+      <c r="AB1489" s="41"/>
+      <c r="AC1489" s="41"/>
+      <c r="AD1489" s="41"/>
+      <c r="AE1489" s="41"/>
+      <c r="AF1489" s="41"/>
+      <c r="AG1489" s="41"/>
+      <c r="AH1489" s="41"/>
     </row>
     <row r="1490" spans="23:34">
       <c r="W1490" s="41"/>
@@ -33295,18 +33749,51 @@
       <c r="AH1492" s="41"/>
     </row>
     <row r="1493" spans="23:34">
-      <c r="W1493" s="41"/>
-      <c r="X1493" s="41"/>
-      <c r="Y1493" s="41"/>
-      <c r="Z1493" s="41"/>
-      <c r="AA1493" s="41"/>
-      <c r="AB1493" s="41"/>
-      <c r="AC1493" s="41"/>
-      <c r="AD1493" s="41"/>
-      <c r="AE1493" s="41"/>
-      <c r="AF1493" s="41"/>
-      <c r="AG1493" s="41"/>
-      <c r="AH1493" s="41"/>
+      <c r="W1493" s="57" t="e">
+        <f t="shared" ref="W1493:AG1493" si="6">(F1493-F1250)/F1250</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X1493" s="57" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y1493" s="57" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z1493" s="57" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA1493" s="57" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB1493" s="57" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1493" s="57" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD1493" s="57" t="e">
+        <f>(W1493-W1250)/W1250</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE1493" s="57" t="e">
+        <f>(X1493-X1250)/X1250</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF1493" s="57" t="e">
+        <f>(Y1493-Y1250)/Y1250</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG1493" s="57" t="e">
+        <f>(Z1493-Z1250)/Z1250</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH1493" s="57"/>
     </row>
     <row r="1494" spans="23:34">
       <c r="W1494" s="41"/>
@@ -36627,51 +37114,18 @@
       <c r="AH1730" s="41"/>
     </row>
     <row r="1731" spans="23:34">
-      <c r="W1731" s="50" t="e">
-        <f t="shared" ref="W1731:AG1731" si="7">(F1731-F1489)/F1489</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X1731" s="50" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y1731" s="50" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z1731" s="50" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA1731" s="50" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB1731" s="50" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC1731" s="50" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD1731" s="50" t="e">
-        <f>(W1731-W1489)/W1489</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE1731" s="50" t="e">
-        <f>(X1731-X1489)/X1489</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF1731" s="50" t="e">
-        <f>(Y1731-Y1489)/Y1489</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG1731" s="50" t="e">
-        <f>(Z1731-Z1489)/Z1489</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH1731" s="50"/>
+      <c r="W1731" s="41"/>
+      <c r="X1731" s="41"/>
+      <c r="Y1731" s="41"/>
+      <c r="Z1731" s="41"/>
+      <c r="AA1731" s="41"/>
+      <c r="AB1731" s="41"/>
+      <c r="AC1731" s="41"/>
+      <c r="AD1731" s="41"/>
+      <c r="AE1731" s="41"/>
+      <c r="AF1731" s="41"/>
+      <c r="AG1731" s="41"/>
+      <c r="AH1731" s="41"/>
     </row>
     <row r="1732" spans="23:34">
       <c r="W1732" s="41"/>
@@ -36716,18 +37170,51 @@
       <c r="AH1734" s="41"/>
     </row>
     <row r="1735" spans="23:34">
-      <c r="W1735" s="41"/>
-      <c r="X1735" s="41"/>
-      <c r="Y1735" s="41"/>
-      <c r="Z1735" s="41"/>
-      <c r="AA1735" s="41"/>
-      <c r="AB1735" s="41"/>
-      <c r="AC1735" s="41"/>
-      <c r="AD1735" s="41"/>
-      <c r="AE1735" s="41"/>
-      <c r="AF1735" s="41"/>
-      <c r="AG1735" s="41"/>
-      <c r="AH1735" s="41"/>
+      <c r="W1735" s="57" t="e">
+        <f t="shared" ref="W1735:AG1735" si="7">(F1735-F1493)/F1493</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X1735" s="57" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y1735" s="57" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z1735" s="57" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA1735" s="57" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB1735" s="57" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1735" s="57" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD1735" s="57" t="e">
+        <f>(W1735-W1493)/W1493</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE1735" s="57" t="e">
+        <f>(X1735-X1493)/X1493</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF1735" s="57" t="e">
+        <f>(Y1735-Y1493)/Y1493</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG1735" s="57" t="e">
+        <f>(Z1735-Z1493)/Z1493</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH1735" s="57"/>
     </row>
     <row r="1736" spans="23:34">
       <c r="W1736" s="41"/>
@@ -40048,51 +40535,18 @@
       <c r="AH1972" s="41"/>
     </row>
     <row r="1973" spans="23:34">
-      <c r="W1973" s="50" t="e">
-        <f t="shared" ref="W1973:AG1973" si="8">(F1973-F1731)/F1731</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X1973" s="50" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y1973" s="50" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z1973" s="50" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA1973" s="50" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB1973" s="50" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC1973" s="50" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD1973" s="50" t="e">
-        <f>(W1973-W1731)/W1731</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE1973" s="50" t="e">
-        <f>(X1973-X1731)/X1731</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF1973" s="50" t="e">
-        <f>(Y1973-Y1731)/Y1731</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG1973" s="50" t="e">
-        <f>(Z1973-Z1731)/Z1731</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH1973" s="50"/>
+      <c r="W1973" s="41"/>
+      <c r="X1973" s="41"/>
+      <c r="Y1973" s="41"/>
+      <c r="Z1973" s="41"/>
+      <c r="AA1973" s="41"/>
+      <c r="AB1973" s="41"/>
+      <c r="AC1973" s="41"/>
+      <c r="AD1973" s="41"/>
+      <c r="AE1973" s="41"/>
+      <c r="AF1973" s="41"/>
+      <c r="AG1973" s="41"/>
+      <c r="AH1973" s="41"/>
     </row>
     <row r="1974" spans="23:34">
       <c r="W1974" s="41"/>
@@ -40137,18 +40591,51 @@
       <c r="AH1976" s="41"/>
     </row>
     <row r="1977" spans="23:34">
-      <c r="W1977" s="41"/>
-      <c r="X1977" s="41"/>
-      <c r="Y1977" s="41"/>
-      <c r="Z1977" s="41"/>
-      <c r="AA1977" s="41"/>
-      <c r="AB1977" s="41"/>
-      <c r="AC1977" s="41"/>
-      <c r="AD1977" s="41"/>
-      <c r="AE1977" s="41"/>
-      <c r="AF1977" s="41"/>
-      <c r="AG1977" s="41"/>
-      <c r="AH1977" s="41"/>
+      <c r="W1977" s="57" t="e">
+        <f t="shared" ref="W1977:AG1977" si="8">(F1977-F1735)/F1735</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X1977" s="57" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y1977" s="57" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z1977" s="57" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA1977" s="57" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB1977" s="57" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1977" s="57" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD1977" s="57" t="e">
+        <f>(W1977-W1735)/W1735</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE1977" s="57" t="e">
+        <f>(X1977-X1735)/X1735</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF1977" s="57" t="e">
+        <f>(Y1977-Y1735)/Y1735</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG1977" s="57" t="e">
+        <f>(Z1977-Z1735)/Z1735</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH1977" s="57"/>
     </row>
     <row r="1978" spans="23:34">
       <c r="W1978" s="41"/>
@@ -43441,51 +43928,18 @@
       <c r="AH2212" s="41"/>
     </row>
     <row r="2213" spans="23:34">
-      <c r="W2213" s="50" t="e">
-        <f t="shared" ref="W2213:AG2213" si="9">(F2213-F1973)/F1973</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X2213" s="50" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y2213" s="50" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z2213" s="50" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA2213" s="50" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB2213" s="50" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC2213" s="50" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD2213" s="50" t="e">
-        <f>(W2213-W1973)/W1973</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE2213" s="50" t="e">
-        <f>(X2213-X1973)/X1973</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF2213" s="50" t="e">
-        <f>(Y2213-Y1973)/Y1973</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG2213" s="50" t="e">
-        <f>(Z2213-Z1973)/Z1973</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH2213" s="50"/>
+      <c r="W2213" s="41"/>
+      <c r="X2213" s="41"/>
+      <c r="Y2213" s="41"/>
+      <c r="Z2213" s="41"/>
+      <c r="AA2213" s="41"/>
+      <c r="AB2213" s="41"/>
+      <c r="AC2213" s="41"/>
+      <c r="AD2213" s="41"/>
+      <c r="AE2213" s="41"/>
+      <c r="AF2213" s="41"/>
+      <c r="AG2213" s="41"/>
+      <c r="AH2213" s="41"/>
     </row>
     <row r="2214" spans="23:34">
       <c r="W2214" s="41"/>
@@ -43530,18 +43984,51 @@
       <c r="AH2216" s="41"/>
     </row>
     <row r="2217" spans="23:34">
-      <c r="W2217" s="41"/>
-      <c r="X2217" s="41"/>
-      <c r="Y2217" s="41"/>
-      <c r="Z2217" s="41"/>
-      <c r="AA2217" s="41"/>
-      <c r="AB2217" s="41"/>
-      <c r="AC2217" s="41"/>
-      <c r="AD2217" s="41"/>
-      <c r="AE2217" s="41"/>
-      <c r="AF2217" s="41"/>
-      <c r="AG2217" s="41"/>
-      <c r="AH2217" s="41"/>
+      <c r="W2217" s="57" t="e">
+        <f t="shared" ref="W2217:AG2217" si="9">(F2217-F1977)/F1977</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X2217" s="57" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y2217" s="57" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z2217" s="57" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA2217" s="57" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB2217" s="57" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC2217" s="57" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD2217" s="57" t="e">
+        <f>(W2217-W1977)/W1977</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE2217" s="57" t="e">
+        <f>(X2217-X1977)/X1977</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF2217" s="57" t="e">
+        <f>(Y2217-Y1977)/Y1977</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG2217" s="57" t="e">
+        <f>(Z2217-Z1977)/Z1977</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH2217" s="57"/>
     </row>
     <row r="2218" spans="23:34">
       <c r="W2218" s="41"/>
@@ -46848,51 +47335,107 @@
       <c r="AH2453" s="41"/>
     </row>
     <row r="2454" spans="23:34">
-      <c r="W2454" s="50" t="e">
-        <f t="shared" ref="W2454:AG2454" si="10">(F2454-F2213)/F2213</f>
+      <c r="W2454" s="41"/>
+      <c r="X2454" s="41"/>
+      <c r="Y2454" s="41"/>
+      <c r="Z2454" s="41"/>
+      <c r="AA2454" s="41"/>
+      <c r="AB2454" s="41"/>
+      <c r="AC2454" s="41"/>
+      <c r="AD2454" s="41"/>
+      <c r="AE2454" s="41"/>
+      <c r="AF2454" s="41"/>
+      <c r="AG2454" s="41"/>
+      <c r="AH2454" s="41"/>
+    </row>
+    <row r="2455" spans="23:34">
+      <c r="W2455" s="41"/>
+      <c r="X2455" s="41"/>
+      <c r="Y2455" s="41"/>
+      <c r="Z2455" s="41"/>
+      <c r="AA2455" s="41"/>
+      <c r="AB2455" s="41"/>
+      <c r="AC2455" s="41"/>
+      <c r="AD2455" s="41"/>
+      <c r="AE2455" s="41"/>
+      <c r="AF2455" s="41"/>
+      <c r="AG2455" s="41"/>
+      <c r="AH2455" s="41"/>
+    </row>
+    <row r="2456" spans="23:34">
+      <c r="W2456" s="41"/>
+      <c r="X2456" s="41"/>
+      <c r="Y2456" s="41"/>
+      <c r="Z2456" s="41"/>
+      <c r="AA2456" s="41"/>
+      <c r="AB2456" s="41"/>
+      <c r="AC2456" s="41"/>
+      <c r="AD2456" s="41"/>
+      <c r="AE2456" s="41"/>
+      <c r="AF2456" s="41"/>
+      <c r="AG2456" s="41"/>
+      <c r="AH2456" s="41"/>
+    </row>
+    <row r="2457" spans="23:34">
+      <c r="W2457" s="41"/>
+      <c r="X2457" s="41"/>
+      <c r="Y2457" s="41"/>
+      <c r="Z2457" s="41"/>
+      <c r="AA2457" s="41"/>
+      <c r="AB2457" s="41"/>
+      <c r="AC2457" s="41"/>
+      <c r="AD2457" s="41"/>
+      <c r="AE2457" s="41"/>
+      <c r="AF2457" s="41"/>
+      <c r="AG2457" s="41"/>
+      <c r="AH2457" s="41"/>
+    </row>
+    <row r="2458" spans="23:34">
+      <c r="W2458" s="57" t="e">
+        <f t="shared" ref="W2458:AG2458" si="10">(F2458-F2217)/F2217</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X2454" s="50" t="e">
+      <c r="X2458" s="57" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y2454" s="50" t="e">
+      <c r="Y2458" s="57" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z2454" s="50" t="e">
+      <c r="Z2458" s="57" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA2454" s="50" t="e">
+      <c r="AA2458" s="57" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB2454" s="50" t="e">
+      <c r="AB2458" s="57" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC2454" s="50" t="e">
+      <c r="AC2458" s="57" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD2454" s="50" t="e">
-        <f>(W2454-W2213)/W2213</f>
+      <c r="AD2458" s="57" t="e">
+        <f>(W2458-W2217)/W2217</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE2454" s="50" t="e">
-        <f>(X2454-X2213)/X2213</f>
+      <c r="AE2458" s="57" t="e">
+        <f>(X2458-X2217)/X2217</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF2454" s="50" t="e">
-        <f>(Y2454-Y2213)/Y2213</f>
+      <c r="AF2458" s="57" t="e">
+        <f>(Y2458-Y2217)/Y2217</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG2454" s="50" t="e">
-        <f>(Z2454-Z2213)/Z2213</f>
+      <c r="AG2458" s="57" t="e">
+        <f>(Z2458-Z2217)/Z2217</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH2454" s="50"/>
+      <c r="AH2458" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/主要指数介绍.xlsx
+++ b/主要指数介绍.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="330">
   <si>
     <t>指数简称</t>
   </si>
@@ -65,16 +65,16 @@
     <t>发布日期</t>
   </si>
   <si>
-    <t>指定年份年收益(%)</t>
+    <t>指定年份年收益</t>
   </si>
   <si>
-    <t>基日以来全部年份年平均收益(%)</t>
+    <t>基日以来全部年份年平均收益</t>
   </si>
   <si>
-    <t>指定年份年波动率(%)</t>
+    <t>指定年份年波动率</t>
   </si>
   <si>
-    <t>基日以来近几年年化收益(%)</t>
+    <t>基日以来近几年年化收益</t>
   </si>
   <si>
     <t>近1年</t>
@@ -933,10 +933,82 @@
     <t>单个样本权重不超过 15%，前五大样本合计权重不超过 60%</t>
   </si>
   <si>
+    <t xml:space="preserve">中证新能   </t>
+  </si>
+  <si>
+    <t>中证新能源指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年日均成交金额排名后 20% 的证券；（2）再选取涉及可再生能源生产、新能源应用、新能源存储以及新能源交互设备等业务的上市公司证券进入新能源主题；（3）再选取过去一年日均总市值排名在前 80 只。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">光伏产业   </t>
+  </si>
+  <si>
+    <t>中证光伏产业指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年日均成交金额排名后 20% 的证券；（2）再选取主营业务涉及光伏产业链上、中、下游的上市公司证券作为待选样本，业务范围包括但不限于硅片、多晶硅、电池片、电缆、光伏玻璃、电池组件、逆变器、光伏支架和光伏电站等；（3）再选取过去一年日均总市值排名靠前的 50 只样本，不足 50 只时全部纳入。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机器人   </t>
+  </si>
+  <si>
+    <t>H30590</t>
+  </si>
+  <si>
+    <t>中证机器人指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年日均成交金额排名后 20% 的证券；（2）再选取为机器人生产提供软件和硬件的上市公司作为待选样本，包括但不限于：系统方案商、数字化车间与生产线系统集成商、自动化设备制造商、底层自动化零部件商以及其他与机器人相关的公司；（3）再选取过去一年日均总市值排名前 100 只样本，不足 100 只时全部纳入。</t>
+  </si>
+  <si>
+    <t>中证汽车</t>
+  </si>
+  <si>
+    <t>中证汽车指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年日均成交金额排名后 20% 的证券；（2）再选取归属于汽车行业的上市公司证券纳入汽车主题；（3）再选取过去一年的日均总市值排名前 100 只。</t>
+  </si>
+  <si>
     <t>中证环保</t>
   </si>
   <si>
     <t>000827</t>
+  </si>
+  <si>
+    <t>中证环保产业指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年日均成交金额排名后 20% 的证券；（2）再选取业务涉及环保产业的上市公司证券作为待选样本，包括但不限于以下领域；① 资源管理：为供水、可回收利用材料生产、清洁能源发电、能源节约与管理等活动提供生产设备、技术、特殊材料、服务、建筑与安装；② 清洁技术和产品：为能源清洁、资源提效等活动提供生产设备、技术、特殊材料、建筑与安装；③ 污染管理：为空气污染防治、废水管理、固体废弃物管理、噪声消除、环境监测、数据收集等活动提供生产设备、特殊材料、建筑与安装。（3）再选取过去一年日均总市值排名前 100 只。</t>
+  </si>
+  <si>
+    <t>中证人工智能</t>
+  </si>
+  <si>
+    <t>中证数据</t>
+  </si>
+  <si>
+    <t>中证数字经济</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中证软件   </t>
+  </si>
+  <si>
+    <t>半导体</t>
+  </si>
+  <si>
+    <t>H30184</t>
+  </si>
+  <si>
+    <t>中证全指半导体产品与设备指数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中证白酒   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">家用电器   </t>
   </si>
   <si>
     <t xml:space="preserve">中证农业   </t>
@@ -945,73 +1017,10 @@
     <t>000949</t>
   </si>
   <si>
-    <t xml:space="preserve">机器人   </t>
-  </si>
-  <si>
-    <t>H30590</t>
+    <t xml:space="preserve">中证旅游   </t>
   </si>
   <si>
     <t xml:space="preserve">养老产业   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">中证新能   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">中证军工   </t>
-  </si>
-  <si>
-    <t>中证传媒</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中证国防   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">中证银行   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">证券公司   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">中证白酒   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">家用电器   </t>
-  </si>
-  <si>
-    <t>中证汽车</t>
-  </si>
-  <si>
-    <t xml:space="preserve">中证软件   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">中证旅游   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">港股科技  </t>
-  </si>
-  <si>
-    <t>港股通高股息</t>
-  </si>
-  <si>
-    <t>香港新股</t>
-  </si>
-  <si>
-    <t>中证数据</t>
-  </si>
-  <si>
-    <t>中证人工智能</t>
-  </si>
-  <si>
-    <t>云计算</t>
-  </si>
-  <si>
-    <t>中证云计算与大数据主题指数</t>
-  </si>
-  <si>
-    <t>中证数字经济</t>
-  </si>
-  <si>
-    <t xml:space="preserve">光伏产业   </t>
   </si>
   <si>
     <t xml:space="preserve">中证中药   </t>
@@ -1032,13 +1041,28 @@
     <t>000813</t>
   </si>
   <si>
-    <t>半导体</t>
+    <t>中证传媒</t>
   </si>
   <si>
-    <t>H30184</t>
+    <t xml:space="preserve">中证银行   </t>
   </si>
   <si>
-    <t>中证全指半导体产品与设备指数</t>
+    <t xml:space="preserve">证券公司   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">中证军工   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">中证国防   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">港股科技  </t>
+  </si>
+  <si>
+    <t>港股通高股息</t>
+  </si>
+  <si>
+    <t>香港新股</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1077,7 @@
     <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
     <numFmt numFmtId="177" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1105,13 +1129,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -1585,13 +1602,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1600,122 +1620,119 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1851,22 +1868,16 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1875,14 +1886,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
@@ -2430,7 +2441,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BQ2458"/>
+  <dimension ref="A1:BQ2464"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.141592920354" style="4" customWidth="1"/>
@@ -2690,7 +2701,7 @@
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="56" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -2894,7 +2905,7 @@
       <c r="A4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="56" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -3098,7 +3109,7 @@
       <c r="A5" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="56" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -3663,7 +3674,7 @@
       <c r="A9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="56" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -3861,7 +3872,7 @@
       <c r="A10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="56" t="s">
         <v>62</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -4124,7 +4135,7 @@
       <c r="A12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="56" t="s">
         <v>68</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -4246,7 +4257,7 @@
       <c r="A13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="56" t="s">
         <v>74</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -4374,7 +4385,7 @@
       <c r="A14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="56" t="s">
         <v>79</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -4487,7 +4498,7 @@
       <c r="A15" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="56" t="s">
         <v>84</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -4505,7 +4516,7 @@
       <c r="H15" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I15" s="58" t="s">
+      <c r="I15" s="56" t="s">
         <v>51</v>
       </c>
       <c r="J15" s="4">
@@ -6232,7 +6243,7 @@
       <c r="A30" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="58" t="s">
+      <c r="B30" s="56" t="s">
         <v>132</v>
       </c>
       <c r="C30" s="4" t="s">
@@ -6585,7 +6596,7 @@
       <c r="BP31" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="BQ31" s="59" t="s">
+      <c r="BQ31" s="57" t="s">
         <v>51</v>
       </c>
     </row>
@@ -6593,7 +6604,7 @@
       <c r="A32" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="58" t="s">
+      <c r="B32" s="56" t="s">
         <v>145</v>
       </c>
       <c r="C32" s="4" t="s">
@@ -6797,7 +6808,7 @@
       <c r="A33" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="58" t="s">
+      <c r="B33" s="56" t="s">
         <v>150</v>
       </c>
       <c r="C33" s="4" t="s">
@@ -7149,19 +7160,19 @@
       <c r="BL34" s="15">
         <v>0.0603036102934573</v>
       </c>
-      <c r="BM34" s="59" t="s">
+      <c r="BM34" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="BN34" s="59" t="s">
+      <c r="BN34" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="BO34" s="59" t="s">
+      <c r="BO34" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="BP34" s="59" t="s">
+      <c r="BP34" s="57" t="s">
         <v>51</v>
       </c>
-      <c r="BQ34" s="59" t="s">
+      <c r="BQ34" s="57" t="s">
         <v>51</v>
       </c>
     </row>
@@ -7318,7 +7329,7 @@
       <c r="BP35" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="BQ35" s="59" t="s">
+      <c r="BQ35" s="57" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8073,7 +8084,7 @@
       <c r="BP40" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="BQ40" s="59" t="s">
+      <c r="BQ40" s="57" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8227,7 +8238,7 @@
       <c r="BO41" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="BP41" s="59" t="s">
+      <c r="BP41" s="57" t="s">
         <v>51</v>
       </c>
       <c r="BQ41" s="17" t="s">
@@ -8384,7 +8395,7 @@
       <c r="BO42" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="BP42" s="59" t="s">
+      <c r="BP42" s="57" t="s">
         <v>51</v>
       </c>
       <c r="BQ42" s="17" t="s">
@@ -8520,19 +8531,19 @@
       <c r="BL43" s="14">
         <v>0.0406</v>
       </c>
-      <c r="BM43" s="60" t="s">
+      <c r="BM43" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BN43" s="60" t="s">
+      <c r="BN43" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BO43" s="60" t="s">
+      <c r="BO43" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BP43" s="60" t="s">
+      <c r="BP43" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BQ43" s="60" t="s">
+      <c r="BQ43" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8712,19 +8723,19 @@
       <c r="BL45" s="15">
         <v>0.113823071174797</v>
       </c>
-      <c r="BM45" s="60" t="s">
+      <c r="BM45" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BN45" s="60" t="s">
+      <c r="BN45" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BO45" s="60" t="s">
+      <c r="BO45" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BP45" s="60" t="s">
+      <c r="BP45" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BQ45" s="60" t="s">
+      <c r="BQ45" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8861,19 +8872,19 @@
       <c r="BL46" s="15">
         <v>0.0852474573735877</v>
       </c>
-      <c r="BM46" s="60" t="s">
+      <c r="BM46" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BN46" s="60" t="s">
+      <c r="BN46" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BO46" s="60" t="s">
+      <c r="BO46" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BP46" s="60" t="s">
+      <c r="BP46" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BQ46" s="60" t="s">
+      <c r="BQ46" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9010,19 +9021,19 @@
       <c r="BL47" s="15">
         <v>0.09350422314173</v>
       </c>
-      <c r="BM47" s="60" t="s">
+      <c r="BM47" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BN47" s="60" t="s">
+      <c r="BN47" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BO47" s="60" t="s">
+      <c r="BO47" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BP47" s="60" t="s">
+      <c r="BP47" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BQ47" s="60" t="s">
+      <c r="BQ47" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9159,19 +9170,19 @@
       <c r="BL48" s="15">
         <v>0.0923653113940854</v>
       </c>
-      <c r="BM48" s="60" t="s">
+      <c r="BM48" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BN48" s="60" t="s">
+      <c r="BN48" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BO48" s="60" t="s">
+      <c r="BO48" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BP48" s="60" t="s">
+      <c r="BP48" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BQ48" s="60" t="s">
+      <c r="BQ48" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9308,19 +9319,19 @@
       <c r="BL49" s="15">
         <v>0.078742377357387</v>
       </c>
-      <c r="BM49" s="60" t="s">
+      <c r="BM49" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BN49" s="60" t="s">
+      <c r="BN49" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BO49" s="60" t="s">
+      <c r="BO49" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BP49" s="60" t="s">
+      <c r="BP49" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BQ49" s="60" t="s">
+      <c r="BQ49" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9371,7 +9382,7 @@
       <c r="A51" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B51" s="58" t="s">
+      <c r="B51" s="56" t="s">
         <v>206</v>
       </c>
       <c r="C51" s="31" t="s">
@@ -9539,10 +9550,10 @@
       <c r="BO51" s="14">
         <v>0.0756</v>
       </c>
-      <c r="BP51" s="60" t="s">
+      <c r="BP51" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BQ51" s="60" t="s">
+      <c r="BQ51" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9550,7 +9561,7 @@
       <c r="A52" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B52" s="58" t="s">
+      <c r="B52" s="56" t="s">
         <v>211</v>
       </c>
       <c r="C52" s="31" t="s">
@@ -9739,7 +9750,7 @@
       <c r="BP52" s="14">
         <v>0.0756</v>
       </c>
-      <c r="BQ52" s="60" t="s">
+      <c r="BQ52" s="58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9872,16 +9883,16 @@
       <c r="BL53" s="14">
         <v>0.0104</v>
       </c>
-      <c r="BM53" s="60" t="s">
+      <c r="BM53" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BN53" s="60" t="s">
+      <c r="BN53" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BO53" s="60" t="s">
+      <c r="BO53" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="BP53" s="60" t="s">
+      <c r="BP53" s="58" t="s">
         <v>51</v>
       </c>
       <c r="BQ53" s="17"/>
@@ -10128,7 +10139,7 @@
       <c r="A56" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="B56" s="61" t="s">
+      <c r="B56" s="59" t="s">
         <v>225</v>
       </c>
       <c r="C56" s="39" t="s">
@@ -10332,7 +10343,7 @@
       <c r="A57" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="B57" s="61" t="s">
+      <c r="B57" s="59" t="s">
         <v>230</v>
       </c>
       <c r="C57" s="39" t="s">
@@ -10536,7 +10547,7 @@
       <c r="A58" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="B58" s="61" t="s">
+      <c r="B58" s="59" t="s">
         <v>233</v>
       </c>
       <c r="C58" s="39" t="s">
@@ -10740,7 +10751,7 @@
       <c r="A59" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="B59" s="61" t="s">
+      <c r="B59" s="59" t="s">
         <v>236</v>
       </c>
       <c r="C59" s="39" t="s">
@@ -10944,7 +10955,7 @@
       <c r="A60" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="B60" s="61" t="s">
+      <c r="B60" s="59" t="s">
         <v>239</v>
       </c>
       <c r="C60" s="39" t="s">
@@ -11148,7 +11159,7 @@
       <c r="A61" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="B61" s="61" t="s">
+      <c r="B61" s="59" t="s">
         <v>242</v>
       </c>
       <c r="C61" s="39" t="s">
@@ -11352,7 +11363,7 @@
       <c r="A62" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="B62" s="61" t="s">
+      <c r="B62" s="59" t="s">
         <v>245</v>
       </c>
       <c r="C62" s="39" t="s">
@@ -11680,7 +11691,7 @@
       <c r="AR63" s="14">
         <v>0.2647</v>
       </c>
-      <c r="AS63" s="58" t="s">
+      <c r="AS63" s="56" t="s">
         <v>51</v>
       </c>
       <c r="AT63" s="14">
@@ -11758,7 +11769,7 @@
       <c r="A64" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="B64" s="61" t="s">
+      <c r="B64" s="59" t="s">
         <v>250</v>
       </c>
       <c r="C64" s="39" t="s">
@@ -11962,7 +11973,7 @@
       <c r="A65" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="B65" s="61" t="s">
+      <c r="B65" s="59" t="s">
         <v>253</v>
       </c>
       <c r="C65" s="39" t="s">
@@ -12166,7 +12177,7 @@
       <c r="A66" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="B66" s="61" t="s">
+      <c r="B66" s="59" t="s">
         <v>256</v>
       </c>
       <c r="C66" s="39" t="s">
@@ -12413,7 +12424,7 @@
       <c r="A68" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="B68" s="58" t="s">
+      <c r="B68" s="56" t="s">
         <v>259</v>
       </c>
       <c r="C68" s="31" t="s">
@@ -12630,7 +12641,7 @@
       <c r="A70" s="42" t="s">
         <v>263</v>
       </c>
-      <c r="B70" s="62" t="s">
+      <c r="B70" s="60" t="s">
         <v>264</v>
       </c>
       <c r="C70" s="43" t="s">
@@ -12832,7 +12843,7 @@
       <c r="A71" s="42" t="s">
         <v>268</v>
       </c>
-      <c r="B71" s="62" t="s">
+      <c r="B71" s="60" t="s">
         <v>269</v>
       </c>
       <c r="C71" s="43" t="s">
@@ -13061,61 +13072,61 @@
       <c r="J72" s="4">
         <v>1000</v>
       </c>
-      <c r="K72" s="45">
+      <c r="K72" s="40">
         <v>39813</v>
       </c>
       <c r="L72" s="6">
         <v>42048</v>
       </c>
-      <c r="Q72" s="46">
+      <c r="Q72" s="44">
         <v>2.0243</v>
       </c>
-      <c r="R72" s="46">
+      <c r="R72" s="44">
         <v>-0.012</v>
       </c>
-      <c r="S72" s="46">
+      <c r="S72" s="44">
         <v>-0.2969</v>
       </c>
-      <c r="T72" s="46">
+      <c r="T72" s="44">
         <v>-0.0729</v>
       </c>
-      <c r="U72" s="46">
+      <c r="U72" s="44">
         <v>-0.4135</v>
       </c>
-      <c r="V72" s="46">
+      <c r="V72" s="44">
         <v>0.2818</v>
       </c>
-      <c r="W72" s="46">
+      <c r="W72" s="44">
         <v>0.0492</v>
       </c>
-      <c r="X72" s="46">
+      <c r="X72" s="44">
         <v>0.0269</v>
       </c>
-      <c r="Y72" s="46">
+      <c r="Y72" s="44">
         <v>0.12</v>
       </c>
-      <c r="Z72" s="46">
+      <c r="Z72" s="44">
         <v>-0.3486</v>
       </c>
-      <c r="AA72" s="46">
+      <c r="AA72" s="44">
         <v>0.1086</v>
       </c>
-      <c r="AB72" s="46">
+      <c r="AB72" s="44">
         <v>0.0742</v>
       </c>
-      <c r="AC72" s="46">
+      <c r="AC72" s="44">
         <v>0.4281</v>
       </c>
-      <c r="AD72" s="46">
+      <c r="AD72" s="44">
         <v>0.102</v>
       </c>
-      <c r="AE72" s="46">
+      <c r="AE72" s="44">
         <v>0.0326</v>
       </c>
-      <c r="AF72" s="46">
+      <c r="AF72" s="44">
         <v>-0.0296</v>
       </c>
-      <c r="AG72" s="46">
+      <c r="AG72" s="44">
         <v>-0.0877</v>
       </c>
       <c r="AH72" s="41"/>
@@ -13123,88 +13134,88 @@
         <f>SUM(Q72:AG72)/17</f>
         <v>0.116852941176471</v>
       </c>
-      <c r="AO72" s="46">
+      <c r="AO72" s="44">
         <v>0.5125</v>
       </c>
-      <c r="AP72" s="46">
+      <c r="AP72" s="44">
         <v>0.4012</v>
       </c>
-      <c r="AQ72" s="46">
+      <c r="AQ72" s="44">
         <v>0.3151</v>
       </c>
-      <c r="AR72" s="46">
+      <c r="AR72" s="44">
         <v>0.312</v>
       </c>
-      <c r="AS72" s="46">
+      <c r="AS72" s="44">
         <v>0.2909</v>
       </c>
-      <c r="AT72" s="46">
+      <c r="AT72" s="44">
         <v>0.2698</v>
       </c>
-      <c r="AU72" s="46">
+      <c r="AU72" s="44">
         <v>0.4882</v>
       </c>
-      <c r="AV72" s="46">
+      <c r="AV72" s="44">
         <v>0.347</v>
       </c>
-      <c r="AW72" s="46">
+      <c r="AW72" s="44">
         <v>0.2453</v>
       </c>
-      <c r="AX72" s="46">
+      <c r="AX72" s="44">
         <v>0.2717</v>
       </c>
-      <c r="AY72" s="46">
+      <c r="AY72" s="44">
         <v>0.2417</v>
       </c>
-      <c r="AZ72" s="46">
+      <c r="AZ72" s="44">
         <v>0.299</v>
       </c>
-      <c r="BA72" s="46">
+      <c r="BA72" s="44">
         <v>0.422</v>
       </c>
-      <c r="BB72" s="46">
+      <c r="BB72" s="44">
         <v>0.3698</v>
       </c>
-      <c r="BC72" s="46">
+      <c r="BC72" s="44">
         <v>0.1906</v>
       </c>
-      <c r="BD72" s="46">
+      <c r="BD72" s="44">
         <v>0.2702</v>
       </c>
-      <c r="BE72" s="46">
+      <c r="BE72" s="44">
         <v>0.2152</v>
       </c>
-      <c r="BG72" s="47">
+      <c r="BG72" s="45">
         <v>-0.0876612559921522</v>
       </c>
-      <c r="BH72" s="47">
+      <c r="BH72" s="45">
         <v>-0.0294923264089031</v>
       </c>
-      <c r="BI72" s="47">
+      <c r="BI72" s="45">
         <v>0.075428131221329</v>
       </c>
-      <c r="BJ72" s="47">
+      <c r="BJ72" s="45">
         <v>0.0799281177142273</v>
       </c>
-      <c r="BK72" s="47">
+      <c r="BK72" s="45">
         <v>0.0250782339861382</v>
       </c>
-      <c r="BL72" s="47">
+      <c r="BL72" s="45">
         <v>0.0274148186713365</v>
       </c>
-      <c r="BM72" s="47">
+      <c r="BM72" s="45">
         <v>0.000945672848502443</v>
       </c>
-      <c r="BN72" s="47">
+      <c r="BN72" s="45">
         <v>-0.027332824660263</v>
       </c>
-      <c r="BO72" s="47">
+      <c r="BO72" s="45">
         <v>0.040743502432081</v>
       </c>
-      <c r="BP72" s="48" t="s">
+      <c r="BP72" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="BQ72" s="48" t="s">
+      <c r="BQ72" s="46" t="s">
         <v>51</v>
       </c>
     </row>
@@ -13239,61 +13250,61 @@
       <c r="J73" s="4">
         <v>1000</v>
       </c>
-      <c r="K73" s="45">
+      <c r="K73" s="40">
         <v>39813</v>
       </c>
       <c r="L73" s="6">
         <v>42094</v>
       </c>
-      <c r="Q73" s="46">
+      <c r="Q73" s="44">
         <v>0.9878</v>
       </c>
-      <c r="R73" s="46">
+      <c r="R73" s="44">
         <v>-0.3105</v>
       </c>
-      <c r="S73" s="46">
+      <c r="S73" s="44">
         <v>-0.2642</v>
       </c>
-      <c r="T73" s="46">
+      <c r="T73" s="44">
         <v>-0.0536</v>
       </c>
-      <c r="U73" s="46">
+      <c r="U73" s="44">
         <v>-0.2087</v>
       </c>
-      <c r="V73" s="46">
+      <c r="V73" s="44">
         <v>0.7128</v>
       </c>
-      <c r="W73" s="46">
+      <c r="W73" s="44">
         <v>0.0943</v>
       </c>
-      <c r="X73" s="46">
+      <c r="X73" s="44">
         <v>-0.0828</v>
       </c>
-      <c r="Y73" s="46">
+      <c r="Y73" s="44">
         <v>0.0972</v>
       </c>
-      <c r="Z73" s="46">
+      <c r="Z73" s="44">
         <v>-0.3265</v>
       </c>
-      <c r="AA73" s="46">
+      <c r="AA73" s="44">
         <v>-0.0157</v>
       </c>
-      <c r="AB73" s="46">
+      <c r="AB73" s="44">
         <v>0.0178</v>
       </c>
-      <c r="AC73" s="46">
+      <c r="AC73" s="44">
         <v>0.3411</v>
       </c>
-      <c r="AD73" s="46">
+      <c r="AD73" s="44">
         <v>-0.2449</v>
       </c>
-      <c r="AE73" s="46">
+      <c r="AE73" s="44">
         <v>-0.0689</v>
       </c>
-      <c r="AF73" s="46">
+      <c r="AF73" s="44">
         <v>0.008</v>
       </c>
-      <c r="AG73" s="46">
+      <c r="AG73" s="44">
         <v>0.2751</v>
       </c>
       <c r="AH73" s="41"/>
@@ -13301,93 +13312,93 @@
         <f>SUM(Q73:AG73)/17</f>
         <v>0.0563705882352941</v>
       </c>
-      <c r="AO73" s="46">
+      <c r="AO73" s="44">
         <v>0.4175</v>
       </c>
-      <c r="AP73" s="46">
+      <c r="AP73" s="44">
         <v>0.2817</v>
       </c>
-      <c r="AQ73" s="46">
+      <c r="AQ73" s="44">
         <v>0.2413</v>
       </c>
-      <c r="AR73" s="46">
+      <c r="AR73" s="44">
         <v>0.22</v>
       </c>
-      <c r="AS73" s="46">
+      <c r="AS73" s="44">
         <v>0.197</v>
       </c>
-      <c r="AT73" s="46">
+      <c r="AT73" s="44">
         <v>0.2366</v>
       </c>
-      <c r="AU73" s="46">
+      <c r="AU73" s="44">
         <v>0.433</v>
       </c>
-      <c r="AV73" s="46">
+      <c r="AV73" s="44">
         <v>0.3204</v>
       </c>
-      <c r="AW73" s="46">
+      <c r="AW73" s="44">
         <v>0.2199</v>
       </c>
-      <c r="AX73" s="46">
+      <c r="AX73" s="44">
         <v>0.239</v>
       </c>
-      <c r="AY73" s="46">
+      <c r="AY73" s="44">
         <v>0.2289</v>
       </c>
-      <c r="AZ73" s="46">
+      <c r="AZ73" s="44">
         <v>0.2497</v>
       </c>
-      <c r="BA73" s="46">
+      <c r="BA73" s="44">
         <v>0.3533</v>
       </c>
-      <c r="BB73" s="46">
+      <c r="BB73" s="44">
         <v>0.2477</v>
       </c>
-      <c r="BC73" s="46">
+      <c r="BC73" s="44">
         <v>0.1547</v>
       </c>
-      <c r="BD73" s="46">
+      <c r="BD73" s="44">
         <v>0.2545</v>
       </c>
-      <c r="BE73" s="46">
+      <c r="BE73" s="44">
         <v>0.2109</v>
       </c>
-      <c r="BG73" s="49">
+      <c r="BG73" s="47">
         <v>0.27512341422301</v>
       </c>
-      <c r="BH73" s="49">
+      <c r="BH73" s="47">
         <v>0.0616982403006807</v>
       </c>
-      <c r="BI73" s="49">
+      <c r="BI73" s="47">
         <v>0.0391906921963963</v>
       </c>
-      <c r="BJ73" s="49">
+      <c r="BJ73" s="47">
         <v>0.0281098648669311</v>
       </c>
-      <c r="BK73" s="49">
+      <c r="BK73" s="47">
         <v>-0.0119723692464356</v>
       </c>
-      <c r="BL73" s="49">
+      <c r="BL73" s="47">
         <v>-0.00947559580708957</v>
       </c>
-      <c r="BM73" s="49">
+      <c r="BM73" s="47">
         <v>0.0154513499284832</v>
       </c>
-      <c r="BN73" s="49">
+      <c r="BN73" s="47">
         <v>-0.0107810374242893</v>
       </c>
-      <c r="BO73" s="49">
+      <c r="BO73" s="47">
         <v>0.00902100998653288</v>
       </c>
-      <c r="BP73" s="50" t="s">
+      <c r="BP73" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="BQ73" s="50" t="s">
+      <c r="BQ73" s="48" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="74" ht="40.5" spans="1:69">
-      <c r="A74" s="51" t="s">
+      <c r="A74" s="49" t="s">
         <v>281</v>
       </c>
       <c r="B74" s="42">
@@ -13399,7 +13410,7 @@
       <c r="D74" s="4">
         <v>50</v>
       </c>
-      <c r="E74" s="52" t="s">
+      <c r="E74" s="50" t="s">
         <v>283</v>
       </c>
       <c r="F74" s="4" t="s">
@@ -13408,7 +13419,7 @@
       <c r="G74" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H74" s="52" t="s">
+      <c r="H74" s="50" t="s">
         <v>285</v>
       </c>
       <c r="I74" s="4" t="s">
@@ -13423,46 +13434,46 @@
       <c r="L74" s="6">
         <v>42136</v>
       </c>
-      <c r="T74" s="46">
+      <c r="T74" s="44">
         <v>0.2845</v>
       </c>
-      <c r="U74" s="46">
+      <c r="U74" s="44">
         <v>-0.3169</v>
       </c>
-      <c r="V74" s="46">
+      <c r="V74" s="44">
         <v>0.364</v>
       </c>
-      <c r="W74" s="46">
+      <c r="W74" s="44">
         <v>0.0918</v>
       </c>
-      <c r="X74" s="46">
+      <c r="X74" s="44">
         <v>-0.1478</v>
       </c>
-      <c r="Y74" s="46">
+      <c r="Y74" s="44">
         <v>0.3972</v>
       </c>
-      <c r="Z74" s="46">
+      <c r="Z74" s="44">
         <v>-0.4247</v>
       </c>
-      <c r="AA74" s="46">
+      <c r="AA74" s="44">
         <v>0.2623</v>
       </c>
-      <c r="AB74" s="46">
+      <c r="AB74" s="44">
         <v>0.3642</v>
       </c>
-      <c r="AC74" s="46">
+      <c r="AC74" s="44">
         <v>0.784</v>
       </c>
-      <c r="AD74" s="46">
+      <c r="AD74" s="44">
         <v>-0.2596</v>
       </c>
-      <c r="AE74" s="46">
+      <c r="AE74" s="44">
         <v>-0.2471</v>
       </c>
-      <c r="AF74" s="46">
+      <c r="AF74" s="44">
         <v>-0.066</v>
       </c>
-      <c r="AG74" s="46">
+      <c r="AG74" s="44">
         <v>0.8939</v>
       </c>
       <c r="AH74" s="41"/>
@@ -13470,228 +13481,1045 @@
         <f>SUM(T74:AG74)/14</f>
         <v>0.141414285714286</v>
       </c>
-      <c r="AR74" s="46">
+      <c r="AR74" s="44">
         <v>0.356</v>
       </c>
-      <c r="AS74" s="46">
+      <c r="AS74" s="44">
         <v>0.3042</v>
       </c>
-      <c r="AT74" s="46">
+      <c r="AT74" s="44">
         <v>0.2529</v>
       </c>
-      <c r="AU74" s="46">
+      <c r="AU74" s="44">
         <v>0.5012</v>
       </c>
-      <c r="AV74" s="46">
+      <c r="AV74" s="44">
         <v>0.3771</v>
       </c>
-      <c r="AW74" s="46">
+      <c r="AW74" s="44">
         <v>0.3215</v>
       </c>
-      <c r="AX74" s="46">
+      <c r="AX74" s="44">
         <v>0.323</v>
       </c>
-      <c r="AY74" s="46">
+      <c r="AY74" s="44">
         <v>0.3101</v>
       </c>
-      <c r="AZ74" s="46">
+      <c r="AZ74" s="44">
         <v>0.377</v>
       </c>
-      <c r="BA74" s="46">
+      <c r="BA74" s="44">
         <v>0.4622</v>
       </c>
-      <c r="BB74" s="46">
+      <c r="BB74" s="44">
         <v>0.3643</v>
       </c>
-      <c r="BC74" s="46">
+      <c r="BC74" s="44">
         <v>0.2226</v>
       </c>
-      <c r="BD74" s="46">
+      <c r="BD74" s="44">
         <v>0.3429</v>
       </c>
-      <c r="BE74" s="46">
+      <c r="BE74" s="44">
         <v>0.3035</v>
       </c>
-      <c r="BG74" s="49">
+      <c r="BG74" s="47">
         <v>0.893872817833167</v>
       </c>
-      <c r="BH74" s="49">
+      <c r="BH74" s="47">
         <v>0.100205205159584</v>
       </c>
-      <c r="BI74" s="49">
+      <c r="BI74" s="47">
         <v>0.119569229540326</v>
       </c>
-      <c r="BJ74" s="49">
+      <c r="BJ74" s="47">
         <v>0.171535040660459</v>
       </c>
-      <c r="BK74" s="49">
+      <c r="BK74" s="47">
         <v>0.103920760507768</v>
       </c>
-      <c r="BL74" s="49">
+      <c r="BL74" s="47">
         <v>0.0771621992656473</v>
       </c>
-      <c r="BM74" s="49">
+      <c r="BM74" s="47">
         <v>0.0591421027895198</v>
       </c>
-      <c r="BN74" s="50" t="s">
+      <c r="BN74" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="BO74" s="50" t="s">
+      <c r="BO74" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="BP74" s="50" t="s">
+      <c r="BP74" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="BQ74" s="50" t="s">
+      <c r="BQ74" s="48" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="75" spans="1:69">
-      <c r="A75" s="43"/>
+    <row r="75" ht="15.75" spans="1:69">
+      <c r="A75" s="49"/>
       <c r="B75" s="42"/>
-      <c r="W75" s="41"/>
-      <c r="X75" s="41"/>
-      <c r="Y75" s="41"/>
-      <c r="Z75" s="41"/>
-      <c r="AA75" s="41"/>
-      <c r="AB75" s="41"/>
-      <c r="AC75" s="41"/>
-      <c r="AD75" s="41"/>
-      <c r="AE75" s="41"/>
-      <c r="AF75" s="41"/>
-      <c r="AG75" s="41"/>
+      <c r="E75" s="50"/>
+      <c r="H75" s="50"/>
+      <c r="T75" s="44"/>
+      <c r="U75" s="44"/>
+      <c r="V75" s="44"/>
+      <c r="W75" s="44"/>
+      <c r="X75" s="44"/>
+      <c r="Y75" s="44"/>
+      <c r="Z75" s="44"/>
+      <c r="AA75" s="44"/>
+      <c r="AB75" s="44"/>
+      <c r="AC75" s="44"/>
+      <c r="AD75" s="44"/>
+      <c r="AE75" s="44"/>
+      <c r="AF75" s="44"/>
+      <c r="AG75" s="44"/>
       <c r="AH75" s="41"/>
-    </row>
-    <row r="76" spans="1:69">
+      <c r="AR75" s="44"/>
+      <c r="AS75" s="44"/>
+      <c r="AT75" s="44"/>
+      <c r="AU75" s="44"/>
+      <c r="AV75" s="44"/>
+      <c r="AW75" s="44"/>
+      <c r="AX75" s="44"/>
+      <c r="AY75" s="44"/>
+      <c r="AZ75" s="44"/>
+      <c r="BA75" s="44"/>
+      <c r="BB75" s="44"/>
+      <c r="BC75" s="44"/>
+      <c r="BD75" s="44"/>
+      <c r="BE75" s="44"/>
+      <c r="BG75" s="47"/>
+      <c r="BH75" s="47"/>
+      <c r="BI75" s="47"/>
+      <c r="BJ75" s="47"/>
+      <c r="BK75" s="47"/>
+      <c r="BL75" s="47"/>
+      <c r="BM75" s="47"/>
+      <c r="BN75" s="48"/>
+      <c r="BO75" s="48"/>
+      <c r="BP75" s="48"/>
+      <c r="BQ75" s="48"/>
+    </row>
+    <row r="76" s="4" customFormat="1" ht="54" spans="1:69">
       <c r="A76" s="42" t="s">
         <v>286</v>
       </c>
-      <c r="B76" s="62" t="s">
+      <c r="B76" s="42">
+        <v>399808</v>
+      </c>
+      <c r="C76" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="K76" s="13"/>
-      <c r="W76" s="41"/>
-      <c r="X76" s="41"/>
-      <c r="Y76" s="41"/>
-      <c r="Z76" s="41"/>
-      <c r="AA76" s="41"/>
-      <c r="AB76" s="41"/>
-      <c r="AC76" s="41"/>
-      <c r="AD76" s="41"/>
-      <c r="AE76" s="41"/>
-      <c r="AF76" s="41"/>
-      <c r="AG76" s="41"/>
+      <c r="D76" s="4">
+        <v>80</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J76" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K76" s="40">
+        <v>40908</v>
+      </c>
+      <c r="L76" s="6">
+        <v>42045</v>
+      </c>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+      <c r="O76" s="6"/>
+      <c r="P76" s="6"/>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="14">
+        <v>-0.1424</v>
+      </c>
+      <c r="U76" s="14">
+        <v>0.2332</v>
+      </c>
+      <c r="V76" s="14">
+        <v>0.3354</v>
+      </c>
+      <c r="W76" s="14">
+        <v>0.5044</v>
+      </c>
+      <c r="X76" s="14">
+        <v>-0.1972</v>
+      </c>
+      <c r="Y76" s="14">
+        <v>0.0815</v>
+      </c>
+      <c r="Z76" s="14">
+        <v>-0.3446</v>
+      </c>
+      <c r="AA76" s="14">
+        <v>0.2432</v>
+      </c>
+      <c r="AB76" s="14">
+        <v>1.0529</v>
+      </c>
+      <c r="AC76" s="14">
+        <v>0.4935</v>
+      </c>
+      <c r="AD76" s="14">
+        <v>-0.281</v>
+      </c>
+      <c r="AE76" s="14">
+        <v>-0.3585</v>
+      </c>
+      <c r="AF76" s="14">
+        <v>-0.0703</v>
+      </c>
+      <c r="AG76" s="14">
+        <v>0.4244</v>
+      </c>
       <c r="AH76" s="41"/>
-    </row>
-    <row r="77" spans="1:69">
+      <c r="AI76" s="7">
+        <f>SUM(T76:AG76)/14</f>
+        <v>0.141035714285714</v>
+      </c>
+      <c r="AR76" s="14">
+        <v>0.2596</v>
+      </c>
+      <c r="AS76" s="14">
+        <v>0.256</v>
+      </c>
+      <c r="AT76" s="14">
+        <v>0.2224</v>
+      </c>
+      <c r="AU76" s="14">
+        <v>0.4816</v>
+      </c>
+      <c r="AV76" s="14">
+        <v>0.3178</v>
+      </c>
+      <c r="AW76" s="14">
+        <v>0.1668</v>
+      </c>
+      <c r="AX76" s="14">
+        <v>0.2435</v>
+      </c>
+      <c r="AY76" s="14">
+        <v>0.2331</v>
+      </c>
+      <c r="AZ76" s="14">
+        <v>0.3433</v>
+      </c>
+      <c r="BA76" s="14">
+        <v>0.3743</v>
+      </c>
+      <c r="BB76" s="14">
+        <v>0.3427</v>
+      </c>
+      <c r="BC76" s="14">
+        <v>0.2277</v>
+      </c>
+      <c r="BD76" s="14">
+        <v>0.3535</v>
+      </c>
+      <c r="BE76" s="14">
+        <v>0.2803</v>
+      </c>
+      <c r="BG76" s="15">
+        <v>0.424431490421107</v>
+      </c>
+      <c r="BH76" s="15">
+        <v>-0.0529058980379562</v>
+      </c>
+      <c r="BI76" s="15">
+        <v>-0.0182033749697655</v>
+      </c>
+      <c r="BJ76" s="15">
+        <v>0.128311781176597</v>
+      </c>
+      <c r="BK76" s="15">
+        <v>0.0572384068663403</v>
+      </c>
+      <c r="BL76" s="15">
+        <v>0.0647056837503679</v>
+      </c>
+      <c r="BM76" s="15">
+        <v>0.0957339948502836</v>
+      </c>
+      <c r="BN76" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="BO76" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="BP76" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="BQ76" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="77" s="4" customFormat="1" ht="81" spans="1:69">
       <c r="A77" s="42" t="s">
-        <v>288</v>
-      </c>
-      <c r="B77" s="62" t="s">
         <v>289</v>
       </c>
-      <c r="K77" s="13"/>
-      <c r="W77" s="41"/>
-      <c r="X77" s="41"/>
-      <c r="Y77" s="41"/>
-      <c r="Z77" s="41"/>
-      <c r="AA77" s="41"/>
-      <c r="AB77" s="41"/>
-      <c r="AC77" s="41"/>
-      <c r="AD77" s="41"/>
-      <c r="AE77" s="41"/>
-      <c r="AF77" s="41"/>
-      <c r="AG77" s="41"/>
+      <c r="B77" s="42">
+        <v>931151</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D77" s="4">
+        <v>50</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J77" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K77" s="40">
+        <v>41274</v>
+      </c>
+      <c r="L77" s="6">
+        <v>43577</v>
+      </c>
+      <c r="M77" s="6"/>
+      <c r="N77" s="6"/>
+      <c r="O77" s="6"/>
+      <c r="P77" s="6"/>
+      <c r="Q77" s="6"/>
+      <c r="R77" s="6"/>
+      <c r="S77" s="6"/>
+      <c r="T77" s="6"/>
+      <c r="U77" s="14">
+        <v>0.317</v>
+      </c>
+      <c r="V77" s="14">
+        <v>0.2505</v>
+      </c>
+      <c r="W77" s="14">
+        <v>0.4539</v>
+      </c>
+      <c r="X77" s="14">
+        <v>-0.167</v>
+      </c>
+      <c r="Y77" s="14">
+        <v>0.0796</v>
+      </c>
+      <c r="Z77" s="14">
+        <v>-0.3696</v>
+      </c>
+      <c r="AA77" s="14">
+        <v>0.2408</v>
+      </c>
+      <c r="AB77" s="14">
+        <v>1.1094</v>
+      </c>
+      <c r="AC77" s="14">
+        <v>0.4926</v>
+      </c>
+      <c r="AD77" s="14">
+        <v>-0.2015</v>
+      </c>
+      <c r="AE77" s="14">
+        <v>-0.3638</v>
+      </c>
+      <c r="AF77" s="14">
+        <v>-0.1593</v>
+      </c>
+      <c r="AG77" s="14">
+        <v>0.262</v>
+      </c>
       <c r="AH77" s="41"/>
-    </row>
-    <row r="78" spans="1:69">
+      <c r="AI77" s="7">
+        <f>SUM(U77:AG77)/13</f>
+        <v>0.149584615384615</v>
+      </c>
+      <c r="AS77" s="14">
+        <v>0.2691</v>
+      </c>
+      <c r="AT77" s="14">
+        <v>0.2224</v>
+      </c>
+      <c r="AU77" s="14">
+        <v>0.4889</v>
+      </c>
+      <c r="AV77" s="14">
+        <v>0.2967</v>
+      </c>
+      <c r="AW77" s="14">
+        <v>0.1847</v>
+      </c>
+      <c r="AX77" s="14">
+        <v>0.2578</v>
+      </c>
+      <c r="AY77" s="14">
+        <v>0.2514</v>
+      </c>
+      <c r="AZ77" s="14">
+        <v>0.3672</v>
+      </c>
+      <c r="BA77" s="14">
+        <v>0.375</v>
+      </c>
+      <c r="BB77" s="14">
+        <v>0.3672</v>
+      </c>
+      <c r="BC77" s="14">
+        <v>0.2556</v>
+      </c>
+      <c r="BD77" s="14">
+        <v>0.3765</v>
+      </c>
+      <c r="BE77" s="14">
+        <v>0.3018</v>
+      </c>
+      <c r="BG77" s="15">
+        <v>0.261957539254994</v>
+      </c>
+      <c r="BH77" s="15">
+        <v>-0.122819513473144</v>
+      </c>
+      <c r="BI77" s="15">
+        <v>-0.0425874870017393</v>
+      </c>
+      <c r="BJ77" s="15">
+        <v>0.112222063704123</v>
+      </c>
+      <c r="BK77" s="15">
+        <v>0.0407754065012629</v>
+      </c>
+      <c r="BL77" s="15">
+        <v>0.051387220246065</v>
+      </c>
+      <c r="BM77" s="15">
+        <v>0.0841288241545439</v>
+      </c>
+      <c r="BN77" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="BO77" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="BP77" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="BQ77" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="78" s="4" customFormat="1" ht="81" spans="1:69">
       <c r="A78" s="42" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B78" s="42" t="s">
-        <v>291</v>
-      </c>
-      <c r="K78" s="13"/>
-      <c r="W78" s="41"/>
-      <c r="X78" s="41"/>
-      <c r="Y78" s="41"/>
-      <c r="Z78" s="41"/>
-      <c r="AA78" s="41"/>
-      <c r="AB78" s="41"/>
-      <c r="AC78" s="41"/>
-      <c r="AD78" s="41"/>
-      <c r="AE78" s="41"/>
-      <c r="AF78" s="41"/>
-      <c r="AG78" s="41"/>
+        <v>293</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D78" s="4">
+        <v>66</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J78" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K78" s="40">
+        <v>40543</v>
+      </c>
+      <c r="L78" s="6">
+        <v>42045</v>
+      </c>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6"/>
+      <c r="P78" s="6"/>
+      <c r="Q78" s="6"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="14">
+        <v>-0.3681</v>
+      </c>
+      <c r="T78" s="14">
+        <v>-0.121</v>
+      </c>
+      <c r="U78" s="14">
+        <v>0.5062</v>
+      </c>
+      <c r="V78" s="14">
+        <v>0.3299</v>
+      </c>
+      <c r="W78" s="14">
+        <v>0.6853</v>
+      </c>
+      <c r="X78" s="14">
+        <v>-0.2276</v>
+      </c>
+      <c r="Y78" s="14">
+        <v>-0.0575</v>
+      </c>
+      <c r="Z78" s="14">
+        <v>-0.2931</v>
+      </c>
+      <c r="AA78" s="14">
+        <v>0.2485</v>
+      </c>
+      <c r="AB78" s="14">
+        <v>0.3998</v>
+      </c>
+      <c r="AC78" s="14">
+        <v>0.1465</v>
+      </c>
+      <c r="AD78" s="14">
+        <v>-0.3176</v>
+      </c>
+      <c r="AE78" s="14">
+        <v>0.0601</v>
+      </c>
+      <c r="AF78" s="14">
+        <v>0.0434</v>
+      </c>
+      <c r="AG78" s="14">
+        <v>0.3078</v>
+      </c>
       <c r="AH78" s="41"/>
-    </row>
-    <row r="79" spans="1:69">
-      <c r="A79" s="42"/>
-      <c r="B79" s="42"/>
-      <c r="K79" s="13"/>
-      <c r="W79" s="41"/>
-      <c r="X79" s="41"/>
-      <c r="Y79" s="41"/>
-      <c r="Z79" s="41"/>
-      <c r="AA79" s="41"/>
-      <c r="AB79" s="41"/>
-      <c r="AC79" s="41"/>
-      <c r="AD79" s="41"/>
-      <c r="AE79" s="41"/>
-      <c r="AF79" s="41"/>
-      <c r="AG79" s="41"/>
+      <c r="AI78" s="7">
+        <f>SUM(S78:AG78)/15</f>
+        <v>0.0895066666666667</v>
+      </c>
+      <c r="AQ78" s="14">
+        <v>0.2566</v>
+      </c>
+      <c r="AR78" s="14">
+        <v>0.2718</v>
+      </c>
+      <c r="AS78" s="14">
+        <v>0.2885</v>
+      </c>
+      <c r="AT78" s="14">
+        <v>0.2595</v>
+      </c>
+      <c r="AU78" s="14">
+        <v>0.524</v>
+      </c>
+      <c r="AV78" s="14">
+        <v>0.3445</v>
+      </c>
+      <c r="AW78" s="14">
+        <v>0.1751</v>
+      </c>
+      <c r="AX78" s="14">
+        <v>0.2645</v>
+      </c>
+      <c r="AY78" s="14">
+        <v>0.2605</v>
+      </c>
+      <c r="AZ78" s="14">
+        <v>0.3019</v>
+      </c>
+      <c r="BA78" s="14">
+        <v>0.2474</v>
+      </c>
+      <c r="BB78" s="14">
+        <v>0.2823</v>
+      </c>
+      <c r="BC78" s="14">
+        <v>0.2053</v>
+      </c>
+      <c r="BD78" s="14">
+        <v>0.3788</v>
+      </c>
+      <c r="BE78" s="14">
+        <v>0.3149</v>
+      </c>
+      <c r="BG78" s="15">
+        <v>0.30784836500963</v>
+      </c>
+      <c r="BH78" s="15">
+        <v>0.130953301591754</v>
+      </c>
+      <c r="BI78" s="15">
+        <v>0.0250512908325602</v>
+      </c>
+      <c r="BJ78" s="15">
+        <v>0.102334327696592</v>
+      </c>
+      <c r="BK78" s="15">
+        <v>0.031127431352026</v>
+      </c>
+      <c r="BL78" s="15">
+        <v>0.0502664176948528</v>
+      </c>
+      <c r="BM78" s="15">
+        <v>0.099588465612481</v>
+      </c>
+      <c r="BN78" s="15">
+        <v>0.044018291518692</v>
+      </c>
+    </row>
+    <row r="79" s="4" customFormat="1" ht="40.5" spans="1:69">
+      <c r="A79" s="31" t="s">
+        <v>296</v>
+      </c>
+      <c r="B79" s="51">
+        <v>930607</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D79" s="4">
+        <v>100</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J79" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K79" s="40">
+        <v>38352</v>
+      </c>
+      <c r="L79" s="6">
+        <v>42094</v>
+      </c>
+      <c r="M79" s="14">
+        <v>-0.1623</v>
+      </c>
+      <c r="N79" s="14">
+        <v>1.1486</v>
+      </c>
+      <c r="O79" s="14">
+        <v>1.5355</v>
+      </c>
+      <c r="P79" s="14">
+        <v>-0.6968</v>
+      </c>
+      <c r="Q79" s="14">
+        <v>2.2806</v>
+      </c>
+      <c r="R79" s="14">
+        <v>-0.0391</v>
+      </c>
+      <c r="S79" s="14">
+        <v>-0.3269</v>
+      </c>
+      <c r="T79" s="14">
+        <v>0.0563</v>
+      </c>
+      <c r="U79" s="14">
+        <v>0.1335</v>
+      </c>
+      <c r="V79" s="14">
+        <v>0.3359</v>
+      </c>
+      <c r="W79" s="14">
+        <v>0.3959</v>
+      </c>
+      <c r="X79" s="14">
+        <v>-0.1188</v>
+      </c>
+      <c r="Y79" s="14">
+        <v>0.0017</v>
+      </c>
+      <c r="Z79" s="14">
+        <v>-0.3458</v>
+      </c>
+      <c r="AA79" s="14">
+        <v>0.1635</v>
+      </c>
+      <c r="AB79" s="14">
+        <v>0.5243</v>
+      </c>
+      <c r="AC79" s="14">
+        <v>0.1321</v>
+      </c>
+      <c r="AD79" s="14">
+        <v>-0.2183</v>
+      </c>
+      <c r="AE79" s="14">
+        <v>0.0136</v>
+      </c>
+      <c r="AF79" s="14">
+        <v>0.143</v>
+      </c>
+      <c r="AG79" s="14">
+        <v>0.1731</v>
+      </c>
       <c r="AH79" s="41"/>
-    </row>
-    <row r="80" spans="1:69">
+      <c r="AI79" s="7">
+        <f>SUM(M79:AG79)/21</f>
+        <v>0.244266666666667</v>
+      </c>
+      <c r="AK79" s="14">
+        <v>0.2701</v>
+      </c>
+      <c r="AL79" s="14">
+        <v>0.2916</v>
+      </c>
+      <c r="AM79" s="14">
+        <v>0.4482</v>
+      </c>
+      <c r="AN79" s="14">
+        <v>0.5519</v>
+      </c>
+      <c r="AO79" s="14">
+        <v>0.3861</v>
+      </c>
+      <c r="AP79" s="14">
+        <v>0.3182</v>
+      </c>
+      <c r="AQ79" s="14">
+        <v>0.2503</v>
+      </c>
+      <c r="AR79" s="14">
+        <v>0.2297</v>
+      </c>
+      <c r="AS79" s="14">
+        <v>0.2689</v>
+      </c>
+      <c r="AT79" s="14">
+        <v>0.2064</v>
+      </c>
+      <c r="AU79" s="14">
+        <v>0.4346</v>
+      </c>
+      <c r="AV79" s="14">
+        <v>0.2595</v>
+      </c>
+      <c r="AW79" s="14">
+        <v>0.1289</v>
+      </c>
+      <c r="AX79" s="14">
+        <v>0.2135</v>
+      </c>
+      <c r="AY79" s="14">
+        <v>0.2354</v>
+      </c>
+      <c r="AZ79" s="14">
+        <v>0.3152</v>
+      </c>
+      <c r="BA79" s="14">
+        <v>0.2607</v>
+      </c>
+      <c r="BB79" s="14">
+        <v>0.3212</v>
+      </c>
+      <c r="BC79" s="14">
+        <v>0.2108</v>
+      </c>
+      <c r="BD79" s="14">
+        <v>0.2696</v>
+      </c>
+      <c r="BE79" s="14">
+        <v>0.2234</v>
+      </c>
+      <c r="BG79" s="15">
+        <v>0.17312438535098</v>
+      </c>
+      <c r="BH79" s="15">
+        <v>0.10767977245035</v>
+      </c>
+      <c r="BI79" s="15">
+        <v>0.0376148686831699</v>
+      </c>
+      <c r="BJ79" s="15">
+        <v>0.114302232765049</v>
+      </c>
+      <c r="BK79" s="15">
+        <v>0.0379186007361549</v>
+      </c>
+      <c r="BL79" s="15">
+        <v>0.0505044838926962</v>
+      </c>
+      <c r="BM79" s="15">
+        <v>0.07638623614566</v>
+      </c>
+      <c r="BN79" s="15">
+        <v>0.0419109564644644</v>
+      </c>
+      <c r="BO79" s="15">
+        <v>0.109338620971297</v>
+      </c>
+      <c r="BP79" s="15">
+        <v>0.0822120269230009</v>
+      </c>
+      <c r="BQ79" s="15">
+        <v>0.104585434484066</v>
+      </c>
+    </row>
+    <row r="80" s="4" customFormat="1" ht="121.5" spans="1:69">
       <c r="A80" s="42" t="s">
-        <v>292</v>
-      </c>
-      <c r="B80" s="42">
-        <v>399812</v>
-      </c>
-      <c r="K80" s="13"/>
-      <c r="W80" s="41"/>
-      <c r="X80" s="41"/>
-      <c r="Y80" s="41"/>
-      <c r="Z80" s="41"/>
-      <c r="AA80" s="41"/>
-      <c r="AB80" s="41"/>
-      <c r="AC80" s="41"/>
-      <c r="AD80" s="41"/>
-      <c r="AE80" s="41"/>
-      <c r="AF80" s="41"/>
-      <c r="AG80" s="41"/>
+        <v>299</v>
+      </c>
+      <c r="B80" s="60" t="s">
+        <v>300</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D80" s="4">
+        <v>100</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="J80" s="4">
+        <v>1000</v>
+      </c>
+      <c r="K80" s="40">
+        <v>40907</v>
+      </c>
+      <c r="L80" s="6">
+        <v>41177</v>
+      </c>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="6"/>
+      <c r="P80" s="6"/>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6"/>
+      <c r="T80" s="14">
+        <v>-0.102</v>
+      </c>
+      <c r="U80" s="14">
+        <v>0.3173</v>
+      </c>
+      <c r="V80" s="14">
+        <v>0.2864</v>
+      </c>
+      <c r="W80" s="14">
+        <v>0.3945</v>
+      </c>
+      <c r="X80" s="14">
+        <v>-0.1717</v>
+      </c>
+      <c r="Y80" s="14">
+        <v>-0.0104</v>
+      </c>
+      <c r="Z80" s="14">
+        <v>-0.3899</v>
+      </c>
+      <c r="AA80" s="14">
+        <v>0.1961</v>
+      </c>
+      <c r="AB80" s="14">
+        <v>0.5372</v>
+      </c>
+      <c r="AC80" s="14">
+        <v>0.4451</v>
+      </c>
+      <c r="AD80" s="14">
+        <v>-0.2508</v>
+      </c>
+      <c r="AE80" s="14">
+        <v>-0.3087</v>
+      </c>
+      <c r="AF80" s="14">
+        <v>0.005</v>
+      </c>
+      <c r="AG80" s="14">
+        <v>0.2698</v>
+      </c>
       <c r="AH80" s="41"/>
-    </row>
-    <row r="81" spans="1:34">
-      <c r="A81" s="42" t="s">
-        <v>293</v>
-      </c>
-      <c r="B81" s="42">
-        <v>399808</v>
-      </c>
-      <c r="K81" s="13"/>
-      <c r="W81" s="41"/>
-      <c r="X81" s="41"/>
-      <c r="Y81" s="41"/>
-      <c r="Z81" s="41"/>
-      <c r="AA81" s="41"/>
-      <c r="AB81" s="41"/>
-      <c r="AC81" s="41"/>
-      <c r="AD81" s="41"/>
-      <c r="AE81" s="41"/>
-      <c r="AF81" s="41"/>
-      <c r="AG81" s="41"/>
+      <c r="AI80" s="7">
+        <f>SUM(T80:AG80)/14</f>
+        <v>0.0869928571428572</v>
+      </c>
+      <c r="AR80" s="14">
+        <v>4.3116</v>
+      </c>
+      <c r="AS80" s="14">
+        <v>0.2564</v>
+      </c>
+      <c r="AT80" s="14">
+        <v>0.2144</v>
+      </c>
+      <c r="AU80" s="14">
+        <v>0.4512</v>
+      </c>
+      <c r="AV80" s="14">
+        <v>0.2908</v>
+      </c>
+      <c r="AW80" s="14">
+        <v>0.1553</v>
+      </c>
+      <c r="AX80" s="14">
+        <v>0.2225</v>
+      </c>
+      <c r="AY80" s="14">
+        <v>0.2367</v>
+      </c>
+      <c r="AZ80" s="14">
+        <v>0.2878</v>
+      </c>
+      <c r="BA80" s="14">
+        <v>0.3163</v>
+      </c>
+      <c r="BB80" s="14">
+        <v>0.3027</v>
+      </c>
+      <c r="BC80" s="14">
+        <v>0.1934</v>
+      </c>
+      <c r="BD80" s="14">
+        <v>0.2922</v>
+      </c>
+      <c r="BE80" s="14">
+        <v>0.2324</v>
+      </c>
+      <c r="BG80" s="15">
+        <v>0.26975333878441</v>
+      </c>
+      <c r="BH80" s="15">
+        <v>-0.0409315217006395</v>
+      </c>
+      <c r="BI80" s="15">
+        <v>-0.00915448898492521</v>
+      </c>
+      <c r="BJ80" s="15">
+        <v>0.0837622051641667</v>
+      </c>
+      <c r="BK80" s="15">
+        <v>0.00651310415021245</v>
+      </c>
+      <c r="BL80" s="15">
+        <v>0.0185909671490054</v>
+      </c>
+      <c r="BM80" s="15">
+        <v>0.0577633559129336</v>
+      </c>
+      <c r="BN80" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="BO80" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="BP80" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="BQ80" s="17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" spans="1:69">
+      <c r="A81" s="49"/>
+      <c r="B81" s="42"/>
+      <c r="E81" s="50"/>
+      <c r="H81" s="50"/>
+      <c r="T81" s="44"/>
+      <c r="U81" s="44"/>
+      <c r="V81" s="44"/>
+      <c r="W81" s="44"/>
+      <c r="X81" s="44"/>
+      <c r="Y81" s="44"/>
+      <c r="Z81" s="44"/>
+      <c r="AA81" s="44"/>
+      <c r="AB81" s="44"/>
+      <c r="AC81" s="44"/>
+      <c r="AD81" s="44"/>
+      <c r="AE81" s="44"/>
+      <c r="AF81" s="44"/>
+      <c r="AG81" s="44"/>
       <c r="AH81" s="41"/>
-    </row>
-    <row r="82" spans="1:34">
+      <c r="AR81" s="44"/>
+      <c r="AS81" s="44"/>
+      <c r="AT81" s="44"/>
+      <c r="AU81" s="44"/>
+      <c r="AV81" s="44"/>
+      <c r="AW81" s="44"/>
+      <c r="AX81" s="44"/>
+      <c r="AY81" s="44"/>
+      <c r="AZ81" s="44"/>
+      <c r="BA81" s="44"/>
+      <c r="BB81" s="44"/>
+      <c r="BC81" s="44"/>
+      <c r="BD81" s="44"/>
+      <c r="BE81" s="44"/>
+      <c r="BG81" s="47"/>
+      <c r="BH81" s="47"/>
+      <c r="BI81" s="47"/>
+      <c r="BJ81" s="47"/>
+      <c r="BK81" s="47"/>
+      <c r="BL81" s="47"/>
+      <c r="BM81" s="47"/>
+      <c r="BN81" s="48"/>
+      <c r="BO81" s="48"/>
+      <c r="BP81" s="48"/>
+      <c r="BQ81" s="48"/>
+    </row>
+    <row r="82" spans="1:69">
       <c r="A82" s="42" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="B82" s="42">
-        <v>399967</v>
-      </c>
-      <c r="K82" s="13"/>
+        <v>931071</v>
+      </c>
+      <c r="K82" s="52">
+        <v>42004</v>
+      </c>
       <c r="W82" s="41"/>
       <c r="X82" s="41"/>
       <c r="Y82" s="41"/>
@@ -13705,14 +14533,16 @@
       <c r="AG82" s="41"/>
       <c r="AH82" s="41"/>
     </row>
-    <row r="83" spans="1:34">
-      <c r="A83" s="42" t="s">
-        <v>295</v>
+    <row r="83" spans="1:69">
+      <c r="A83" s="43" t="s">
+        <v>304</v>
       </c>
       <c r="B83" s="42">
-        <v>399971</v>
-      </c>
-      <c r="K83" s="13"/>
+        <v>930902</v>
+      </c>
+      <c r="K83" s="52">
+        <v>41274</v>
+      </c>
       <c r="W83" s="41"/>
       <c r="X83" s="41"/>
       <c r="Y83" s="41"/>
@@ -13726,14 +14556,16 @@
       <c r="AG83" s="41"/>
       <c r="AH83" s="41"/>
     </row>
-    <row r="84" spans="1:34">
+    <row r="84" spans="1:69">
       <c r="A84" s="42" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B84" s="42">
-        <v>399973</v>
-      </c>
-      <c r="K84" s="13"/>
+        <v>931582</v>
+      </c>
+      <c r="K84" s="52">
+        <v>42734</v>
+      </c>
       <c r="W84" s="41"/>
       <c r="X84" s="41"/>
       <c r="Y84" s="41"/>
@@ -13747,10 +14579,16 @@
       <c r="AG84" s="41"/>
       <c r="AH84" s="41"/>
     </row>
-    <row r="85" spans="1:34">
-      <c r="A85" s="42"/>
-      <c r="B85" s="42"/>
-      <c r="K85" s="13"/>
+    <row r="85" spans="1:69">
+      <c r="A85" s="42" t="s">
+        <v>306</v>
+      </c>
+      <c r="B85" s="42">
+        <v>930601</v>
+      </c>
+      <c r="K85" s="53">
+        <v>38352</v>
+      </c>
       <c r="W85" s="41"/>
       <c r="X85" s="41"/>
       <c r="Y85" s="41"/>
@@ -13764,14 +14602,19 @@
       <c r="AG85" s="41"/>
       <c r="AH85" s="41"/>
     </row>
-    <row r="86" spans="1:34">
-      <c r="A86" s="42" t="s">
-        <v>297</v>
-      </c>
-      <c r="B86" s="42">
-        <v>399986</v>
-      </c>
-      <c r="K86" s="13"/>
+    <row r="86" spans="1:69">
+      <c r="A86" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="C86" s="43" t="s">
+        <v>309</v>
+      </c>
+      <c r="K86" s="53">
+        <v>38352</v>
+      </c>
       <c r="W86" s="41"/>
       <c r="X86" s="41"/>
       <c r="Y86" s="41"/>
@@ -13785,14 +14628,10 @@
       <c r="AG86" s="41"/>
       <c r="AH86" s="41"/>
     </row>
-    <row r="87" spans="1:34">
-      <c r="A87" s="42" t="s">
-        <v>298</v>
-      </c>
-      <c r="B87" s="42">
-        <v>399975</v>
-      </c>
-      <c r="K87" s="13"/>
+    <row r="87" spans="1:69">
+      <c r="A87" s="42"/>
+      <c r="B87" s="42"/>
+      <c r="K87" s="53"/>
       <c r="W87" s="41"/>
       <c r="X87" s="41"/>
       <c r="Y87" s="41"/>
@@ -13806,9 +14645,9 @@
       <c r="AG87" s="41"/>
       <c r="AH87" s="41"/>
     </row>
-    <row r="88" spans="1:34">
+    <row r="88" spans="1:69">
       <c r="A88" s="42" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="B88" s="42">
         <v>399997</v>
@@ -13827,12 +14666,33 @@
       <c r="AG88" s="41"/>
       <c r="AH88" s="41"/>
     </row>
-    <row r="90" spans="1:34">
+    <row r="89" spans="1:69">
+      <c r="A89" s="42" t="s">
+        <v>311</v>
+      </c>
+      <c r="B89" s="42">
+        <v>930697</v>
+      </c>
+      <c r="K89" s="13"/>
+      <c r="W89" s="41"/>
+      <c r="X89" s="41"/>
+      <c r="Y89" s="41"/>
+      <c r="Z89" s="41"/>
+      <c r="AA89" s="41"/>
+      <c r="AB89" s="41"/>
+      <c r="AC89" s="41"/>
+      <c r="AD89" s="41"/>
+      <c r="AE89" s="41"/>
+      <c r="AF89" s="41"/>
+      <c r="AG89" s="41"/>
+      <c r="AH89" s="41"/>
+    </row>
+    <row r="90" spans="1:69">
       <c r="A90" s="42" t="s">
-        <v>300</v>
-      </c>
-      <c r="B90" s="42">
-        <v>930697</v>
+        <v>312</v>
+      </c>
+      <c r="B90" s="60" t="s">
+        <v>313</v>
       </c>
       <c r="K90" s="13"/>
       <c r="W90" s="41"/>
@@ -13848,9 +14708,13 @@
       <c r="AG90" s="41"/>
       <c r="AH90" s="41"/>
     </row>
-    <row r="91" spans="1:34">
-      <c r="A91" s="42"/>
-      <c r="B91" s="42"/>
+    <row r="91" spans="1:69">
+      <c r="A91" s="42" t="s">
+        <v>314</v>
+      </c>
+      <c r="B91" s="42">
+        <v>930633</v>
+      </c>
       <c r="K91" s="13"/>
       <c r="W91" s="41"/>
       <c r="X91" s="41"/>
@@ -13865,12 +14729,12 @@
       <c r="AG91" s="41"/>
       <c r="AH91" s="41"/>
     </row>
-    <row r="92" spans="1:34">
-      <c r="A92" s="43" t="s">
-        <v>301</v>
-      </c>
-      <c r="B92" s="53">
-        <v>930607</v>
+    <row r="92" spans="1:69">
+      <c r="A92" s="42" t="s">
+        <v>315</v>
+      </c>
+      <c r="B92" s="42">
+        <v>399812</v>
       </c>
       <c r="K92" s="13"/>
       <c r="W92" s="41"/>
@@ -13886,16 +14750,10 @@
       <c r="AG92" s="41"/>
       <c r="AH92" s="41"/>
     </row>
-    <row r="93" spans="1:34">
-      <c r="A93" s="42" t="s">
-        <v>302</v>
-      </c>
-      <c r="B93" s="42">
-        <v>930601</v>
-      </c>
-      <c r="K93" s="54">
-        <v>38352</v>
-      </c>
+    <row r="93" spans="1:69">
+      <c r="A93" s="42"/>
+      <c r="B93" s="42"/>
+      <c r="K93" s="53"/>
       <c r="W93" s="41"/>
       <c r="X93" s="41"/>
       <c r="Y93" s="41"/>
@@ -13909,14 +14767,39 @@
       <c r="AG93" s="41"/>
       <c r="AH93" s="41"/>
     </row>
-    <row r="95" spans="1:34">
+    <row r="94" spans="1:69">
+      <c r="A94" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="B94" s="42">
+        <v>930641</v>
+      </c>
+      <c r="K94" s="53">
+        <v>38352</v>
+      </c>
+      <c r="W94" s="41"/>
+      <c r="X94" s="41"/>
+      <c r="Y94" s="41"/>
+      <c r="Z94" s="41"/>
+      <c r="AA94" s="41"/>
+      <c r="AB94" s="41"/>
+      <c r="AC94" s="41"/>
+      <c r="AD94" s="41"/>
+      <c r="AE94" s="41"/>
+      <c r="AF94" s="41"/>
+      <c r="AG94" s="41"/>
+      <c r="AH94" s="41"/>
+    </row>
+    <row r="95" spans="1:69">
       <c r="A95" s="42" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="B95" s="42">
-        <v>930633</v>
-      </c>
-      <c r="K95" s="13"/>
+        <v>931152</v>
+      </c>
+      <c r="K95" s="53">
+        <v>42004</v>
+      </c>
       <c r="W95" s="41"/>
       <c r="X95" s="41"/>
       <c r="Y95" s="41"/>
@@ -13930,14 +14813,19 @@
       <c r="AG95" s="41"/>
       <c r="AH95" s="41"/>
     </row>
-    <row r="96" spans="1:34">
-      <c r="A96" s="42" t="s">
-        <v>304</v>
+    <row r="96" spans="1:69">
+      <c r="A96" s="43" t="s">
+        <v>318</v>
       </c>
       <c r="B96" s="42">
-        <v>931574</v>
-      </c>
-      <c r="K96" s="13"/>
+        <v>931153</v>
+      </c>
+      <c r="C96" s="54" t="s">
+        <v>319</v>
+      </c>
+      <c r="K96" s="53">
+        <v>41089</v>
+      </c>
       <c r="W96" s="41"/>
       <c r="X96" s="41"/>
       <c r="Y96" s="41"/>
@@ -13952,27 +14840,38 @@
       <c r="AH96" s="41"/>
     </row>
     <row r="97" spans="1:34">
-      <c r="K97" s="13"/>
-      <c r="W97" s="41"/>
-      <c r="X97" s="41"/>
-      <c r="Y97" s="41"/>
-      <c r="Z97" s="41"/>
-      <c r="AA97" s="41"/>
-      <c r="AB97" s="41"/>
-      <c r="AC97" s="41"/>
-      <c r="AD97" s="41"/>
-      <c r="AE97" s="41"/>
-      <c r="AF97" s="41"/>
-      <c r="AG97" s="41"/>
-      <c r="AH97" s="41"/>
+      <c r="A97" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B97" s="56" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="98" spans="1:34">
+      <c r="A98" s="42" t="s">
+        <v>322</v>
+      </c>
+      <c r="B98" s="42">
+        <v>399971</v>
+      </c>
+      <c r="K98" s="13"/>
+      <c r="W98" s="41"/>
+      <c r="X98" s="41"/>
+      <c r="Y98" s="41"/>
+      <c r="Z98" s="41"/>
+      <c r="AA98" s="41"/>
+      <c r="AB98" s="41"/>
+      <c r="AC98" s="41"/>
+      <c r="AD98" s="41"/>
+      <c r="AE98" s="41"/>
+      <c r="AF98" s="41"/>
+      <c r="AG98" s="41"/>
+      <c r="AH98" s="41"/>
     </row>
     <row r="99" spans="1:34">
-      <c r="A99" s="43" t="s">
-        <v>305</v>
-      </c>
-      <c r="B99" s="42">
-        <v>930914</v>
-      </c>
+      <c r="A99" s="42"/>
+      <c r="B99" s="42"/>
+      <c r="K99" s="13"/>
       <c r="W99" s="41"/>
       <c r="X99" s="41"/>
       <c r="Y99" s="41"/>
@@ -13987,15 +14886,13 @@
       <c r="AH99" s="41"/>
     </row>
     <row r="100" spans="1:34">
-      <c r="A100" s="43" t="s">
-        <v>306</v>
+      <c r="A100" s="42" t="s">
+        <v>323</v>
       </c>
       <c r="B100" s="42">
-        <v>930945</v>
-      </c>
-      <c r="K100" s="54">
-        <v>38352</v>
-      </c>
+        <v>399986</v>
+      </c>
+      <c r="K100" s="13"/>
       <c r="W100" s="41"/>
       <c r="X100" s="41"/>
       <c r="Y100" s="41"/>
@@ -14010,8 +14907,13 @@
       <c r="AH100" s="41"/>
     </row>
     <row r="101" spans="1:34">
-      <c r="A101" s="42"/>
-      <c r="B101" s="42"/>
+      <c r="A101" s="42" t="s">
+        <v>324</v>
+      </c>
+      <c r="B101" s="42">
+        <v>399975</v>
+      </c>
+      <c r="K101" s="13"/>
       <c r="W101" s="41"/>
       <c r="X101" s="41"/>
       <c r="Y101" s="41"/>
@@ -14026,15 +14928,13 @@
       <c r="AH101" s="41"/>
     </row>
     <row r="102" spans="1:34">
-      <c r="A102" s="43" t="s">
-        <v>307</v>
+      <c r="A102" s="42" t="s">
+        <v>325</v>
       </c>
       <c r="B102" s="42">
-        <v>930902</v>
-      </c>
-      <c r="K102" s="55">
-        <v>41274</v>
-      </c>
+        <v>399967</v>
+      </c>
+      <c r="K102" s="13"/>
       <c r="W102" s="41"/>
       <c r="X102" s="41"/>
       <c r="Y102" s="41"/>
@@ -14050,14 +14950,12 @@
     </row>
     <row r="103" spans="1:34">
       <c r="A103" s="42" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="B103" s="42">
-        <v>931071</v>
-      </c>
-      <c r="K103" s="55">
-        <v>42004</v>
-      </c>
+        <v>399973</v>
+      </c>
+      <c r="K103" s="13"/>
       <c r="W103" s="41"/>
       <c r="X103" s="41"/>
       <c r="Y103" s="41"/>
@@ -14073,15 +14971,12 @@
     </row>
     <row r="104" spans="1:34">
       <c r="A104" s="42" t="s">
-        <v>309</v>
-      </c>
-      <c r="B104" s="42"/>
-      <c r="C104" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="K104" s="55">
-        <v>41089</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="B104" s="42">
+        <v>931574</v>
+      </c>
+      <c r="K104" s="13"/>
       <c r="W104" s="41"/>
       <c r="X104" s="41"/>
       <c r="Y104" s="41"/>
@@ -14096,15 +14991,7 @@
       <c r="AH104" s="41"/>
     </row>
     <row r="105" spans="1:34">
-      <c r="A105" s="42" t="s">
-        <v>311</v>
-      </c>
-      <c r="B105" s="42">
-        <v>931582</v>
-      </c>
-      <c r="K105" s="55">
-        <v>42734</v>
-      </c>
+      <c r="K105" s="13"/>
       <c r="W105" s="41"/>
       <c r="X105" s="41"/>
       <c r="Y105" s="41"/>
@@ -14119,14 +15006,11 @@
       <c r="AH105" s="41"/>
     </row>
     <row r="106" spans="1:34">
-      <c r="A106" s="42" t="s">
-        <v>312</v>
+      <c r="A106" s="43" t="s">
+        <v>328</v>
       </c>
       <c r="B106" s="42">
-        <v>931151</v>
-      </c>
-      <c r="K106" s="55">
-        <v>41274</v>
+        <v>930914</v>
       </c>
       <c r="W106" s="41"/>
       <c r="X106" s="41"/>
@@ -14142,8 +15026,15 @@
       <c r="AH106" s="41"/>
     </row>
     <row r="107" spans="1:34">
-      <c r="A107" s="42"/>
-      <c r="B107" s="42"/>
+      <c r="A107" s="43" t="s">
+        <v>329</v>
+      </c>
+      <c r="B107" s="42">
+        <v>930945</v>
+      </c>
+      <c r="K107" s="53">
+        <v>38352</v>
+      </c>
       <c r="W107" s="41"/>
       <c r="X107" s="41"/>
       <c r="Y107" s="41"/>
@@ -14158,15 +15049,8 @@
       <c r="AH107" s="41"/>
     </row>
     <row r="108" spans="1:34">
-      <c r="A108" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="B108" s="42">
-        <v>930641</v>
-      </c>
-      <c r="K108" s="54">
-        <v>38352</v>
-      </c>
+      <c r="A108" s="42"/>
+      <c r="B108" s="42"/>
       <c r="W108" s="41"/>
       <c r="X108" s="41"/>
       <c r="Y108" s="41"/>
@@ -14180,90 +15064,9 @@
       <c r="AG108" s="41"/>
       <c r="AH108" s="41"/>
     </row>
-    <row r="109" spans="1:34">
-      <c r="A109" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="B109" s="42">
-        <v>931152</v>
-      </c>
-      <c r="K109" s="54">
-        <v>42004</v>
-      </c>
-      <c r="W109" s="41"/>
-      <c r="X109" s="41"/>
-      <c r="Y109" s="41"/>
-      <c r="Z109" s="41"/>
-      <c r="AA109" s="41"/>
-      <c r="AB109" s="41"/>
-      <c r="AC109" s="41"/>
-      <c r="AD109" s="41"/>
-      <c r="AE109" s="41"/>
-      <c r="AF109" s="41"/>
-      <c r="AG109" s="41"/>
-      <c r="AH109" s="41"/>
-    </row>
-    <row r="110" spans="1:34">
-      <c r="A110" s="43" t="s">
-        <v>315</v>
-      </c>
-      <c r="B110" s="42">
-        <v>931153</v>
-      </c>
-      <c r="C110" s="56" t="s">
-        <v>316</v>
-      </c>
-      <c r="K110" s="54">
-        <v>41089</v>
-      </c>
-      <c r="W110" s="41"/>
-      <c r="X110" s="41"/>
-      <c r="Y110" s="41"/>
-      <c r="Z110" s="41"/>
-      <c r="AA110" s="41"/>
-      <c r="AB110" s="41"/>
-      <c r="AC110" s="41"/>
-      <c r="AD110" s="41"/>
-      <c r="AE110" s="41"/>
-      <c r="AF110" s="41"/>
-      <c r="AG110" s="41"/>
-      <c r="AH110" s="41"/>
-    </row>
-    <row r="111" spans="1:34">
-      <c r="A111" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B111" s="58" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="112" spans="1:34">
-      <c r="A112" s="43" t="s">
-        <v>319</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="C112" s="43" t="s">
-        <v>321</v>
-      </c>
-      <c r="K112" s="54">
-        <v>38352</v>
-      </c>
-      <c r="W112" s="41"/>
-      <c r="X112" s="41"/>
-      <c r="Y112" s="41"/>
-      <c r="Z112" s="41"/>
-      <c r="AA112" s="41"/>
-      <c r="AB112" s="41"/>
-      <c r="AC112" s="41"/>
-      <c r="AD112" s="41"/>
-      <c r="AE112" s="41"/>
-      <c r="AF112" s="41"/>
-      <c r="AG112" s="41"/>
-      <c r="AH112" s="41"/>
-    </row>
-    <row r="113" spans="23:34">
+    <row r="113" spans="1:34">
+      <c r="A113" s="42"/>
+      <c r="B113" s="42"/>
       <c r="W113" s="41"/>
       <c r="X113" s="41"/>
       <c r="Y113" s="41"/>
@@ -14277,77 +15080,7 @@
       <c r="AG113" s="41"/>
       <c r="AH113" s="41"/>
     </row>
-    <row r="114" spans="23:34">
-      <c r="W114" s="41"/>
-      <c r="X114" s="41"/>
-      <c r="Y114" s="41"/>
-      <c r="Z114" s="41"/>
-      <c r="AA114" s="41"/>
-      <c r="AB114" s="41"/>
-      <c r="AC114" s="41"/>
-      <c r="AD114" s="41"/>
-      <c r="AE114" s="41"/>
-      <c r="AF114" s="41"/>
-      <c r="AG114" s="41"/>
-      <c r="AH114" s="41"/>
-    </row>
-    <row r="115" spans="23:34">
-      <c r="W115" s="41"/>
-      <c r="X115" s="41"/>
-      <c r="Y115" s="41"/>
-      <c r="Z115" s="41"/>
-      <c r="AA115" s="41"/>
-      <c r="AB115" s="41"/>
-      <c r="AC115" s="41"/>
-      <c r="AD115" s="41"/>
-      <c r="AE115" s="41"/>
-      <c r="AF115" s="41"/>
-      <c r="AG115" s="41"/>
-      <c r="AH115" s="41"/>
-    </row>
-    <row r="116" spans="23:34">
-      <c r="W116" s="41"/>
-      <c r="X116" s="41"/>
-      <c r="Y116" s="41"/>
-      <c r="Z116" s="41"/>
-      <c r="AA116" s="41"/>
-      <c r="AB116" s="41"/>
-      <c r="AC116" s="41"/>
-      <c r="AD116" s="41"/>
-      <c r="AE116" s="41"/>
-      <c r="AF116" s="41"/>
-      <c r="AG116" s="41"/>
-      <c r="AH116" s="41"/>
-    </row>
-    <row r="117" spans="23:34">
-      <c r="W117" s="41"/>
-      <c r="X117" s="41"/>
-      <c r="Y117" s="41"/>
-      <c r="Z117" s="41"/>
-      <c r="AA117" s="41"/>
-      <c r="AB117" s="41"/>
-      <c r="AC117" s="41"/>
-      <c r="AD117" s="41"/>
-      <c r="AE117" s="41"/>
-      <c r="AF117" s="41"/>
-      <c r="AG117" s="41"/>
-      <c r="AH117" s="41"/>
-    </row>
-    <row r="118" spans="23:34">
-      <c r="W118" s="41"/>
-      <c r="X118" s="41"/>
-      <c r="Y118" s="41"/>
-      <c r="Z118" s="41"/>
-      <c r="AA118" s="41"/>
-      <c r="AB118" s="41"/>
-      <c r="AC118" s="41"/>
-      <c r="AD118" s="41"/>
-      <c r="AE118" s="41"/>
-      <c r="AF118" s="41"/>
-      <c r="AG118" s="41"/>
-      <c r="AH118" s="41"/>
-    </row>
-    <row r="119" spans="23:34">
+    <row r="119" spans="1:34">
       <c r="W119" s="41"/>
       <c r="X119" s="41"/>
       <c r="Y119" s="41"/>
@@ -14361,7 +15094,7 @@
       <c r="AG119" s="41"/>
       <c r="AH119" s="41"/>
     </row>
-    <row r="120" spans="23:34">
+    <row r="120" spans="1:34">
       <c r="W120" s="41"/>
       <c r="X120" s="41"/>
       <c r="Y120" s="41"/>
@@ -14375,7 +15108,7 @@
       <c r="AG120" s="41"/>
       <c r="AH120" s="41"/>
     </row>
-    <row r="121" spans="23:34">
+    <row r="121" spans="1:34">
       <c r="W121" s="41"/>
       <c r="X121" s="41"/>
       <c r="Y121" s="41"/>
@@ -14389,7 +15122,7 @@
       <c r="AG121" s="41"/>
       <c r="AH121" s="41"/>
     </row>
-    <row r="122" spans="23:34">
+    <row r="122" spans="1:34">
       <c r="W122" s="41"/>
       <c r="X122" s="41"/>
       <c r="Y122" s="41"/>
@@ -14403,7 +15136,7 @@
       <c r="AG122" s="41"/>
       <c r="AH122" s="41"/>
     </row>
-    <row r="123" spans="23:34">
+    <row r="123" spans="1:34">
       <c r="W123" s="41"/>
       <c r="X123" s="41"/>
       <c r="Y123" s="41"/>
@@ -14417,7 +15150,7 @@
       <c r="AG123" s="41"/>
       <c r="AH123" s="41"/>
     </row>
-    <row r="124" spans="23:34">
+    <row r="124" spans="1:34">
       <c r="W124" s="41"/>
       <c r="X124" s="41"/>
       <c r="Y124" s="41"/>
@@ -14431,7 +15164,7 @@
       <c r="AG124" s="41"/>
       <c r="AH124" s="41"/>
     </row>
-    <row r="125" spans="23:34">
+    <row r="125" spans="1:34">
       <c r="W125" s="41"/>
       <c r="X125" s="41"/>
       <c r="Y125" s="41"/>
@@ -14445,7 +15178,7 @@
       <c r="AG125" s="41"/>
       <c r="AH125" s="41"/>
     </row>
-    <row r="126" spans="23:34">
+    <row r="126" spans="1:34">
       <c r="W126" s="41"/>
       <c r="X126" s="41"/>
       <c r="Y126" s="41"/>
@@ -14459,7 +15192,7 @@
       <c r="AG126" s="41"/>
       <c r="AH126" s="41"/>
     </row>
-    <row r="127" spans="23:34">
+    <row r="127" spans="1:34">
       <c r="W127" s="41"/>
       <c r="X127" s="41"/>
       <c r="Y127" s="41"/>
@@ -14473,7 +15206,7 @@
       <c r="AG127" s="41"/>
       <c r="AH127" s="41"/>
     </row>
-    <row r="128" spans="23:34">
+    <row r="128" spans="1:34">
       <c r="W128" s="41"/>
       <c r="X128" s="41"/>
       <c r="Y128" s="41"/>
@@ -16546,51 +17279,18 @@
       <c r="AH275" s="41"/>
     </row>
     <row r="276" spans="23:34">
-      <c r="W276" s="57" t="e">
-        <f t="shared" ref="W276:AG276" si="1">(F276-F3)/F3</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="X276" s="57" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Y276" s="57" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="Z276" s="57" t="e">
-        <f t="shared" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AA276" s="57">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="AB276" s="57">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="AC276" s="57">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="AD276" s="57" t="e">
-        <f>(W276-W10)/W10</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AE276" s="57" t="e">
-        <f>(X276-#REF!)/#REF!</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AF276" s="57" t="e">
-        <f>(Y276-#REF!)/#REF!</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AG276" s="57" t="e">
-        <f>(Z276-#REF!)/#REF!</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="AH276" s="57"/>
+      <c r="W276" s="41"/>
+      <c r="X276" s="41"/>
+      <c r="Y276" s="41"/>
+      <c r="Z276" s="41"/>
+      <c r="AA276" s="41"/>
+      <c r="AB276" s="41"/>
+      <c r="AC276" s="41"/>
+      <c r="AD276" s="41"/>
+      <c r="AE276" s="41"/>
+      <c r="AF276" s="41"/>
+      <c r="AG276" s="41"/>
+      <c r="AH276" s="41"/>
     </row>
     <row r="277" spans="23:34">
       <c r="W277" s="41"/>
@@ -16663,18 +17363,51 @@
       <c r="AH281" s="41"/>
     </row>
     <row r="282" spans="23:34">
-      <c r="W282" s="41"/>
-      <c r="X282" s="41"/>
-      <c r="Y282" s="41"/>
-      <c r="Z282" s="41"/>
-      <c r="AA282" s="41"/>
-      <c r="AB282" s="41"/>
-      <c r="AC282" s="41"/>
-      <c r="AD282" s="41"/>
-      <c r="AE282" s="41"/>
-      <c r="AF282" s="41"/>
-      <c r="AG282" s="41"/>
-      <c r="AH282" s="41"/>
+      <c r="W282" s="55" t="e">
+        <f t="shared" ref="W282:AG282" si="1">(F282-F3)/F3</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="X282" s="55" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Y282" s="55" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Z282" s="55" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AA282" s="55">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="AB282" s="55">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="AC282" s="55">
+        <f t="shared" si="1"/>
+        <v>-1</v>
+      </c>
+      <c r="AD282" s="55" t="e">
+        <f>(W282-W10)/W10</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AE282" s="55" t="e">
+        <f>(X282-#REF!)/#REF!</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AF282" s="55" t="e">
+        <f>(Y282-#REF!)/#REF!</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AG282" s="55" t="e">
+        <f>(Z282-#REF!)/#REF!</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AH282" s="55"/>
     </row>
     <row r="283" spans="23:34">
       <c r="W283" s="41"/>
@@ -19995,51 +20728,18 @@
       <c r="AH519" s="41"/>
     </row>
     <row r="520" spans="23:34">
-      <c r="W520" s="57" t="e">
-        <f t="shared" ref="W520:AG520" si="2">(F520-F276)/F276</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X520" s="57" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y520" s="57" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z520" s="57" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA520" s="57" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB520" s="57" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC520" s="57" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD520" s="57" t="e">
-        <f>(W520-W276)/W276</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE520" s="57" t="e">
-        <f>(X520-X276)/X276</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF520" s="57" t="e">
-        <f>(Y520-Y276)/Y276</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG520" s="57" t="e">
-        <f>(Z520-Z276)/Z276</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH520" s="57"/>
+      <c r="W520" s="41"/>
+      <c r="X520" s="41"/>
+      <c r="Y520" s="41"/>
+      <c r="Z520" s="41"/>
+      <c r="AA520" s="41"/>
+      <c r="AB520" s="41"/>
+      <c r="AC520" s="41"/>
+      <c r="AD520" s="41"/>
+      <c r="AE520" s="41"/>
+      <c r="AF520" s="41"/>
+      <c r="AG520" s="41"/>
+      <c r="AH520" s="41"/>
     </row>
     <row r="521" spans="23:34">
       <c r="W521" s="41"/>
@@ -20112,18 +20812,51 @@
       <c r="AH525" s="41"/>
     </row>
     <row r="526" spans="23:34">
-      <c r="W526" s="41"/>
-      <c r="X526" s="41"/>
-      <c r="Y526" s="41"/>
-      <c r="Z526" s="41"/>
-      <c r="AA526" s="41"/>
-      <c r="AB526" s="41"/>
-      <c r="AC526" s="41"/>
-      <c r="AD526" s="41"/>
-      <c r="AE526" s="41"/>
-      <c r="AF526" s="41"/>
-      <c r="AG526" s="41"/>
-      <c r="AH526" s="41"/>
+      <c r="W526" s="55" t="e">
+        <f t="shared" ref="W526:AG526" si="2">(F526-F282)/F282</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X526" s="55" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y526" s="55" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z526" s="55" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA526" s="55" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB526" s="55" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC526" s="55" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD526" s="55" t="e">
+        <f>(W526-W282)/W282</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE526" s="55" t="e">
+        <f>(X526-X282)/X282</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF526" s="55" t="e">
+        <f>(Y526-Y282)/Y282</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG526" s="55" t="e">
+        <f>(Z526-Z282)/Z282</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH526" s="55"/>
     </row>
     <row r="527" spans="23:34">
       <c r="W527" s="41"/>
@@ -23430,51 +24163,18 @@
       <c r="AH762" s="41"/>
     </row>
     <row r="763" spans="23:34">
-      <c r="W763" s="57" t="e">
-        <f t="shared" ref="W763:AG763" si="3">(F763-F520)/F520</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X763" s="57" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y763" s="57" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z763" s="57" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA763" s="57" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB763" s="57" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC763" s="57" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD763" s="57" t="e">
-        <f>(W763-W520)/W520</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE763" s="57" t="e">
-        <f>(X763-X520)/X520</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF763" s="57" t="e">
-        <f>(Y763-Y520)/Y520</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG763" s="57" t="e">
-        <f>(Z763-Z520)/Z520</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH763" s="57"/>
+      <c r="W763" s="41"/>
+      <c r="X763" s="41"/>
+      <c r="Y763" s="41"/>
+      <c r="Z763" s="41"/>
+      <c r="AA763" s="41"/>
+      <c r="AB763" s="41"/>
+      <c r="AC763" s="41"/>
+      <c r="AD763" s="41"/>
+      <c r="AE763" s="41"/>
+      <c r="AF763" s="41"/>
+      <c r="AG763" s="41"/>
+      <c r="AH763" s="41"/>
     </row>
     <row r="764" spans="23:34">
       <c r="W764" s="41"/>
@@ -23547,18 +24247,51 @@
       <c r="AH768" s="41"/>
     </row>
     <row r="769" spans="23:34">
-      <c r="W769" s="41"/>
-      <c r="X769" s="41"/>
-      <c r="Y769" s="41"/>
-      <c r="Z769" s="41"/>
-      <c r="AA769" s="41"/>
-      <c r="AB769" s="41"/>
-      <c r="AC769" s="41"/>
-      <c r="AD769" s="41"/>
-      <c r="AE769" s="41"/>
-      <c r="AF769" s="41"/>
-      <c r="AG769" s="41"/>
-      <c r="AH769" s="41"/>
+      <c r="W769" s="55" t="e">
+        <f t="shared" ref="W769:AG769" si="3">(F769-F526)/F526</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X769" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y769" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z769" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA769" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB769" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC769" s="55" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD769" s="55" t="e">
+        <f>(W769-W526)/W526</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE769" s="55" t="e">
+        <f>(X769-X526)/X526</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF769" s="55" t="e">
+        <f>(Y769-Y526)/Y526</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG769" s="55" t="e">
+        <f>(Z769-Z526)/Z526</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH769" s="55"/>
     </row>
     <row r="770" spans="23:34">
       <c r="W770" s="41"/>
@@ -26879,51 +27612,18 @@
       <c r="AH1006" s="41"/>
     </row>
     <row r="1007" spans="23:34">
-      <c r="W1007" s="57" t="e">
-        <f t="shared" ref="W1007:AG1007" si="4">(F1007-F763)/F763</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X1007" s="57" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y1007" s="57" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z1007" s="57" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA1007" s="57" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB1007" s="57" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC1007" s="57" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD1007" s="57" t="e">
-        <f>(W1007-W763)/W763</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE1007" s="57" t="e">
-        <f>(X1007-X763)/X763</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF1007" s="57" t="e">
-        <f>(Y1007-Y763)/Y763</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG1007" s="57" t="e">
-        <f>(Z1007-Z763)/Z763</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH1007" s="57"/>
+      <c r="W1007" s="41"/>
+      <c r="X1007" s="41"/>
+      <c r="Y1007" s="41"/>
+      <c r="Z1007" s="41"/>
+      <c r="AA1007" s="41"/>
+      <c r="AB1007" s="41"/>
+      <c r="AC1007" s="41"/>
+      <c r="AD1007" s="41"/>
+      <c r="AE1007" s="41"/>
+      <c r="AF1007" s="41"/>
+      <c r="AG1007" s="41"/>
+      <c r="AH1007" s="41"/>
     </row>
     <row r="1008" spans="23:34">
       <c r="W1008" s="41"/>
@@ -26996,18 +27696,51 @@
       <c r="AH1012" s="41"/>
     </row>
     <row r="1013" spans="23:34">
-      <c r="W1013" s="41"/>
-      <c r="X1013" s="41"/>
-      <c r="Y1013" s="41"/>
-      <c r="Z1013" s="41"/>
-      <c r="AA1013" s="41"/>
-      <c r="AB1013" s="41"/>
-      <c r="AC1013" s="41"/>
-      <c r="AD1013" s="41"/>
-      <c r="AE1013" s="41"/>
-      <c r="AF1013" s="41"/>
-      <c r="AG1013" s="41"/>
-      <c r="AH1013" s="41"/>
+      <c r="W1013" s="55" t="e">
+        <f t="shared" ref="W1013:AG1013" si="4">(F1013-F769)/F769</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X1013" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y1013" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z1013" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA1013" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB1013" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1013" s="55" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD1013" s="55" t="e">
+        <f>(W1013-W769)/W769</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE1013" s="55" t="e">
+        <f>(X1013-X769)/X769</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF1013" s="55" t="e">
+        <f>(Y1013-Y769)/Y769</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG1013" s="55" t="e">
+        <f>(Z1013-Z769)/Z769</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH1013" s="55"/>
     </row>
     <row r="1014" spans="23:34">
       <c r="W1014" s="41"/>
@@ -30314,51 +31047,18 @@
       <c r="AH1249" s="41"/>
     </row>
     <row r="1250" spans="23:34">
-      <c r="W1250" s="57" t="e">
-        <f t="shared" ref="W1250:AG1250" si="5">(F1250-F1007)/F1007</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X1250" s="57" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y1250" s="57" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z1250" s="57" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA1250" s="57" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB1250" s="57" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC1250" s="57" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD1250" s="57" t="e">
-        <f>(W1250-W1007)/W1007</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE1250" s="57" t="e">
-        <f>(X1250-X1007)/X1007</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF1250" s="57" t="e">
-        <f>(Y1250-Y1007)/Y1007</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG1250" s="57" t="e">
-        <f>(Z1250-Z1007)/Z1007</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH1250" s="57"/>
+      <c r="W1250" s="41"/>
+      <c r="X1250" s="41"/>
+      <c r="Y1250" s="41"/>
+      <c r="Z1250" s="41"/>
+      <c r="AA1250" s="41"/>
+      <c r="AB1250" s="41"/>
+      <c r="AC1250" s="41"/>
+      <c r="AD1250" s="41"/>
+      <c r="AE1250" s="41"/>
+      <c r="AF1250" s="41"/>
+      <c r="AG1250" s="41"/>
+      <c r="AH1250" s="41"/>
     </row>
     <row r="1251" spans="23:34">
       <c r="W1251" s="41"/>
@@ -30431,18 +31131,51 @@
       <c r="AH1255" s="41"/>
     </row>
     <row r="1256" spans="23:34">
-      <c r="W1256" s="41"/>
-      <c r="X1256" s="41"/>
-      <c r="Y1256" s="41"/>
-      <c r="Z1256" s="41"/>
-      <c r="AA1256" s="41"/>
-      <c r="AB1256" s="41"/>
-      <c r="AC1256" s="41"/>
-      <c r="AD1256" s="41"/>
-      <c r="AE1256" s="41"/>
-      <c r="AF1256" s="41"/>
-      <c r="AG1256" s="41"/>
-      <c r="AH1256" s="41"/>
+      <c r="W1256" s="55" t="e">
+        <f t="shared" ref="W1256:AG1256" si="5">(F1256-F1013)/F1013</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X1256" s="55" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y1256" s="55" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z1256" s="55" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA1256" s="55" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB1256" s="55" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1256" s="55" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD1256" s="55" t="e">
+        <f>(W1256-W1013)/W1013</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE1256" s="55" t="e">
+        <f>(X1256-X1013)/X1013</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF1256" s="55" t="e">
+        <f>(Y1256-Y1013)/Y1013</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG1256" s="55" t="e">
+        <f>(Z1256-Z1013)/Z1013</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH1256" s="55"/>
     </row>
     <row r="1257" spans="23:34">
       <c r="W1257" s="41"/>
@@ -33749,51 +34482,18 @@
       <c r="AH1492" s="41"/>
     </row>
     <row r="1493" spans="23:34">
-      <c r="W1493" s="57" t="e">
-        <f t="shared" ref="W1493:AG1493" si="6">(F1493-F1250)/F1250</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X1493" s="57" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y1493" s="57" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z1493" s="57" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA1493" s="57" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB1493" s="57" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC1493" s="57" t="e">
-        <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD1493" s="57" t="e">
-        <f>(W1493-W1250)/W1250</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE1493" s="57" t="e">
-        <f>(X1493-X1250)/X1250</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF1493" s="57" t="e">
-        <f>(Y1493-Y1250)/Y1250</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG1493" s="57" t="e">
-        <f>(Z1493-Z1250)/Z1250</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH1493" s="57"/>
+      <c r="W1493" s="41"/>
+      <c r="X1493" s="41"/>
+      <c r="Y1493" s="41"/>
+      <c r="Z1493" s="41"/>
+      <c r="AA1493" s="41"/>
+      <c r="AB1493" s="41"/>
+      <c r="AC1493" s="41"/>
+      <c r="AD1493" s="41"/>
+      <c r="AE1493" s="41"/>
+      <c r="AF1493" s="41"/>
+      <c r="AG1493" s="41"/>
+      <c r="AH1493" s="41"/>
     </row>
     <row r="1494" spans="23:34">
       <c r="W1494" s="41"/>
@@ -33866,18 +34566,51 @@
       <c r="AH1498" s="41"/>
     </row>
     <row r="1499" spans="23:34">
-      <c r="W1499" s="41"/>
-      <c r="X1499" s="41"/>
-      <c r="Y1499" s="41"/>
-      <c r="Z1499" s="41"/>
-      <c r="AA1499" s="41"/>
-      <c r="AB1499" s="41"/>
-      <c r="AC1499" s="41"/>
-      <c r="AD1499" s="41"/>
-      <c r="AE1499" s="41"/>
-      <c r="AF1499" s="41"/>
-      <c r="AG1499" s="41"/>
-      <c r="AH1499" s="41"/>
+      <c r="W1499" s="55" t="e">
+        <f t="shared" ref="W1499:AG1499" si="6">(F1499-F1256)/F1256</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X1499" s="55" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y1499" s="55" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z1499" s="55" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA1499" s="55" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB1499" s="55" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1499" s="55" t="e">
+        <f t="shared" si="6"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD1499" s="55" t="e">
+        <f>(W1499-W1256)/W1256</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE1499" s="55" t="e">
+        <f>(X1499-X1256)/X1256</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF1499" s="55" t="e">
+        <f>(Y1499-Y1256)/Y1256</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG1499" s="55" t="e">
+        <f>(Z1499-Z1256)/Z1256</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH1499" s="55"/>
     </row>
     <row r="1500" spans="23:34">
       <c r="W1500" s="41"/>
@@ -37170,51 +37903,18 @@
       <c r="AH1734" s="41"/>
     </row>
     <row r="1735" spans="23:34">
-      <c r="W1735" s="57" t="e">
-        <f t="shared" ref="W1735:AG1735" si="7">(F1735-F1493)/F1493</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X1735" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y1735" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z1735" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA1735" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB1735" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC1735" s="57" t="e">
-        <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD1735" s="57" t="e">
-        <f>(W1735-W1493)/W1493</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE1735" s="57" t="e">
-        <f>(X1735-X1493)/X1493</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF1735" s="57" t="e">
-        <f>(Y1735-Y1493)/Y1493</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG1735" s="57" t="e">
-        <f>(Z1735-Z1493)/Z1493</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH1735" s="57"/>
+      <c r="W1735" s="41"/>
+      <c r="X1735" s="41"/>
+      <c r="Y1735" s="41"/>
+      <c r="Z1735" s="41"/>
+      <c r="AA1735" s="41"/>
+      <c r="AB1735" s="41"/>
+      <c r="AC1735" s="41"/>
+      <c r="AD1735" s="41"/>
+      <c r="AE1735" s="41"/>
+      <c r="AF1735" s="41"/>
+      <c r="AG1735" s="41"/>
+      <c r="AH1735" s="41"/>
     </row>
     <row r="1736" spans="23:34">
       <c r="W1736" s="41"/>
@@ -37287,18 +37987,51 @@
       <c r="AH1740" s="41"/>
     </row>
     <row r="1741" spans="23:34">
-      <c r="W1741" s="41"/>
-      <c r="X1741" s="41"/>
-      <c r="Y1741" s="41"/>
-      <c r="Z1741" s="41"/>
-      <c r="AA1741" s="41"/>
-      <c r="AB1741" s="41"/>
-      <c r="AC1741" s="41"/>
-      <c r="AD1741" s="41"/>
-      <c r="AE1741" s="41"/>
-      <c r="AF1741" s="41"/>
-      <c r="AG1741" s="41"/>
-      <c r="AH1741" s="41"/>
+      <c r="W1741" s="55" t="e">
+        <f t="shared" ref="W1741:AG1741" si="7">(F1741-F1499)/F1499</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X1741" s="55" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y1741" s="55" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z1741" s="55" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA1741" s="55" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB1741" s="55" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1741" s="55" t="e">
+        <f t="shared" si="7"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD1741" s="55" t="e">
+        <f>(W1741-W1499)/W1499</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE1741" s="55" t="e">
+        <f>(X1741-X1499)/X1499</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF1741" s="55" t="e">
+        <f>(Y1741-Y1499)/Y1499</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG1741" s="55" t="e">
+        <f>(Z1741-Z1499)/Z1499</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH1741" s="55"/>
     </row>
     <row r="1742" spans="23:34">
       <c r="W1742" s="41"/>
@@ -40591,51 +41324,18 @@
       <c r="AH1976" s="41"/>
     </row>
     <row r="1977" spans="23:34">
-      <c r="W1977" s="57" t="e">
-        <f t="shared" ref="W1977:AG1977" si="8">(F1977-F1735)/F1735</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X1977" s="57" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y1977" s="57" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z1977" s="57" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA1977" s="57" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB1977" s="57" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC1977" s="57" t="e">
-        <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD1977" s="57" t="e">
-        <f>(W1977-W1735)/W1735</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE1977" s="57" t="e">
-        <f>(X1977-X1735)/X1735</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF1977" s="57" t="e">
-        <f>(Y1977-Y1735)/Y1735</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG1977" s="57" t="e">
-        <f>(Z1977-Z1735)/Z1735</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH1977" s="57"/>
+      <c r="W1977" s="41"/>
+      <c r="X1977" s="41"/>
+      <c r="Y1977" s="41"/>
+      <c r="Z1977" s="41"/>
+      <c r="AA1977" s="41"/>
+      <c r="AB1977" s="41"/>
+      <c r="AC1977" s="41"/>
+      <c r="AD1977" s="41"/>
+      <c r="AE1977" s="41"/>
+      <c r="AF1977" s="41"/>
+      <c r="AG1977" s="41"/>
+      <c r="AH1977" s="41"/>
     </row>
     <row r="1978" spans="23:34">
       <c r="W1978" s="41"/>
@@ -40708,18 +41408,51 @@
       <c r="AH1982" s="41"/>
     </row>
     <row r="1983" spans="23:34">
-      <c r="W1983" s="41"/>
-      <c r="X1983" s="41"/>
-      <c r="Y1983" s="41"/>
-      <c r="Z1983" s="41"/>
-      <c r="AA1983" s="41"/>
-      <c r="AB1983" s="41"/>
-      <c r="AC1983" s="41"/>
-      <c r="AD1983" s="41"/>
-      <c r="AE1983" s="41"/>
-      <c r="AF1983" s="41"/>
-      <c r="AG1983" s="41"/>
-      <c r="AH1983" s="41"/>
+      <c r="W1983" s="55" t="e">
+        <f t="shared" ref="W1983:AG1983" si="8">(F1983-F1741)/F1741</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X1983" s="55" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y1983" s="55" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z1983" s="55" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA1983" s="55" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB1983" s="55" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC1983" s="55" t="e">
+        <f t="shared" si="8"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD1983" s="55" t="e">
+        <f>(W1983-W1741)/W1741</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE1983" s="55" t="e">
+        <f>(X1983-X1741)/X1741</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF1983" s="55" t="e">
+        <f>(Y1983-Y1741)/Y1741</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG1983" s="55" t="e">
+        <f>(Z1983-Z1741)/Z1741</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH1983" s="55"/>
     </row>
     <row r="1984" spans="23:34">
       <c r="W1984" s="41"/>
@@ -43984,51 +44717,18 @@
       <c r="AH2216" s="41"/>
     </row>
     <row r="2217" spans="23:34">
-      <c r="W2217" s="57" t="e">
-        <f t="shared" ref="W2217:AG2217" si="9">(F2217-F1977)/F1977</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X2217" s="57" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y2217" s="57" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z2217" s="57" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AA2217" s="57" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AB2217" s="57" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC2217" s="57" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AD2217" s="57" t="e">
-        <f>(W2217-W1977)/W1977</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AE2217" s="57" t="e">
-        <f>(X2217-X1977)/X1977</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF2217" s="57" t="e">
-        <f>(Y2217-Y1977)/Y1977</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG2217" s="57" t="e">
-        <f>(Z2217-Z1977)/Z1977</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH2217" s="57"/>
+      <c r="W2217" s="41"/>
+      <c r="X2217" s="41"/>
+      <c r="Y2217" s="41"/>
+      <c r="Z2217" s="41"/>
+      <c r="AA2217" s="41"/>
+      <c r="AB2217" s="41"/>
+      <c r="AC2217" s="41"/>
+      <c r="AD2217" s="41"/>
+      <c r="AE2217" s="41"/>
+      <c r="AF2217" s="41"/>
+      <c r="AG2217" s="41"/>
+      <c r="AH2217" s="41"/>
     </row>
     <row r="2218" spans="23:34">
       <c r="W2218" s="41"/>
@@ -44101,18 +44801,51 @@
       <c r="AH2222" s="41"/>
     </row>
     <row r="2223" spans="23:34">
-      <c r="W2223" s="41"/>
-      <c r="X2223" s="41"/>
-      <c r="Y2223" s="41"/>
-      <c r="Z2223" s="41"/>
-      <c r="AA2223" s="41"/>
-      <c r="AB2223" s="41"/>
-      <c r="AC2223" s="41"/>
-      <c r="AD2223" s="41"/>
-      <c r="AE2223" s="41"/>
-      <c r="AF2223" s="41"/>
-      <c r="AG2223" s="41"/>
-      <c r="AH2223" s="41"/>
+      <c r="W2223" s="55" t="e">
+        <f t="shared" ref="W2223:AG2223" si="9">(F2223-F1983)/F1983</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X2223" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Y2223" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z2223" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AA2223" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AB2223" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC2223" s="55" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AD2223" s="55" t="e">
+        <f>(W2223-W1983)/W1983</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AE2223" s="55" t="e">
+        <f>(X2223-X1983)/X1983</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF2223" s="55" t="e">
+        <f>(Y2223-Y1983)/Y1983</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AG2223" s="55" t="e">
+        <f>(Z2223-Z1983)/Z1983</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AH2223" s="55"/>
     </row>
     <row r="2224" spans="23:34">
       <c r="W2224" s="41"/>
@@ -47391,51 +48124,135 @@
       <c r="AH2457" s="41"/>
     </row>
     <row r="2458" spans="23:34">
-      <c r="W2458" s="57" t="e">
-        <f t="shared" ref="W2458:AG2458" si="10">(F2458-F2217)/F2217</f>
+      <c r="W2458" s="41"/>
+      <c r="X2458" s="41"/>
+      <c r="Y2458" s="41"/>
+      <c r="Z2458" s="41"/>
+      <c r="AA2458" s="41"/>
+      <c r="AB2458" s="41"/>
+      <c r="AC2458" s="41"/>
+      <c r="AD2458" s="41"/>
+      <c r="AE2458" s="41"/>
+      <c r="AF2458" s="41"/>
+      <c r="AG2458" s="41"/>
+      <c r="AH2458" s="41"/>
+    </row>
+    <row r="2459" spans="23:34">
+      <c r="W2459" s="41"/>
+      <c r="X2459" s="41"/>
+      <c r="Y2459" s="41"/>
+      <c r="Z2459" s="41"/>
+      <c r="AA2459" s="41"/>
+      <c r="AB2459" s="41"/>
+      <c r="AC2459" s="41"/>
+      <c r="AD2459" s="41"/>
+      <c r="AE2459" s="41"/>
+      <c r="AF2459" s="41"/>
+      <c r="AG2459" s="41"/>
+      <c r="AH2459" s="41"/>
+    </row>
+    <row r="2460" spans="23:34">
+      <c r="W2460" s="41"/>
+      <c r="X2460" s="41"/>
+      <c r="Y2460" s="41"/>
+      <c r="Z2460" s="41"/>
+      <c r="AA2460" s="41"/>
+      <c r="AB2460" s="41"/>
+      <c r="AC2460" s="41"/>
+      <c r="AD2460" s="41"/>
+      <c r="AE2460" s="41"/>
+      <c r="AF2460" s="41"/>
+      <c r="AG2460" s="41"/>
+      <c r="AH2460" s="41"/>
+    </row>
+    <row r="2461" spans="23:34">
+      <c r="W2461" s="41"/>
+      <c r="X2461" s="41"/>
+      <c r="Y2461" s="41"/>
+      <c r="Z2461" s="41"/>
+      <c r="AA2461" s="41"/>
+      <c r="AB2461" s="41"/>
+      <c r="AC2461" s="41"/>
+      <c r="AD2461" s="41"/>
+      <c r="AE2461" s="41"/>
+      <c r="AF2461" s="41"/>
+      <c r="AG2461" s="41"/>
+      <c r="AH2461" s="41"/>
+    </row>
+    <row r="2462" spans="23:34">
+      <c r="W2462" s="41"/>
+      <c r="X2462" s="41"/>
+      <c r="Y2462" s="41"/>
+      <c r="Z2462" s="41"/>
+      <c r="AA2462" s="41"/>
+      <c r="AB2462" s="41"/>
+      <c r="AC2462" s="41"/>
+      <c r="AD2462" s="41"/>
+      <c r="AE2462" s="41"/>
+      <c r="AF2462" s="41"/>
+      <c r="AG2462" s="41"/>
+      <c r="AH2462" s="41"/>
+    </row>
+    <row r="2463" spans="23:34">
+      <c r="W2463" s="41"/>
+      <c r="X2463" s="41"/>
+      <c r="Y2463" s="41"/>
+      <c r="Z2463" s="41"/>
+      <c r="AA2463" s="41"/>
+      <c r="AB2463" s="41"/>
+      <c r="AC2463" s="41"/>
+      <c r="AD2463" s="41"/>
+      <c r="AE2463" s="41"/>
+      <c r="AF2463" s="41"/>
+      <c r="AG2463" s="41"/>
+      <c r="AH2463" s="41"/>
+    </row>
+    <row r="2464" spans="23:34">
+      <c r="W2464" s="55" t="e">
+        <f t="shared" ref="W2464:AG2464" si="10">(F2464-F2223)/F2223</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X2458" s="57" t="e">
+      <c r="X2464" s="55" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y2458" s="57" t="e">
+      <c r="Y2464" s="55" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z2458" s="57" t="e">
+      <c r="Z2464" s="55" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA2458" s="57" t="e">
+      <c r="AA2464" s="55" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB2458" s="57" t="e">
+      <c r="AB2464" s="55" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC2458" s="57" t="e">
+      <c r="AC2464" s="55" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD2458" s="57" t="e">
-        <f>(W2458-W2217)/W2217</f>
+      <c r="AD2464" s="55" t="e">
+        <f>(W2464-W2223)/W2223</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE2458" s="57" t="e">
-        <f>(X2458-X2217)/X2217</f>
+      <c r="AE2464" s="55" t="e">
+        <f>(X2464-X2223)/X2223</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF2458" s="57" t="e">
-        <f>(Y2458-Y2217)/Y2217</f>
+      <c r="AF2464" s="55" t="e">
+        <f>(Y2464-Y2223)/Y2223</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG2458" s="57" t="e">
-        <f>(Z2458-Z2217)/Z2217</f>
+      <c r="AG2464" s="55" t="e">
+        <f>(Z2464-Z2223)/Z2223</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH2458" s="57"/>
+      <c r="AH2464" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="16">

--- a/主要指数介绍.xlsx
+++ b/主要指数介绍.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="378">
   <si>
     <t>指数简称</t>
   </si>
@@ -1009,10 +1009,7 @@
     <t>（1）剔除过去一年的日均成交金额排名后 20%的证券；（2）再选取业务涉及大数据存储设备、大数据分析技术、大数据运营平台、大数据生产、大数据应用等领域的上市公司证券归为大数据产业主题；（3）再选取过去一年日均总市值排名靠前的 50 只。</t>
   </si>
   <si>
-    <t>2012/20/31</t>
-  </si>
-  <si>
-    <t>中证数字经济</t>
+    <t>数字经济</t>
   </si>
   <si>
     <t>中证数字经济主题指数</t>
@@ -1030,7 +1027,7 @@
     <t>（1）剔除过去一年的日均成交金额排名后 20%的证券；（2）按照中证行业分类，再选取归属于软件开发和信息技术服务行业的上市公司证券；（3）再选取过去一年的日均总市值排名前 30 只。</t>
   </si>
   <si>
-    <t>单 个样本权重不超过 15%，前五大样本权重合计不超过 60%</t>
+    <t>单个样本权重不超过 15%，前五大样本权重合计不超过 60%</t>
   </si>
   <si>
     <t>半导体</t>
@@ -1043,9 +1040,6 @@
   </si>
   <si>
     <t>（1）选取主营业务涉及半导体产品和半导体设备的上市公司证券；（2）再剔除过去一年日均成交金额排名后 10% 的证券;（3）再剔除累积总市值占比后 10% 的证券。</t>
-  </si>
-  <si>
-    <t>单 个样本权重不超过 15%</t>
   </si>
   <si>
     <t xml:space="preserve">中证白酒   </t>
@@ -1072,16 +1066,52 @@
     <t>000949</t>
   </si>
   <si>
+    <t>中证农业主题指数</t>
+  </si>
+  <si>
+    <t>（1）选取业务涉及农产品、农用机械、化肥、农药、畜禽药物等领域的上市公司证券；（2）再选取过去一年日均总市值排名前 50 只。</t>
+  </si>
+  <si>
+    <t>农产品相关的单个样本权重不超过 15%，其它单个样本权重不超过 5%，前五大样本权重合计不超过 60%</t>
+  </si>
+  <si>
     <t xml:space="preserve">中证旅游   </t>
+  </si>
+  <si>
+    <t>中证旅游主题指数</t>
+  </si>
+  <si>
+    <t>（1）选取业务涉及旅游住宿、旅游游览、旅游购物、旅游娱乐、旅游综合服务、旅游出行、旅游餐饮、旅游地产开发等旅游产业链的上市公司证券；（2）再过去一年日均总市值排名前 50 只。</t>
+  </si>
+  <si>
+    <t>单个样本权重不超过 15%，且旅游出行、旅游餐饮、旅游地产开发及旅游相关业务占比较低的样本合计权重不超过 40%，前五大样本合计权重不超过 60%</t>
   </si>
   <si>
     <t xml:space="preserve">养老产业   </t>
   </si>
   <si>
+    <t>中证养老产业指数</t>
+  </si>
+  <si>
+    <t>（1）选取医药卫生、健康食品、休闲旅游、人寿保险、小家电等养老产业相关上市公司证券；（2）再优先选取各中证四级行业中过去一年日均总市值最大的上市公司证券；（3）再选取过去一年日均总市值排名靠前的上市公司证券使得样本数量达到 80 只，且单个中证一级行业样本数量不超过 30 只。</t>
+  </si>
+  <si>
     <t xml:space="preserve">中证中药   </t>
   </si>
   <si>
+    <t>中证中药指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年的日均成交金额，排名后 20% 的证券；（2）再选取涉及中药生产与销售等业务的上市公司证券纳入中药主题；（3）再选取过去一年的日均总市值排名前 50 只。</t>
+  </si>
+  <si>
     <t xml:space="preserve">CS创新药   </t>
+  </si>
+  <si>
+    <t>中证创新药产业指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年的日均成交金额排名后 20%的证券；（2）选取主营业务涉及创新药研发的上市公司证券作为待选样本，包括但不限于研发投入强度高的公司、有创新药品在海外或国内上市的公司以及处于创新药研发产业链的公司；（3）再选取过去一年日均总市值排名靠前的 50 只，不足 50 只时全部纳入。</t>
   </si>
   <si>
     <r>
@@ -1107,31 +1137,97 @@
     <t>中证生物医药指数</t>
   </si>
   <si>
-    <t>细分化工</t>
+    <t>同中证全指指数的样本空间，过去一年日均成交金额位于样本空间内前 80%</t>
   </si>
   <si>
-    <t>000813</t>
+    <t>（1）选取提供细胞医疗、基因测序、血液制品、生物技术药物、疫苗、体外诊断等产品和服务的上市公司证券；（2）再选取过去一年日均总市值排名靠前的 30 只。</t>
+  </si>
+  <si>
+    <t>中证医疗</t>
+  </si>
+  <si>
+    <t>中证医疗指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年的日均成交金额排名后 20%的证券；（2）选取业务涉及医疗器械、医疗服务、医疗信息化等医疗主题的上市公司证券；（3）再选取过去一年日均总市值排名前 50 只，不足 50 只时全部纳入。</t>
+  </si>
+  <si>
+    <t>单个样本权重不超过 10%，前五大样本权重合计不超过 40%</t>
   </si>
   <si>
     <t>中证传媒</t>
   </si>
   <si>
+    <t>中证传媒指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年的日均成交金额排名后 20% 的证券；（2）选取营销与广告、文化娱乐、数字媒体等行业中主营业务与传媒相关的上市公司证券；（3）剔除商誉占净资产比例大于 80% 的证券，第一大股东累计质押比例大于 95% 的证券；（4）再选取过去一年日均总市值排名前 50 只。</t>
+  </si>
+  <si>
     <t xml:space="preserve">中证银行   </t>
+  </si>
+  <si>
+    <t>中证银行指数</t>
+  </si>
+  <si>
+    <t>（1）样本空间证券按中证行业分类划分；（2）行业内证券≤50 只时，全部纳入对应全指行业指数样本；（3）行业内证券＞50 只时，剔除成交金额排名后 10% 及累计市值占比超 98% 后的证券，优先保证剩余数量≥50 只，剩余证券作为行业指数样本。</t>
+  </si>
+  <si>
+    <t>单个样本权重上限 15%</t>
   </si>
   <si>
     <t xml:space="preserve">证券公司   </t>
   </si>
   <si>
+    <t>中证全指证券公司指数</t>
+  </si>
+  <si>
     <t xml:space="preserve">中证军工   </t>
+  </si>
+  <si>
+    <t>中证军工指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年的日均成交金额排名后 20% 的证券；（2）将由十大军工集团控股且主营业务与军工行业相关的上市公司，以及业务范围涵盖航空、航天、船舶、兵器、军事电子和卫星等军工领域的其他军工类上市公司作为待选样本；（3）再选取按照过去一年日均总市值不超过 80 只证券。</t>
+  </si>
+  <si>
+    <t>单个样本权重上限 10%</t>
   </si>
   <si>
     <t xml:space="preserve">中证国防   </t>
   </si>
   <si>
+    <t>中证国防指数</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年的日均成交金额排名后 20% 的证券；（2）将隶属于国防工业系统下的十大集团公司旗下的上市公司证券；十大集团公司以外的为国家武装力量提供武器装备的上市公司证券；与军方有实际的装备承制销售金额或签订合同的相关上市公司证券；（3）再选取过去一年日均总市值前50 只。</t>
+  </si>
+  <si>
     <t xml:space="preserve">港股科技  </t>
   </si>
   <si>
+    <t>中证香港科技指数</t>
+  </si>
+  <si>
+    <t>同中证香港 300 指数样本空间</t>
+  </si>
+  <si>
+    <t>（1）剔除过去一年日均成交金额不足 1000 万港元的证券；（2）选取通信、互联网、医疗器械、生物科技、电子、半导体、新能源等行业的上市公司证券作为科技主题空间；（3）剔除过去两年营业收入增速连续为负以及过去两年研发投入占营业收入的比例不足 3% 的证券，对各中证二级行业中市值排名前三的证券豁免上述要求；（4）再选取过去一年日均总市值排名靠前的 50 只，不足 50 只时，全部纳入。</t>
+  </si>
+  <si>
     <t>港股通高股息</t>
+  </si>
+  <si>
+    <t>中证港股通高股息投资指数</t>
+  </si>
+  <si>
+    <t>中证香港 300 指数样本中符合港股通条件的证券，过去一年日均成交金额不低于 5000 万港元</t>
+  </si>
+  <si>
+    <t>（1）选取过去三年连续分红且过去三年股利支付率的均值和过去一年股利支付率均大于0且小于1的上市公司证券；（2）再选取过去三年平均股息率排名靠前的 30 只。</t>
+  </si>
+  <si>
+    <t>采用股息率加权</t>
   </si>
 </sst>
 </file>
@@ -1801,7 +1897,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1939,6 +2035,12 @@
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2483,15 +2585,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BR2463"/>
+  <dimension ref="A1:BR2462"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.141592920354" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.36283185840708" style="1" customWidth="1"/>
     <col min="3" max="3" width="29.6017699115044" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.36283185840708" style="1" customWidth="1"/>
-    <col min="5" max="5" width="45.070796460177" style="1" customWidth="1"/>
-    <col min="6" max="6" width="57.6902654867257" style="1" customWidth="1"/>
+    <col min="5" max="5" width="36.3628318584071" style="1" customWidth="1"/>
+    <col min="6" max="6" width="73.1681415929203" style="1" customWidth="1"/>
     <col min="7" max="7" width="28.5309734513274" style="1" customWidth="1"/>
     <col min="8" max="8" width="31.7964601769912" style="1" customWidth="1"/>
     <col min="9" max="9" width="34.646017699115" style="1" customWidth="1"/>
@@ -2743,7 +2845,7 @@
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="50" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -2947,7 +3049,7 @@
       <c r="A4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="50" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -3151,7 +3253,7 @@
       <c r="A5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="50" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -3716,7 +3818,7 @@
       <c r="A9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="50" t="s">
         <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -3914,7 +4016,7 @@
       <c r="A10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="50" t="s">
         <v>62</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -4173,11 +4275,11 @@
       <c r="BP11" s="12"/>
       <c r="BQ11" s="12"/>
     </row>
-    <row r="12" ht="54" spans="1:69">
+    <row r="12" ht="67.5" spans="1:69">
       <c r="A12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="50" t="s">
         <v>68</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -4299,7 +4401,7 @@
       <c r="A13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="50" t="s">
         <v>74</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -4427,7 +4529,7 @@
       <c r="A14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="50" t="s">
         <v>79</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -4540,7 +4642,7 @@
       <c r="A15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="50" t="s">
         <v>84</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -4558,7 +4660,7 @@
       <c r="H15" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I15" s="48" t="s">
+      <c r="I15" s="50" t="s">
         <v>51</v>
       </c>
       <c r="J15" s="1">
@@ -4732,7 +4834,7 @@
       <c r="BP16" s="14"/>
       <c r="BQ16" s="14"/>
     </row>
-    <row r="17" s="3" customFormat="1" spans="1:69">
+    <row r="17" s="3" customFormat="1" ht="27" spans="1:69">
       <c r="A17" s="3" t="s">
         <v>89</v>
       </c>
@@ -4983,7 +5085,7 @@
         <v>0.0777</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="27" spans="1:69">
+    <row r="20" s="1" customFormat="1" spans="1:69">
       <c r="A20" s="1" t="s">
         <v>98</v>
       </c>
@@ -5484,7 +5586,7 @@
       <c r="AH23" s="13"/>
       <c r="AI23" s="10"/>
     </row>
-    <row r="24" s="4" customFormat="1" ht="54" spans="1:69">
+    <row r="24" s="4" customFormat="1" ht="40.5" spans="1:69">
       <c r="A24" s="4" t="s">
         <v>110</v>
       </c>
@@ -6281,11 +6383,11 @@
       <c r="BP29" s="14"/>
       <c r="BQ29" s="14"/>
     </row>
-    <row r="30" ht="54" spans="1:69">
+    <row r="30" ht="67.5" spans="1:69">
       <c r="A30" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="50" t="s">
         <v>132</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -6485,7 +6587,7 @@
         <v>0.0846018129869686</v>
       </c>
     </row>
-    <row r="31" ht="54" spans="1:69">
+    <row r="31" ht="67.5" spans="1:69">
       <c r="A31" s="1" t="s">
         <v>139</v>
       </c>
@@ -6638,7 +6740,7 @@
       <c r="BP31" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BQ31" s="49" t="s">
+      <c r="BQ31" s="51" t="s">
         <v>51</v>
       </c>
     </row>
@@ -6646,7 +6748,7 @@
       <c r="A32" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="50" t="s">
         <v>145</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -6850,7 +6952,7 @@
       <c r="A33" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="50" t="s">
         <v>150</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -7202,19 +7304,19 @@
       <c r="BL34" s="12">
         <v>0.0603036102934573</v>
       </c>
-      <c r="BM34" s="49" t="s">
+      <c r="BM34" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="BN34" s="49" t="s">
+      <c r="BN34" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="BO34" s="49" t="s">
+      <c r="BO34" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="BP34" s="49" t="s">
+      <c r="BP34" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="BQ34" s="49" t="s">
+      <c r="BQ34" s="51" t="s">
         <v>51</v>
       </c>
     </row>
@@ -7371,11 +7473,11 @@
       <c r="BP35" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BQ35" s="49" t="s">
+      <c r="BQ35" s="51" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="37" ht="54" spans="1:69">
+    <row r="37" ht="67.5" spans="1:69">
       <c r="A37" s="1" t="s">
         <v>159</v>
       </c>
@@ -7769,7 +7871,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="39" ht="67.5" spans="1:69">
+    <row r="39" ht="54" spans="1:69">
       <c r="A39" s="1" t="s">
         <v>171</v>
       </c>
@@ -7973,7 +8075,7 @@
         <v>0.0983390163708719</v>
       </c>
     </row>
-    <row r="40" ht="81" spans="1:69">
+    <row r="40" ht="67.5" spans="1:69">
       <c r="A40" s="1" t="s">
         <v>175</v>
       </c>
@@ -8126,11 +8228,11 @@
       <c r="BP40" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BQ40" s="49" t="s">
+      <c r="BQ40" s="51" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="41" ht="67.5" spans="1:69">
+    <row r="41" ht="54" spans="1:69">
       <c r="A41" s="1" t="s">
         <v>179</v>
       </c>
@@ -8280,14 +8382,14 @@
       <c r="BO41" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BP41" s="49" t="s">
+      <c r="BP41" s="51" t="s">
         <v>51</v>
       </c>
       <c r="BQ41" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="42" ht="67.5" spans="1:69">
+    <row r="42" ht="54" spans="1:69">
       <c r="A42" s="1" t="s">
         <v>182</v>
       </c>
@@ -8437,14 +8539,14 @@
       <c r="BO42" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BP42" s="49" t="s">
+      <c r="BP42" s="51" t="s">
         <v>51</v>
       </c>
       <c r="BQ42" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="43" ht="94.5" spans="1:69">
+    <row r="43" ht="108" spans="1:69">
       <c r="A43" s="1" t="s">
         <v>185</v>
       </c>
@@ -8573,19 +8675,19 @@
       <c r="BL43" s="11">
         <v>0.0406</v>
       </c>
-      <c r="BM43" s="50" t="s">
+      <c r="BM43" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BN43" s="50" t="s">
+      <c r="BN43" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BO43" s="50" t="s">
+      <c r="BO43" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BP43" s="50" t="s">
+      <c r="BP43" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BQ43" s="50" t="s">
+      <c r="BQ43" s="52" t="s">
         <v>51</v>
       </c>
     </row>
@@ -8632,7 +8734,7 @@
       <c r="BP44" s="14"/>
       <c r="BQ44" s="14"/>
     </row>
-    <row r="45" ht="54" spans="1:69">
+    <row r="45" ht="40.5" spans="1:69">
       <c r="A45" s="1" t="s">
         <v>190</v>
       </c>
@@ -8765,23 +8867,23 @@
       <c r="BL45" s="12">
         <v>0.113823071174797</v>
       </c>
-      <c r="BM45" s="50" t="s">
+      <c r="BM45" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BN45" s="50" t="s">
+      <c r="BN45" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BO45" s="50" t="s">
+      <c r="BO45" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BP45" s="50" t="s">
+      <c r="BP45" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BQ45" s="50" t="s">
+      <c r="BQ45" s="52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="46" ht="54" spans="1:69">
+    <row r="46" ht="40.5" spans="1:69">
       <c r="A46" s="1" t="s">
         <v>196</v>
       </c>
@@ -8914,23 +9016,23 @@
       <c r="BL46" s="12">
         <v>0.0852474573735877</v>
       </c>
-      <c r="BM46" s="50" t="s">
+      <c r="BM46" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BN46" s="50" t="s">
+      <c r="BN46" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BO46" s="50" t="s">
+      <c r="BO46" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BP46" s="50" t="s">
+      <c r="BP46" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BQ46" s="50" t="s">
+      <c r="BQ46" s="52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="47" ht="54" spans="1:69">
+    <row r="47" ht="40.5" spans="1:69">
       <c r="A47" s="1" t="s">
         <v>198</v>
       </c>
@@ -9063,23 +9165,23 @@
       <c r="BL47" s="12">
         <v>0.09350422314173</v>
       </c>
-      <c r="BM47" s="50" t="s">
+      <c r="BM47" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BN47" s="50" t="s">
+      <c r="BN47" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BO47" s="50" t="s">
+      <c r="BO47" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BP47" s="50" t="s">
+      <c r="BP47" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BQ47" s="50" t="s">
+      <c r="BQ47" s="52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="48" ht="54" spans="1:69">
+    <row r="48" ht="40.5" spans="1:69">
       <c r="A48" s="1" t="s">
         <v>200</v>
       </c>
@@ -9212,23 +9314,23 @@
       <c r="BL48" s="12">
         <v>0.0923653113940854</v>
       </c>
-      <c r="BM48" s="50" t="s">
+      <c r="BM48" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BN48" s="50" t="s">
+      <c r="BN48" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BO48" s="50" t="s">
+      <c r="BO48" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BP48" s="50" t="s">
+      <c r="BP48" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BQ48" s="50" t="s">
+      <c r="BQ48" s="52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="49" ht="54" spans="1:69">
+    <row r="49" ht="40.5" spans="1:69">
       <c r="A49" s="1" t="s">
         <v>203</v>
       </c>
@@ -9361,19 +9463,19 @@
       <c r="BL49" s="12">
         <v>0.078742377357387</v>
       </c>
-      <c r="BM49" s="50" t="s">
+      <c r="BM49" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BN49" s="50" t="s">
+      <c r="BN49" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BO49" s="50" t="s">
+      <c r="BO49" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BP49" s="50" t="s">
+      <c r="BP49" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BQ49" s="50" t="s">
+      <c r="BQ49" s="52" t="s">
         <v>51</v>
       </c>
     </row>
@@ -9420,11 +9522,11 @@
       <c r="BP50" s="14"/>
       <c r="BQ50" s="14"/>
     </row>
-    <row r="51" ht="67.5" spans="1:69">
+    <row r="51" ht="81" spans="1:69">
       <c r="A51" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B51" s="48" t="s">
+      <c r="B51" s="50" t="s">
         <v>206</v>
       </c>
       <c r="C51" s="28" t="s">
@@ -9592,18 +9694,18 @@
       <c r="BO51" s="11">
         <v>0.0756</v>
       </c>
-      <c r="BP51" s="50" t="s">
+      <c r="BP51" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BQ51" s="50" t="s">
+      <c r="BQ51" s="52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="52" ht="81" spans="1:69">
+    <row r="52" ht="94.5" spans="1:69">
       <c r="A52" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B52" s="48" t="s">
+      <c r="B52" s="50" t="s">
         <v>211</v>
       </c>
       <c r="C52" s="28" t="s">
@@ -9792,11 +9894,11 @@
       <c r="BP52" s="11">
         <v>0.0756</v>
       </c>
-      <c r="BQ52" s="50" t="s">
+      <c r="BQ52" s="52" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="53" ht="54" spans="1:69">
+    <row r="53" ht="67.5" spans="1:69">
       <c r="A53" s="1" t="s">
         <v>215</v>
       </c>
@@ -9925,16 +10027,16 @@
       <c r="BL53" s="11">
         <v>0.0104</v>
       </c>
-      <c r="BM53" s="50" t="s">
+      <c r="BM53" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BN53" s="50" t="s">
+      <c r="BN53" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BO53" s="50" t="s">
+      <c r="BO53" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="BP53" s="50" t="s">
+      <c r="BP53" s="52" t="s">
         <v>51</v>
       </c>
       <c r="BQ53" s="14"/>
@@ -10181,7 +10283,7 @@
       <c r="A56" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="B56" s="51" t="s">
+      <c r="B56" s="53" t="s">
         <v>225</v>
       </c>
       <c r="C56" s="7" t="s">
@@ -10385,7 +10487,7 @@
       <c r="A57" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="B57" s="51" t="s">
+      <c r="B57" s="53" t="s">
         <v>230</v>
       </c>
       <c r="C57" s="7" t="s">
@@ -10589,7 +10691,7 @@
       <c r="A58" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B58" s="51" t="s">
+      <c r="B58" s="53" t="s">
         <v>233</v>
       </c>
       <c r="C58" s="7" t="s">
@@ -10793,7 +10895,7 @@
       <c r="A59" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="B59" s="51" t="s">
+      <c r="B59" s="53" t="s">
         <v>236</v>
       </c>
       <c r="C59" s="7" t="s">
@@ -10997,7 +11099,7 @@
       <c r="A60" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="B60" s="51" t="s">
+      <c r="B60" s="53" t="s">
         <v>239</v>
       </c>
       <c r="C60" s="7" t="s">
@@ -11201,7 +11303,7 @@
       <c r="A61" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="B61" s="51" t="s">
+      <c r="B61" s="53" t="s">
         <v>242</v>
       </c>
       <c r="C61" s="7" t="s">
@@ -11405,7 +11507,7 @@
       <c r="A62" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B62" s="51" t="s">
+      <c r="B62" s="53" t="s">
         <v>245</v>
       </c>
       <c r="C62" s="7" t="s">
@@ -11733,7 +11835,7 @@
       <c r="AR63" s="11">
         <v>0.2647</v>
       </c>
-      <c r="AS63" s="48" t="s">
+      <c r="AS63" s="50" t="s">
         <v>51</v>
       </c>
       <c r="AT63" s="11">
@@ -11811,7 +11913,7 @@
       <c r="A64" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="B64" s="51" t="s">
+      <c r="B64" s="53" t="s">
         <v>250</v>
       </c>
       <c r="C64" s="7" t="s">
@@ -12015,7 +12117,7 @@
       <c r="A65" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="B65" s="51" t="s">
+      <c r="B65" s="53" t="s">
         <v>253</v>
       </c>
       <c r="C65" s="7" t="s">
@@ -12219,7 +12321,7 @@
       <c r="A66" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B66" s="51" t="s">
+      <c r="B66" s="53" t="s">
         <v>256</v>
       </c>
       <c r="C66" s="7" t="s">
@@ -12466,7 +12568,7 @@
       <c r="A68" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B68" s="48" t="s">
+      <c r="B68" s="50" t="s">
         <v>259</v>
       </c>
       <c r="C68" s="28" t="s">
@@ -12679,11 +12781,11 @@
       <c r="AG69" s="37"/>
       <c r="AH69" s="37"/>
     </row>
-    <row r="70" ht="40.5" spans="1:69">
+    <row r="70" ht="27" spans="1:69">
       <c r="A70" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="B70" s="52" t="s">
+      <c r="B70" s="54" t="s">
         <v>264</v>
       </c>
       <c r="C70" s="28" t="s">
@@ -12881,11 +12983,11 @@
         <v>0.1123</v>
       </c>
     </row>
-    <row r="71" ht="67.5" spans="1:69">
+    <row r="71" ht="54" spans="1:69">
       <c r="A71" s="38" t="s">
         <v>268</v>
       </c>
-      <c r="B71" s="52" t="s">
+      <c r="B71" s="54" t="s">
         <v>269</v>
       </c>
       <c r="C71" s="28" t="s">
@@ -13083,7 +13185,7 @@
         <v>0.0955</v>
       </c>
     </row>
-    <row r="72" ht="81" spans="1:69">
+    <row r="72" ht="67.5" spans="1:69">
       <c r="A72" s="38" t="s">
         <v>273</v>
       </c>
@@ -13261,7 +13363,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="73" ht="81" spans="1:69">
+    <row r="73" ht="67.5" spans="1:69">
       <c r="A73" s="38" t="s">
         <v>278</v>
       </c>
@@ -13645,7 +13747,7 @@
       <c r="BP75" s="14"/>
       <c r="BQ75" s="14"/>
     </row>
-    <row r="76" s="1" customFormat="1" ht="54" spans="1:69">
+    <row r="76" s="1" customFormat="1" ht="40.5" spans="1:69">
       <c r="A76" s="38" t="s">
         <v>286</v>
       </c>
@@ -13812,7 +13914,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="77" s="1" customFormat="1" ht="81" spans="1:69">
+    <row r="77" s="1" customFormat="1" ht="54" spans="1:69">
       <c r="A77" s="38" t="s">
         <v>289</v>
       </c>
@@ -13974,7 +14076,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" s="1" customFormat="1" ht="81" spans="1:69">
+    <row r="78" s="1" customFormat="1" ht="67.5" spans="1:69">
       <c r="A78" s="38" t="s">
         <v>292</v>
       </c>
@@ -14137,7 +14239,7 @@
         <v>0.044018291518692</v>
       </c>
     </row>
-    <row r="79" s="1" customFormat="1" ht="40.5" spans="1:69">
+    <row r="79" s="1" customFormat="1" ht="27" spans="1:69">
       <c r="A79" s="28" t="s">
         <v>296</v>
       </c>
@@ -14339,11 +14441,11 @@
         <v>0.104585434484066</v>
       </c>
     </row>
-    <row r="80" s="1" customFormat="1" ht="121.5" spans="1:69">
+    <row r="80" s="1" customFormat="1" ht="94.5" spans="1:69">
       <c r="A80" s="38" t="s">
         <v>299</v>
       </c>
-      <c r="B80" s="52" t="s">
+      <c r="B80" s="54" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="1" t="s">
@@ -14552,7 +14654,7 @@
       <c r="BP81" s="14"/>
       <c r="BQ81" s="14"/>
     </row>
-    <row r="82" ht="175.5" spans="1:70">
+    <row r="82" ht="121.5" spans="1:70">
       <c r="A82" s="38" t="s">
         <v>303</v>
       </c>
@@ -14725,8 +14827,8 @@
       <c r="J83" s="1">
         <v>1000</v>
       </c>
-      <c r="K83" s="5" t="s">
-        <v>310</v>
+      <c r="K83" s="5">
+        <v>41274</v>
       </c>
       <c r="L83" s="5">
         <v>42661</v>
@@ -14849,15 +14951,15 @@
       </c>
       <c r="BR83" s="14"/>
     </row>
-    <row r="84" ht="67.5" spans="1:70">
+    <row r="84" ht="54" spans="1:70">
       <c r="A84" s="38" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B84" s="38">
         <v>931582</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D84" s="1">
         <v>50</v>
@@ -14866,7 +14968,7 @@
         <v>167</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>32</v>
@@ -14983,13 +15085,13 @@
     </row>
     <row r="85" ht="40.5" spans="1:70">
       <c r="A85" s="38" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B85" s="38">
         <v>930601</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D85" s="1">
         <v>30</v>
@@ -14998,13 +15100,13 @@
         <v>167</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H85" s="42" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>262</v>
@@ -15183,15 +15285,15 @@
         <v>0.091498698746413</v>
       </c>
     </row>
-    <row r="86" ht="40.5" spans="1:70">
+    <row r="86" ht="27" spans="1:70">
       <c r="A86" s="28" t="s">
+        <v>317</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="28" t="s">
         <v>319</v>
-      </c>
-      <c r="C86" s="28" t="s">
-        <v>320</v>
       </c>
       <c r="D86" s="1">
         <v>86</v>
@@ -15200,13 +15302,13 @@
         <v>167</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H86" s="42" t="s">
-        <v>322</v>
+        <v>33</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>262</v>
@@ -15402,15 +15504,15 @@
       <c r="AG87" s="37"/>
       <c r="AH87" s="37"/>
     </row>
-    <row r="88" ht="40.5" spans="1:70">
+    <row r="88" ht="27" spans="1:70">
       <c r="A88" s="38" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B88" s="38">
         <v>399997</v>
       </c>
       <c r="C88" s="43" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D88" s="1">
         <v>18</v>
@@ -15419,13 +15521,13 @@
         <v>167</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H88" s="42" t="s">
-        <v>322</v>
+        <v>33</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>262</v>
@@ -15580,15 +15682,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" ht="67.5" spans="1:70">
+    <row r="89" ht="54" spans="1:70">
       <c r="A89" s="38" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B89" s="38">
         <v>930697</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D89" s="1">
         <v>69</v>
@@ -15597,13 +15699,13 @@
         <v>167</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>32</v>
       </c>
       <c r="H89" s="42" t="s">
-        <v>322</v>
+        <v>33</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>262</v>
@@ -15782,14 +15884,43 @@
         <v>0.129035894389747</v>
       </c>
     </row>
-    <row r="90" ht="15.75" spans="1:70">
+    <row r="90" ht="40.5" spans="1:70">
       <c r="A90" s="38" t="s">
+        <v>327</v>
+      </c>
+      <c r="B90" s="54" t="s">
+        <v>328</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="B90" s="52" t="s">
+      <c r="D90" s="1">
+        <v>50</v>
+      </c>
+      <c r="E90" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="K90" s="10"/>
+      <c r="G90" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H90" s="42" t="s">
+        <v>331</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J90" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K90" s="36">
+        <v>38352</v>
+      </c>
+      <c r="L90" s="5">
+        <v>40114</v>
+      </c>
       <c r="M90" s="11">
         <v>-0.0614</v>
       </c>
@@ -15955,14 +16086,43 @@
         <v>0.087218714943015</v>
       </c>
     </row>
-    <row r="91" ht="15.75" spans="1:70">
+    <row r="91" ht="67.5" spans="1:70">
       <c r="A91" s="38" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B91" s="38">
         <v>930633</v>
       </c>
-      <c r="K91" s="10"/>
+      <c r="C91" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D91" s="1">
+        <v>41</v>
+      </c>
+      <c r="E91" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H91" s="42" t="s">
+        <v>335</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J91" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K91" s="36">
+        <v>39813</v>
+      </c>
+      <c r="L91" s="5">
+        <v>42132</v>
+      </c>
       <c r="Q91" s="11">
         <v>1.1884</v>
       </c>
@@ -16104,14 +16264,43 @@
         <v>51</v>
       </c>
     </row>
-    <row r="92" ht="15.75" spans="1:70">
+    <row r="92" ht="54" spans="1:70">
       <c r="A92" s="38" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B92" s="38">
         <v>399812</v>
       </c>
-      <c r="K92" s="10"/>
+      <c r="C92" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D92" s="1">
+        <v>79</v>
+      </c>
+      <c r="E92" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H92" t="s">
+        <v>272</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J92" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K92" s="36">
+        <v>38352</v>
+      </c>
+      <c r="L92" s="5">
+        <v>41796</v>
+      </c>
       <c r="M92" s="11">
         <v>-0.1262</v>
       </c>
@@ -16294,15 +16483,42 @@
       <c r="AG93" s="37"/>
       <c r="AH93" s="37"/>
     </row>
-    <row r="94" ht="15.75" spans="1:70">
+    <row r="94" ht="40.5" spans="1:70">
       <c r="A94" s="38" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B94" s="38">
         <v>930641</v>
       </c>
+      <c r="C94" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="D94" s="1">
+        <v>41</v>
+      </c>
+      <c r="E94" t="s">
+        <v>167</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H94" t="s">
+        <v>40</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J94" s="1">
+        <v>1000</v>
+      </c>
       <c r="K94" s="34">
         <v>38352</v>
+      </c>
+      <c r="L94" s="5">
+        <v>42143</v>
       </c>
       <c r="M94" s="44">
         <v>-0.0552</v>
@@ -16469,15 +16685,42 @@
         <v>0.113244694548857</v>
       </c>
     </row>
-    <row r="95" ht="15.75" spans="1:70">
+    <row r="95" ht="54" spans="1:70">
       <c r="A95" s="38" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="B95" s="38">
         <v>931152</v>
       </c>
+      <c r="C95" s="43" t="s">
+        <v>343</v>
+      </c>
+      <c r="D95" s="1">
+        <v>49</v>
+      </c>
+      <c r="E95" t="s">
+        <v>167</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H95" t="s">
+        <v>40</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J95" s="1">
+        <v>1000</v>
+      </c>
       <c r="K95" s="34">
         <v>42004</v>
+      </c>
+      <c r="L95" s="5">
+        <v>43577</v>
       </c>
       <c r="W95" s="44">
         <v>0.4756</v>
@@ -16584,18 +16827,42 @@
         <v>51</v>
       </c>
     </row>
-    <row r="96" ht="15.75" spans="1:70">
+    <row r="96" ht="27" spans="1:70">
       <c r="A96" s="28" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B96" s="38">
         <v>930726</v>
       </c>
       <c r="C96" s="29" t="s">
-        <v>336</v>
+        <v>346</v>
+      </c>
+      <c r="D96" s="1">
+        <v>30</v>
+      </c>
+      <c r="E96" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H96" s="42" t="s">
+        <v>316</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J96" s="1">
+        <v>1000</v>
       </c>
       <c r="K96" s="34">
         <v>41089</v>
+      </c>
+      <c r="L96" s="5">
+        <v>42221</v>
       </c>
       <c r="U96" s="44">
         <v>0.6141</v>
@@ -16717,185 +16984,245 @@
         <v>51</v>
       </c>
     </row>
-    <row r="97" ht="15.75" spans="1:69">
-      <c r="A97" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="B97" s="48" t="s">
-        <v>338</v>
+    <row r="97" ht="40.5" spans="1:69">
+      <c r="A97" s="38" t="s">
+        <v>349</v>
+      </c>
+      <c r="B97" s="38">
+        <v>399989</v>
+      </c>
+      <c r="C97" s="43" t="s">
+        <v>350</v>
+      </c>
+      <c r="D97" s="1">
+        <v>50</v>
+      </c>
+      <c r="E97" t="s">
+        <v>167</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H97" s="42" t="s">
+        <v>352</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J97" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K97" s="5">
+        <v>38352</v>
+      </c>
+      <c r="L97" s="5">
+        <v>41943</v>
       </c>
       <c r="M97" s="44">
-        <v>-0.048</v>
+        <v>-0.1315</v>
       </c>
       <c r="N97" s="44">
-        <v>0.892</v>
+        <v>0.4876</v>
       </c>
       <c r="O97" s="44">
-        <v>1.9447</v>
+        <v>1.2263</v>
       </c>
       <c r="P97" s="44">
-        <v>-0.6334</v>
+        <v>-0.4712</v>
       </c>
       <c r="Q97" s="44">
-        <v>0.9352</v>
+        <v>1.3395</v>
       </c>
       <c r="R97" s="44">
-        <v>-0.0077</v>
+        <v>0.29</v>
       </c>
       <c r="S97" s="44">
-        <v>-0.3577</v>
+        <v>-0.302</v>
       </c>
       <c r="T97" s="44">
-        <v>-0.0866</v>
+        <v>-0.0766</v>
       </c>
       <c r="U97" s="44">
-        <v>0.0118</v>
+        <v>0.776</v>
       </c>
       <c r="V97" s="44">
-        <v>0.1992</v>
+        <v>0.2051</v>
       </c>
       <c r="W97" s="44">
-        <v>0.493</v>
+        <v>0.6766</v>
       </c>
       <c r="X97" s="44">
-        <v>-0.1583</v>
+        <v>-0.2439</v>
       </c>
       <c r="Y97" s="44">
-        <v>0.0576</v>
+        <v>-0.1352</v>
       </c>
       <c r="Z97" s="44">
-        <v>-0.3551</v>
+        <v>-0.1179</v>
       </c>
       <c r="AA97" s="44">
-        <v>0.251</v>
+        <v>0.4867</v>
       </c>
       <c r="AB97" s="44">
-        <v>0.5168</v>
+        <v>0.7967</v>
       </c>
       <c r="AC97" s="44">
-        <v>0.1572</v>
+        <v>-0.1471</v>
       </c>
       <c r="AD97" s="44">
-        <v>-0.2689</v>
+        <v>-0.251</v>
       </c>
       <c r="AE97" s="44">
-        <v>-0.2317</v>
+        <v>-0.2425</v>
       </c>
       <c r="AF97" s="44">
-        <v>-0.0383</v>
+        <v>-0.1716</v>
       </c>
       <c r="AG97" s="44">
-        <v>0.4109</v>
-      </c>
+        <v>0.0308</v>
+      </c>
+      <c r="AH97" s="37"/>
       <c r="AI97" s="6">
         <f>SUM(M97:AG97)/21</f>
-        <v>0.175414285714286</v>
+        <v>0.191657142857143</v>
       </c>
       <c r="AK97" s="44">
-        <v>0.2589</v>
+        <v>0.2659</v>
       </c>
       <c r="AL97" s="44">
-        <v>0.2261</v>
+        <v>0.3452</v>
       </c>
       <c r="AM97" s="44">
-        <v>0.3867</v>
+        <v>0.4777</v>
       </c>
       <c r="AN97" s="44">
-        <v>0.4559</v>
+        <v>0.579</v>
       </c>
       <c r="AO97" s="44">
-        <v>0.382</v>
+        <v>0.3599</v>
       </c>
       <c r="AP97" s="44">
-        <v>0.312</v>
+        <v>0.3207</v>
       </c>
       <c r="AQ97" s="44">
-        <v>0.2749</v>
+        <v>0.2358</v>
       </c>
       <c r="AR97" s="44">
-        <v>0.2646</v>
+        <v>0.2548</v>
       </c>
       <c r="AS97" s="44">
-        <v>0.2319</v>
+        <v>0.3026</v>
       </c>
       <c r="AT97" s="44">
-        <v>0.1829</v>
+        <v>0.2383</v>
       </c>
       <c r="AU97" s="44">
-        <v>0.4476</v>
+        <v>0.5057</v>
       </c>
       <c r="AV97" s="44">
-        <v>0.2824</v>
+        <v>0.3243</v>
       </c>
       <c r="AW97" s="44">
-        <v>0.153</v>
+        <v>0.174</v>
       </c>
       <c r="AX97" s="44">
-        <v>0.2383</v>
+        <v>0.299</v>
       </c>
       <c r="AY97" s="44">
-        <v>0.2484</v>
+        <v>0.2434</v>
       </c>
       <c r="AZ97" s="44">
-        <v>0.2697</v>
+        <v>0.3072</v>
       </c>
       <c r="BA97" s="44">
-        <v>0.2913</v>
+        <v>0.3347</v>
       </c>
       <c r="BB97" s="44">
-        <v>0.2553</v>
+        <v>0.3087</v>
       </c>
       <c r="BC97" s="44">
-        <v>0.1559</v>
+        <v>0.1999</v>
       </c>
       <c r="BD97" s="44">
-        <v>0.2652</v>
+        <v>0.3481</v>
       </c>
       <c r="BE97" s="44">
-        <v>0.2086</v>
+        <v>0.2162</v>
       </c>
       <c r="BG97" s="45">
-        <v>0.410947954289774</v>
+        <v>0.0307750719325186</v>
       </c>
       <c r="BH97" s="45">
-        <v>0.0139729253826917</v>
+        <v>-0.135173002244907</v>
       </c>
       <c r="BI97" s="45">
-        <v>-0.0247899379086938</v>
+        <v>-0.162008200944188</v>
       </c>
       <c r="BJ97" s="45">
-        <v>0.0763577321717719</v>
+        <v>0.0142070226121631</v>
       </c>
       <c r="BK97" s="45">
-        <v>0.0148123105134477</v>
+        <v>-0.0189221375712399</v>
       </c>
       <c r="BL97" s="45">
-        <v>0.0333419871217899</v>
+        <v>0.00595679394189608</v>
       </c>
       <c r="BM97" s="45">
-        <v>0.0435432967109244</v>
+        <v>0.0656196888361051</v>
       </c>
       <c r="BN97" s="45">
-        <v>0.00138896047960491</v>
+        <v>0.0261387787808975</v>
       </c>
       <c r="BO97" s="45">
-        <v>0.0403979413885471</v>
+        <v>0.0917062428539528</v>
       </c>
       <c r="BP97" s="45">
-        <v>0.0402540465804782</v>
+        <v>0.0910041280336145</v>
       </c>
       <c r="BQ97" s="45">
-        <v>0.0658052445962278</v>
-      </c>
-    </row>
-    <row r="98" ht="15.75" spans="1:69">
+        <v>0.0952706620238624</v>
+      </c>
+    </row>
+    <row r="98" ht="54" spans="1:69">
       <c r="A98" s="38" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B98" s="38">
         <v>399971</v>
       </c>
-      <c r="K98" s="10"/>
+      <c r="C98" s="47" t="s">
+        <v>354</v>
+      </c>
+      <c r="D98" s="1">
+        <v>50</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H98" s="42" t="s">
+        <v>352</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J98" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K98" s="36">
+        <v>40543</v>
+      </c>
+      <c r="L98" s="5">
+        <v>41744</v>
+      </c>
       <c r="T98" s="44">
         <v>-0.0257</v>
       </c>
@@ -17018,7 +17345,7 @@
       <c r="BP98" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="BQ98" s="53" t="s">
+      <c r="BQ98" s="55" t="s">
         <v>51</v>
       </c>
     </row>
@@ -17039,14 +17366,43 @@
       <c r="AG99" s="37"/>
       <c r="AH99" s="37"/>
     </row>
-    <row r="100" ht="15.75" spans="1:69">
+    <row r="100" ht="54" spans="1:69">
       <c r="A100" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="B100" s="38">
         <v>399986</v>
       </c>
-      <c r="K100" s="10"/>
+      <c r="C100" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D100" s="1">
+        <v>42</v>
+      </c>
+      <c r="E100" t="s">
+        <v>167</v>
+      </c>
+      <c r="F100" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H100" t="s">
+        <v>359</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J100" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K100" s="36">
+        <v>38352</v>
+      </c>
+      <c r="L100" s="5">
+        <v>41470</v>
+      </c>
       <c r="M100" s="11">
         <v>0.2056</v>
       </c>
@@ -17212,14 +17568,43 @@
         <v>0.101418033805068</v>
       </c>
     </row>
-    <row r="101" ht="15.75" spans="1:69">
+    <row r="101" ht="54" spans="1:69">
       <c r="A101" s="38" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="B101" s="38">
         <v>399975</v>
       </c>
-      <c r="K101" s="10"/>
+      <c r="C101" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D101" s="1">
+        <v>49</v>
+      </c>
+      <c r="E101" t="s">
+        <v>167</v>
+      </c>
+      <c r="F101" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H101" t="s">
+        <v>359</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J101" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K101" s="36">
+        <v>39262</v>
+      </c>
+      <c r="L101" s="5">
+        <v>41470</v>
+      </c>
       <c r="P101" s="11">
         <v>-0.6222</v>
       </c>
@@ -17361,14 +17746,43 @@
         <v>0.0185921981199078</v>
       </c>
     </row>
-    <row r="102" ht="15.75" spans="1:69">
+    <row r="102" ht="54" spans="1:69">
       <c r="A102" s="38" t="s">
-        <v>342</v>
+        <v>362</v>
       </c>
       <c r="B102" s="38">
         <v>399967</v>
       </c>
-      <c r="K102" s="10"/>
+      <c r="C102" s="43" t="s">
+        <v>363</v>
+      </c>
+      <c r="D102" s="1">
+        <v>80</v>
+      </c>
+      <c r="E102" t="s">
+        <v>167</v>
+      </c>
+      <c r="F102" s="42" t="s">
+        <v>364</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H102" t="s">
+        <v>365</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J102" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K102" s="36">
+        <v>38352</v>
+      </c>
+      <c r="L102" s="5">
+        <v>41634</v>
+      </c>
       <c r="M102" s="11">
         <v>0.0883</v>
       </c>
@@ -17534,14 +17948,43 @@
         <v>0.133950181562191</v>
       </c>
     </row>
-    <row r="103" ht="15.75" spans="1:69">
+    <row r="103" ht="54" spans="1:69">
       <c r="A103" s="38" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="B103" s="38">
         <v>399973</v>
       </c>
-      <c r="K103" s="10"/>
+      <c r="C103" s="43" t="s">
+        <v>367</v>
+      </c>
+      <c r="D103" s="1">
+        <v>50</v>
+      </c>
+      <c r="E103" t="s">
+        <v>167</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H103" t="s">
+        <v>365</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J103" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K103" s="36">
+        <v>40724</v>
+      </c>
+      <c r="L103" s="5">
+        <v>41744</v>
+      </c>
       <c r="T103" s="11">
         <v>-0.0728</v>
       </c>
@@ -17668,14 +18111,43 @@
         <v>51</v>
       </c>
     </row>
-    <row r="104" ht="15.75" spans="1:69">
+    <row r="104" ht="67.5" spans="1:69">
       <c r="A104" s="38" t="s">
-        <v>344</v>
+        <v>369</v>
       </c>
       <c r="B104" s="38">
         <v>931574</v>
       </c>
-      <c r="K104" s="10"/>
+      <c r="C104" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="D104" s="1">
+        <v>50</v>
+      </c>
+      <c r="E104" t="s">
+        <v>371</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H104" t="s">
+        <v>365</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J104" s="1">
+        <v>1000</v>
+      </c>
+      <c r="K104" s="36">
+        <v>42004</v>
+      </c>
+      <c r="L104" s="5">
+        <v>41415</v>
+      </c>
       <c r="W104" s="11">
         <v>0.0488</v>
       </c>
@@ -17796,149 +18268,187 @@
       <c r="AG105" s="37"/>
       <c r="AH105" s="37"/>
     </row>
-    <row r="106" ht="15.75" spans="1:69">
+    <row r="106" s="1" customFormat="1" ht="40.5" spans="1:69">
       <c r="A106" s="35" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="B106" s="38">
         <v>930914</v>
       </c>
-      <c r="W106" s="44">
+      <c r="C106" s="48" t="s">
+        <v>374</v>
+      </c>
+      <c r="D106" s="1">
+        <v>30</v>
+      </c>
+      <c r="E106" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="H106" t="s">
+        <v>365</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J106" s="1">
+        <v>3000</v>
+      </c>
+      <c r="K106" s="5">
+        <v>41957</v>
+      </c>
+      <c r="L106" s="5">
+        <v>42699</v>
+      </c>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5"/>
+      <c r="P106" s="5"/>
+      <c r="Q106" s="5"/>
+      <c r="R106" s="5"/>
+      <c r="S106" s="5"/>
+      <c r="T106" s="5"/>
+      <c r="U106" s="5"/>
+      <c r="V106" s="5"/>
+      <c r="W106" s="11">
         <v>-0.081</v>
       </c>
-      <c r="X106" s="44">
+      <c r="X106" s="11">
         <v>0.0157</v>
       </c>
-      <c r="Y106" s="44">
+      <c r="Y106" s="11">
         <v>0.738</v>
       </c>
-      <c r="Z106" s="44">
+      <c r="Z106" s="11">
         <v>-0.1556</v>
       </c>
-      <c r="AA106" s="44">
+      <c r="AA106" s="11">
         <v>0.0979</v>
       </c>
-      <c r="AB106" s="44">
+      <c r="AB106" s="11">
         <v>-0.1524</v>
       </c>
-      <c r="AC106" s="44">
+      <c r="AC106" s="11">
         <v>-0.0495</v>
       </c>
-      <c r="AD106" s="44">
+      <c r="AD106" s="11">
         <v>-0.0656</v>
       </c>
-      <c r="AE106" s="44">
+      <c r="AE106" s="11">
         <v>-0.0213</v>
       </c>
-      <c r="AF106" s="44">
+      <c r="AF106" s="11">
         <v>0.2254</v>
       </c>
-      <c r="AG106" s="44">
+      <c r="AG106" s="11">
         <v>0.1588</v>
       </c>
-      <c r="AH106" s="44"/>
+      <c r="AH106" s="11"/>
       <c r="AI106" s="6">
         <f>SUM(W106:AG106)/11</f>
         <v>0.0645818181818182</v>
       </c>
-      <c r="AU106" s="44">
+      <c r="AU106" s="11">
         <v>0.7113</v>
       </c>
-      <c r="AV106" s="44">
+      <c r="AV106" s="11">
         <v>1.8649</v>
       </c>
-      <c r="AW106" s="44">
+      <c r="AW106" s="11">
         <v>2.0973</v>
       </c>
-      <c r="AX106" s="44">
+      <c r="AX106" s="11">
         <v>1.7294</v>
       </c>
-      <c r="AY106" s="44">
+      <c r="AY106" s="11">
         <v>2.4846</v>
       </c>
-      <c r="AZ106" s="44">
+      <c r="AZ106" s="11">
         <v>2.726</v>
       </c>
-      <c r="BA106" s="44">
+      <c r="BA106" s="11">
         <v>1.1191</v>
       </c>
-      <c r="BB106" s="44">
+      <c r="BB106" s="11">
         <v>2.1355</v>
       </c>
-      <c r="BC106" s="44">
+      <c r="BC106" s="11">
         <v>3.0811</v>
       </c>
-      <c r="BD106" s="44">
+      <c r="BD106" s="11">
         <v>3.4425</v>
       </c>
-      <c r="BE106" s="44">
+      <c r="BE106" s="11">
         <v>3.4258</v>
       </c>
-      <c r="BG106" s="45">
+      <c r="BG106" s="12">
         <v>0.106838665195262</v>
       </c>
-      <c r="BH106" s="45">
+      <c r="BH106" s="12">
         <v>0.118524922165984</v>
       </c>
-      <c r="BI106" s="45">
+      <c r="BI106" s="12">
         <v>0.0563465358010211</v>
       </c>
-      <c r="BJ106" s="45">
+      <c r="BJ106" s="12">
         <v>0.0232250895565205</v>
       </c>
-      <c r="BK106" s="45">
+      <c r="BK106" s="12">
         <v>0.0599721545605574</v>
       </c>
-      <c r="BL106" s="45">
+      <c r="BL106" s="12">
         <v>0.0531591816406556</v>
       </c>
-      <c r="BM106" s="46" t="s">
+      <c r="BM106" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BN106" s="46" t="s">
+      <c r="BN106" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BO106" s="46" t="s">
+      <c r="BO106" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BP106" s="46" t="s">
+      <c r="BP106" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="BQ106" s="46" t="s">
+      <c r="BQ106" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:69">
-      <c r="A107" s="38"/>
-      <c r="B107" s="38"/>
-      <c r="W107" s="37"/>
-      <c r="X107" s="37"/>
-      <c r="Y107" s="37"/>
-      <c r="Z107" s="37"/>
-      <c r="AA107" s="37"/>
-      <c r="AB107" s="37"/>
-      <c r="AC107" s="37"/>
-      <c r="AD107" s="37"/>
-      <c r="AE107" s="37"/>
-      <c r="AF107" s="37"/>
-      <c r="AG107" s="37"/>
-      <c r="AH107" s="37"/>
-    </row>
-    <row r="112" spans="1:69">
-      <c r="A112" s="38"/>
-      <c r="B112" s="38"/>
-      <c r="W112" s="37"/>
-      <c r="X112" s="37"/>
-      <c r="Y112" s="37"/>
-      <c r="Z112" s="37"/>
-      <c r="AA112" s="37"/>
-      <c r="AB112" s="37"/>
-      <c r="AC112" s="37"/>
-      <c r="AD112" s="37"/>
-      <c r="AE112" s="37"/>
-      <c r="AF112" s="37"/>
-      <c r="AG112" s="37"/>
-      <c r="AH112" s="37"/>
+    <row r="111" spans="1:69">
+      <c r="A111" s="38"/>
+      <c r="B111" s="38"/>
+      <c r="W111" s="37"/>
+      <c r="X111" s="37"/>
+      <c r="Y111" s="37"/>
+      <c r="Z111" s="37"/>
+      <c r="AA111" s="37"/>
+      <c r="AB111" s="37"/>
+      <c r="AC111" s="37"/>
+      <c r="AD111" s="37"/>
+      <c r="AE111" s="37"/>
+      <c r="AF111" s="37"/>
+      <c r="AG111" s="37"/>
+      <c r="AH111" s="37"/>
+    </row>
+    <row r="117" spans="23:34">
+      <c r="W117" s="37"/>
+      <c r="X117" s="37"/>
+      <c r="Y117" s="37"/>
+      <c r="Z117" s="37"/>
+      <c r="AA117" s="37"/>
+      <c r="AB117" s="37"/>
+      <c r="AC117" s="37"/>
+      <c r="AD117" s="37"/>
+      <c r="AE117" s="37"/>
+      <c r="AF117" s="37"/>
+      <c r="AG117" s="37"/>
+      <c r="AH117" s="37"/>
     </row>
     <row r="118" spans="23:34">
       <c r="W118" s="37"/>
@@ -20209,65 +20719,65 @@
       <c r="AH279" s="37"/>
     </row>
     <row r="280" spans="23:34">
-      <c r="W280" s="37"/>
-      <c r="X280" s="37"/>
-      <c r="Y280" s="37"/>
-      <c r="Z280" s="37"/>
-      <c r="AA280" s="37"/>
-      <c r="AB280" s="37"/>
-      <c r="AC280" s="37"/>
-      <c r="AD280" s="37"/>
-      <c r="AE280" s="37"/>
-      <c r="AF280" s="37"/>
-      <c r="AG280" s="37"/>
-      <c r="AH280" s="37"/>
-    </row>
-    <row r="281" spans="23:34">
-      <c r="W281" s="47" t="e">
-        <f t="shared" ref="W281:AG281" si="2">(F281-F3)/F3</f>
+      <c r="W280" s="49" t="e">
+        <f t="shared" ref="W280:AG280" si="2">(F280-F3)/F3</f>
         <v>#VALUE!</v>
       </c>
-      <c r="X281" s="47" t="e">
+      <c r="X280" s="49" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Y281" s="47" t="e">
+      <c r="Y280" s="49" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="Z281" s="47" t="e">
+      <c r="Z280" s="49" t="e">
         <f t="shared" si="2"/>
         <v>#VALUE!</v>
       </c>
-      <c r="AA281" s="47">
+      <c r="AA280" s="49">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="AB281" s="47">
+      <c r="AB280" s="49">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="AC281" s="47">
+      <c r="AC280" s="49">
         <f t="shared" si="2"/>
         <v>-1</v>
       </c>
-      <c r="AD281" s="47" t="e">
-        <f>(W281-W10)/W10</f>
+      <c r="AD280" s="49" t="e">
+        <f>(W280-W10)/W10</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AE281" s="47" t="e">
-        <f>(X281-#REF!)/#REF!</f>
+      <c r="AE280" s="49" t="e">
+        <f>(X280-#REF!)/#REF!</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AF281" s="47" t="e">
-        <f>(Y281-#REF!)/#REF!</f>
+      <c r="AF280" s="49" t="e">
+        <f>(Y280-#REF!)/#REF!</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AG281" s="47" t="e">
-        <f>(Z281-#REF!)/#REF!</f>
+      <c r="AG280" s="49" t="e">
+        <f>(Z280-#REF!)/#REF!</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AH281" s="47"/>
+      <c r="AH280" s="49"/>
+    </row>
+    <row r="281" spans="23:34">
+      <c r="W281" s="37"/>
+      <c r="X281" s="37"/>
+      <c r="Y281" s="37"/>
+      <c r="Z281" s="37"/>
+      <c r="AA281" s="37"/>
+      <c r="AB281" s="37"/>
+      <c r="AC281" s="37"/>
+      <c r="AD281" s="37"/>
+      <c r="AE281" s="37"/>
+      <c r="AF281" s="37"/>
+      <c r="AG281" s="37"/>
+      <c r="AH281" s="37"/>
     </row>
     <row r="282" spans="23:34">
       <c r="W282" s="37"/>
@@ -23658,65 +24168,65 @@
       <c r="AH523" s="37"/>
     </row>
     <row r="524" spans="23:34">
-      <c r="W524" s="37"/>
-      <c r="X524" s="37"/>
-      <c r="Y524" s="37"/>
-      <c r="Z524" s="37"/>
-      <c r="AA524" s="37"/>
-      <c r="AB524" s="37"/>
-      <c r="AC524" s="37"/>
-      <c r="AD524" s="37"/>
-      <c r="AE524" s="37"/>
-      <c r="AF524" s="37"/>
-      <c r="AG524" s="37"/>
-      <c r="AH524" s="37"/>
-    </row>
-    <row r="525" spans="23:34">
-      <c r="W525" s="47" t="e">
-        <f t="shared" ref="W525:AG525" si="3">(F525-F281)/F281</f>
+      <c r="W524" s="49" t="e">
+        <f t="shared" ref="W524:AG524" si="3">(F524-F280)/F280</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X525" s="47" t="e">
+      <c r="X524" s="49" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y525" s="47" t="e">
+      <c r="Y524" s="49" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z525" s="47" t="e">
+      <c r="Z524" s="49" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA525" s="47" t="e">
+      <c r="AA524" s="49" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB525" s="47" t="e">
+      <c r="AB524" s="49" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC525" s="47" t="e">
+      <c r="AC524" s="49" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD525" s="47" t="e">
-        <f>(W525-W281)/W281</f>
+      <c r="AD524" s="49" t="e">
+        <f>(W524-W280)/W280</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE525" s="47" t="e">
-        <f>(X525-X281)/X281</f>
+      <c r="AE524" s="49" t="e">
+        <f>(X524-X280)/X280</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF525" s="47" t="e">
-        <f>(Y525-Y281)/Y281</f>
+      <c r="AF524" s="49" t="e">
+        <f>(Y524-Y280)/Y280</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG525" s="47" t="e">
-        <f>(Z525-Z281)/Z281</f>
+      <c r="AG524" s="49" t="e">
+        <f>(Z524-Z280)/Z280</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH525" s="47"/>
+      <c r="AH524" s="49"/>
+    </row>
+    <row r="525" spans="23:34">
+      <c r="W525" s="37"/>
+      <c r="X525" s="37"/>
+      <c r="Y525" s="37"/>
+      <c r="Z525" s="37"/>
+      <c r="AA525" s="37"/>
+      <c r="AB525" s="37"/>
+      <c r="AC525" s="37"/>
+      <c r="AD525" s="37"/>
+      <c r="AE525" s="37"/>
+      <c r="AF525" s="37"/>
+      <c r="AG525" s="37"/>
+      <c r="AH525" s="37"/>
     </row>
     <row r="526" spans="23:34">
       <c r="W526" s="37"/>
@@ -27093,65 +27603,65 @@
       <c r="AH766" s="37"/>
     </row>
     <row r="767" spans="23:34">
-      <c r="W767" s="37"/>
-      <c r="X767" s="37"/>
-      <c r="Y767" s="37"/>
-      <c r="Z767" s="37"/>
-      <c r="AA767" s="37"/>
-      <c r="AB767" s="37"/>
-      <c r="AC767" s="37"/>
-      <c r="AD767" s="37"/>
-      <c r="AE767" s="37"/>
-      <c r="AF767" s="37"/>
-      <c r="AG767" s="37"/>
-      <c r="AH767" s="37"/>
-    </row>
-    <row r="768" spans="23:34">
-      <c r="W768" s="47" t="e">
-        <f t="shared" ref="W768:AG768" si="4">(F768-F525)/F525</f>
+      <c r="W767" s="49" t="e">
+        <f t="shared" ref="W767:AG767" si="4">(F767-F524)/F524</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X768" s="47" t="e">
+      <c r="X767" s="49" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y768" s="47" t="e">
+      <c r="Y767" s="49" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z768" s="47" t="e">
+      <c r="Z767" s="49" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA768" s="47" t="e">
+      <c r="AA767" s="49" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB768" s="47" t="e">
+      <c r="AB767" s="49" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC768" s="47" t="e">
+      <c r="AC767" s="49" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD768" s="47" t="e">
-        <f>(W768-W525)/W525</f>
+      <c r="AD767" s="49" t="e">
+        <f>(W767-W524)/W524</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE768" s="47" t="e">
-        <f>(X768-X525)/X525</f>
+      <c r="AE767" s="49" t="e">
+        <f>(X767-X524)/X524</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF768" s="47" t="e">
-        <f>(Y768-Y525)/Y525</f>
+      <c r="AF767" s="49" t="e">
+        <f>(Y767-Y524)/Y524</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG768" s="47" t="e">
-        <f>(Z768-Z525)/Z525</f>
+      <c r="AG767" s="49" t="e">
+        <f>(Z767-Z524)/Z524</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH768" s="47"/>
+      <c r="AH767" s="49"/>
+    </row>
+    <row r="768" spans="23:34">
+      <c r="W768" s="37"/>
+      <c r="X768" s="37"/>
+      <c r="Y768" s="37"/>
+      <c r="Z768" s="37"/>
+      <c r="AA768" s="37"/>
+      <c r="AB768" s="37"/>
+      <c r="AC768" s="37"/>
+      <c r="AD768" s="37"/>
+      <c r="AE768" s="37"/>
+      <c r="AF768" s="37"/>
+      <c r="AG768" s="37"/>
+      <c r="AH768" s="37"/>
     </row>
     <row r="769" spans="23:34">
       <c r="W769" s="37"/>
@@ -30542,65 +31052,65 @@
       <c r="AH1010" s="37"/>
     </row>
     <row r="1011" spans="23:34">
-      <c r="W1011" s="37"/>
-      <c r="X1011" s="37"/>
-      <c r="Y1011" s="37"/>
-      <c r="Z1011" s="37"/>
-      <c r="AA1011" s="37"/>
-      <c r="AB1011" s="37"/>
-      <c r="AC1011" s="37"/>
-      <c r="AD1011" s="37"/>
-      <c r="AE1011" s="37"/>
-      <c r="AF1011" s="37"/>
-      <c r="AG1011" s="37"/>
-      <c r="AH1011" s="37"/>
-    </row>
-    <row r="1012" spans="23:34">
-      <c r="W1012" s="47" t="e">
-        <f t="shared" ref="W1012:AG1012" si="5">(F1012-F768)/F768</f>
+      <c r="W1011" s="49" t="e">
+        <f t="shared" ref="W1011:AG1011" si="5">(F1011-F767)/F767</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X1012" s="47" t="e">
+      <c r="X1011" s="49" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y1012" s="47" t="e">
+      <c r="Y1011" s="49" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z1012" s="47" t="e">
+      <c r="Z1011" s="49" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA1012" s="47" t="e">
+      <c r="AA1011" s="49" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB1012" s="47" t="e">
+      <c r="AB1011" s="49" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC1012" s="47" t="e">
+      <c r="AC1011" s="49" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD1012" s="47" t="e">
-        <f>(W1012-W768)/W768</f>
+      <c r="AD1011" s="49" t="e">
+        <f>(W1011-W767)/W767</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE1012" s="47" t="e">
-        <f>(X1012-X768)/X768</f>
+      <c r="AE1011" s="49" t="e">
+        <f>(X1011-X767)/X767</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF1012" s="47" t="e">
-        <f>(Y1012-Y768)/Y768</f>
+      <c r="AF1011" s="49" t="e">
+        <f>(Y1011-Y767)/Y767</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG1012" s="47" t="e">
-        <f>(Z1012-Z768)/Z768</f>
+      <c r="AG1011" s="49" t="e">
+        <f>(Z1011-Z767)/Z767</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH1012" s="47"/>
+      <c r="AH1011" s="49"/>
+    </row>
+    <row r="1012" spans="23:34">
+      <c r="W1012" s="37"/>
+      <c r="X1012" s="37"/>
+      <c r="Y1012" s="37"/>
+      <c r="Z1012" s="37"/>
+      <c r="AA1012" s="37"/>
+      <c r="AB1012" s="37"/>
+      <c r="AC1012" s="37"/>
+      <c r="AD1012" s="37"/>
+      <c r="AE1012" s="37"/>
+      <c r="AF1012" s="37"/>
+      <c r="AG1012" s="37"/>
+      <c r="AH1012" s="37"/>
     </row>
     <row r="1013" spans="23:34">
       <c r="W1013" s="37"/>
@@ -33977,65 +34487,65 @@
       <c r="AH1253" s="37"/>
     </row>
     <row r="1254" spans="23:34">
-      <c r="W1254" s="37"/>
-      <c r="X1254" s="37"/>
-      <c r="Y1254" s="37"/>
-      <c r="Z1254" s="37"/>
-      <c r="AA1254" s="37"/>
-      <c r="AB1254" s="37"/>
-      <c r="AC1254" s="37"/>
-      <c r="AD1254" s="37"/>
-      <c r="AE1254" s="37"/>
-      <c r="AF1254" s="37"/>
-      <c r="AG1254" s="37"/>
-      <c r="AH1254" s="37"/>
-    </row>
-    <row r="1255" spans="23:34">
-      <c r="W1255" s="47" t="e">
-        <f t="shared" ref="W1255:AG1255" si="6">(F1255-F1012)/F1012</f>
+      <c r="W1254" s="49" t="e">
+        <f t="shared" ref="W1254:AG1254" si="6">(F1254-F1011)/F1011</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X1255" s="47" t="e">
+      <c r="X1254" s="49" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y1255" s="47" t="e">
+      <c r="Y1254" s="49" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z1255" s="47" t="e">
+      <c r="Z1254" s="49" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA1255" s="47" t="e">
+      <c r="AA1254" s="49" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB1255" s="47" t="e">
+      <c r="AB1254" s="49" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC1255" s="47" t="e">
+      <c r="AC1254" s="49" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD1255" s="47" t="e">
-        <f>(W1255-W1012)/W1012</f>
+      <c r="AD1254" s="49" t="e">
+        <f>(W1254-W1011)/W1011</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE1255" s="47" t="e">
-        <f>(X1255-X1012)/X1012</f>
+      <c r="AE1254" s="49" t="e">
+        <f>(X1254-X1011)/X1011</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF1255" s="47" t="e">
-        <f>(Y1255-Y1012)/Y1012</f>
+      <c r="AF1254" s="49" t="e">
+        <f>(Y1254-Y1011)/Y1011</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG1255" s="47" t="e">
-        <f>(Z1255-Z1012)/Z1012</f>
+      <c r="AG1254" s="49" t="e">
+        <f>(Z1254-Z1011)/Z1011</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH1255" s="47"/>
+      <c r="AH1254" s="49"/>
+    </row>
+    <row r="1255" spans="23:34">
+      <c r="W1255" s="37"/>
+      <c r="X1255" s="37"/>
+      <c r="Y1255" s="37"/>
+      <c r="Z1255" s="37"/>
+      <c r="AA1255" s="37"/>
+      <c r="AB1255" s="37"/>
+      <c r="AC1255" s="37"/>
+      <c r="AD1255" s="37"/>
+      <c r="AE1255" s="37"/>
+      <c r="AF1255" s="37"/>
+      <c r="AG1255" s="37"/>
+      <c r="AH1255" s="37"/>
     </row>
     <row r="1256" spans="23:34">
       <c r="W1256" s="37"/>
@@ -37412,65 +37922,65 @@
       <c r="AH1496" s="37"/>
     </row>
     <row r="1497" spans="23:34">
-      <c r="W1497" s="37"/>
-      <c r="X1497" s="37"/>
-      <c r="Y1497" s="37"/>
-      <c r="Z1497" s="37"/>
-      <c r="AA1497" s="37"/>
-      <c r="AB1497" s="37"/>
-      <c r="AC1497" s="37"/>
-      <c r="AD1497" s="37"/>
-      <c r="AE1497" s="37"/>
-      <c r="AF1497" s="37"/>
-      <c r="AG1497" s="37"/>
-      <c r="AH1497" s="37"/>
-    </row>
-    <row r="1498" spans="23:34">
-      <c r="W1498" s="47" t="e">
-        <f t="shared" ref="W1498:AG1498" si="7">(F1498-F1255)/F1255</f>
+      <c r="W1497" s="49" t="e">
+        <f t="shared" ref="W1497:AG1497" si="7">(F1497-F1254)/F1254</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X1498" s="47" t="e">
+      <c r="X1497" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y1498" s="47" t="e">
+      <c r="Y1497" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z1498" s="47" t="e">
+      <c r="Z1497" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA1498" s="47" t="e">
+      <c r="AA1497" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB1498" s="47" t="e">
+      <c r="AB1497" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC1498" s="47" t="e">
+      <c r="AC1497" s="49" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD1498" s="47" t="e">
-        <f>(W1498-W1255)/W1255</f>
+      <c r="AD1497" s="49" t="e">
+        <f>(W1497-W1254)/W1254</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE1498" s="47" t="e">
-        <f>(X1498-X1255)/X1255</f>
+      <c r="AE1497" s="49" t="e">
+        <f>(X1497-X1254)/X1254</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF1498" s="47" t="e">
-        <f>(Y1498-Y1255)/Y1255</f>
+      <c r="AF1497" s="49" t="e">
+        <f>(Y1497-Y1254)/Y1254</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG1498" s="47" t="e">
-        <f>(Z1498-Z1255)/Z1255</f>
+      <c r="AG1497" s="49" t="e">
+        <f>(Z1497-Z1254)/Z1254</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH1498" s="47"/>
+      <c r="AH1497" s="49"/>
+    </row>
+    <row r="1498" spans="23:34">
+      <c r="W1498" s="37"/>
+      <c r="X1498" s="37"/>
+      <c r="Y1498" s="37"/>
+      <c r="Z1498" s="37"/>
+      <c r="AA1498" s="37"/>
+      <c r="AB1498" s="37"/>
+      <c r="AC1498" s="37"/>
+      <c r="AD1498" s="37"/>
+      <c r="AE1498" s="37"/>
+      <c r="AF1498" s="37"/>
+      <c r="AG1498" s="37"/>
+      <c r="AH1498" s="37"/>
     </row>
     <row r="1499" spans="23:34">
       <c r="W1499" s="37"/>
@@ -40833,65 +41343,65 @@
       <c r="AH1738" s="37"/>
     </row>
     <row r="1739" spans="23:34">
-      <c r="W1739" s="37"/>
-      <c r="X1739" s="37"/>
-      <c r="Y1739" s="37"/>
-      <c r="Z1739" s="37"/>
-      <c r="AA1739" s="37"/>
-      <c r="AB1739" s="37"/>
-      <c r="AC1739" s="37"/>
-      <c r="AD1739" s="37"/>
-      <c r="AE1739" s="37"/>
-      <c r="AF1739" s="37"/>
-      <c r="AG1739" s="37"/>
-      <c r="AH1739" s="37"/>
-    </row>
-    <row r="1740" spans="23:34">
-      <c r="W1740" s="47" t="e">
-        <f t="shared" ref="W1740:AG1740" si="8">(F1740-F1498)/F1498</f>
+      <c r="W1739" s="49" t="e">
+        <f t="shared" ref="W1739:AG1739" si="8">(F1739-F1497)/F1497</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X1740" s="47" t="e">
+      <c r="X1739" s="49" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y1740" s="47" t="e">
+      <c r="Y1739" s="49" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z1740" s="47" t="e">
+      <c r="Z1739" s="49" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA1740" s="47" t="e">
+      <c r="AA1739" s="49" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB1740" s="47" t="e">
+      <c r="AB1739" s="49" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC1740" s="47" t="e">
+      <c r="AC1739" s="49" t="e">
         <f t="shared" si="8"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD1740" s="47" t="e">
-        <f>(W1740-W1498)/W1498</f>
+      <c r="AD1739" s="49" t="e">
+        <f>(W1739-W1497)/W1497</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE1740" s="47" t="e">
-        <f>(X1740-X1498)/X1498</f>
+      <c r="AE1739" s="49" t="e">
+        <f>(X1739-X1497)/X1497</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF1740" s="47" t="e">
-        <f>(Y1740-Y1498)/Y1498</f>
+      <c r="AF1739" s="49" t="e">
+        <f>(Y1739-Y1497)/Y1497</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG1740" s="47" t="e">
-        <f>(Z1740-Z1498)/Z1498</f>
+      <c r="AG1739" s="49" t="e">
+        <f>(Z1739-Z1497)/Z1497</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH1740" s="47"/>
+      <c r="AH1739" s="49"/>
+    </row>
+    <row r="1740" spans="23:34">
+      <c r="W1740" s="37"/>
+      <c r="X1740" s="37"/>
+      <c r="Y1740" s="37"/>
+      <c r="Z1740" s="37"/>
+      <c r="AA1740" s="37"/>
+      <c r="AB1740" s="37"/>
+      <c r="AC1740" s="37"/>
+      <c r="AD1740" s="37"/>
+      <c r="AE1740" s="37"/>
+      <c r="AF1740" s="37"/>
+      <c r="AG1740" s="37"/>
+      <c r="AH1740" s="37"/>
     </row>
     <row r="1741" spans="23:34">
       <c r="W1741" s="37"/>
@@ -44254,65 +44764,65 @@
       <c r="AH1980" s="37"/>
     </row>
     <row r="1981" spans="23:34">
-      <c r="W1981" s="37"/>
-      <c r="X1981" s="37"/>
-      <c r="Y1981" s="37"/>
-      <c r="Z1981" s="37"/>
-      <c r="AA1981" s="37"/>
-      <c r="AB1981" s="37"/>
-      <c r="AC1981" s="37"/>
-      <c r="AD1981" s="37"/>
-      <c r="AE1981" s="37"/>
-      <c r="AF1981" s="37"/>
-      <c r="AG1981" s="37"/>
-      <c r="AH1981" s="37"/>
-    </row>
-    <row r="1982" spans="23:34">
-      <c r="W1982" s="47" t="e">
-        <f t="shared" ref="W1982:AG1982" si="9">(F1982-F1740)/F1740</f>
+      <c r="W1981" s="49" t="e">
+        <f t="shared" ref="W1981:AG1981" si="9">(F1981-F1739)/F1739</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X1982" s="47" t="e">
+      <c r="X1981" s="49" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y1982" s="47" t="e">
+      <c r="Y1981" s="49" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z1982" s="47" t="e">
+      <c r="Z1981" s="49" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA1982" s="47" t="e">
+      <c r="AA1981" s="49" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB1982" s="47" t="e">
+      <c r="AB1981" s="49" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC1982" s="47" t="e">
+      <c r="AC1981" s="49" t="e">
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD1982" s="47" t="e">
-        <f>(W1982-W1740)/W1740</f>
+      <c r="AD1981" s="49" t="e">
+        <f>(W1981-W1739)/W1739</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE1982" s="47" t="e">
-        <f>(X1982-X1740)/X1740</f>
+      <c r="AE1981" s="49" t="e">
+        <f>(X1981-X1739)/X1739</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF1982" s="47" t="e">
-        <f>(Y1982-Y1740)/Y1740</f>
+      <c r="AF1981" s="49" t="e">
+        <f>(Y1981-Y1739)/Y1739</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG1982" s="47" t="e">
-        <f>(Z1982-Z1740)/Z1740</f>
+      <c r="AG1981" s="49" t="e">
+        <f>(Z1981-Z1739)/Z1739</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH1982" s="47"/>
+      <c r="AH1981" s="49"/>
+    </row>
+    <row r="1982" spans="23:34">
+      <c r="W1982" s="37"/>
+      <c r="X1982" s="37"/>
+      <c r="Y1982" s="37"/>
+      <c r="Z1982" s="37"/>
+      <c r="AA1982" s="37"/>
+      <c r="AB1982" s="37"/>
+      <c r="AC1982" s="37"/>
+      <c r="AD1982" s="37"/>
+      <c r="AE1982" s="37"/>
+      <c r="AF1982" s="37"/>
+      <c r="AG1982" s="37"/>
+      <c r="AH1982" s="37"/>
     </row>
     <row r="1983" spans="23:34">
       <c r="W1983" s="37"/>
@@ -47647,65 +48157,65 @@
       <c r="AH2220" s="37"/>
     </row>
     <row r="2221" spans="23:34">
-      <c r="W2221" s="37"/>
-      <c r="X2221" s="37"/>
-      <c r="Y2221" s="37"/>
-      <c r="Z2221" s="37"/>
-      <c r="AA2221" s="37"/>
-      <c r="AB2221" s="37"/>
-      <c r="AC2221" s="37"/>
-      <c r="AD2221" s="37"/>
-      <c r="AE2221" s="37"/>
-      <c r="AF2221" s="37"/>
-      <c r="AG2221" s="37"/>
-      <c r="AH2221" s="37"/>
-    </row>
-    <row r="2222" spans="23:34">
-      <c r="W2222" s="47" t="e">
-        <f t="shared" ref="W2222:AG2222" si="10">(F2222-F1982)/F1982</f>
+      <c r="W2221" s="49" t="e">
+        <f t="shared" ref="W2221:AG2221" si="10">(F2221-F1981)/F1981</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X2222" s="47" t="e">
+      <c r="X2221" s="49" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y2222" s="47" t="e">
+      <c r="Y2221" s="49" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z2222" s="47" t="e">
+      <c r="Z2221" s="49" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA2222" s="47" t="e">
+      <c r="AA2221" s="49" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB2222" s="47" t="e">
+      <c r="AB2221" s="49" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC2222" s="47" t="e">
+      <c r="AC2221" s="49" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD2222" s="47" t="e">
-        <f>(W2222-W1982)/W1982</f>
+      <c r="AD2221" s="49" t="e">
+        <f>(W2221-W1981)/W1981</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE2222" s="47" t="e">
-        <f>(X2222-X1982)/X1982</f>
+      <c r="AE2221" s="49" t="e">
+        <f>(X2221-X1981)/X1981</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF2222" s="47" t="e">
-        <f>(Y2222-Y1982)/Y1982</f>
+      <c r="AF2221" s="49" t="e">
+        <f>(Y2221-Y1981)/Y1981</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG2222" s="47" t="e">
-        <f>(Z2222-Z1982)/Z1982</f>
+      <c r="AG2221" s="49" t="e">
+        <f>(Z2221-Z1981)/Z1981</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH2222" s="47"/>
+      <c r="AH2221" s="49"/>
+    </row>
+    <row r="2222" spans="23:34">
+      <c r="W2222" s="37"/>
+      <c r="X2222" s="37"/>
+      <c r="Y2222" s="37"/>
+      <c r="Z2222" s="37"/>
+      <c r="AA2222" s="37"/>
+      <c r="AB2222" s="37"/>
+      <c r="AC2222" s="37"/>
+      <c r="AD2222" s="37"/>
+      <c r="AE2222" s="37"/>
+      <c r="AF2222" s="37"/>
+      <c r="AG2222" s="37"/>
+      <c r="AH2222" s="37"/>
     </row>
     <row r="2223" spans="23:34">
       <c r="W2223" s="37"/>
@@ -51054,65 +51564,51 @@
       <c r="AH2461" s="37"/>
     </row>
     <row r="2462" spans="23:34">
-      <c r="W2462" s="37"/>
-      <c r="X2462" s="37"/>
-      <c r="Y2462" s="37"/>
-      <c r="Z2462" s="37"/>
-      <c r="AA2462" s="37"/>
-      <c r="AB2462" s="37"/>
-      <c r="AC2462" s="37"/>
-      <c r="AD2462" s="37"/>
-      <c r="AE2462" s="37"/>
-      <c r="AF2462" s="37"/>
-      <c r="AG2462" s="37"/>
-      <c r="AH2462" s="37"/>
-    </row>
-    <row r="2463" spans="23:34">
-      <c r="W2463" s="47" t="e">
-        <f t="shared" ref="W2463:AG2463" si="11">(F2463-F2222)/F2222</f>
+      <c r="W2462" s="49" t="e">
+        <f t="shared" ref="W2462:AG2462" si="11">(F2462-F2221)/F2221</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="X2463" s="47" t="e">
+      <c r="X2462" s="49" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y2463" s="47" t="e">
+      <c r="Y2462" s="49" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z2463" s="47" t="e">
+      <c r="Z2462" s="49" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA2463" s="47" t="e">
+      <c r="AA2462" s="49" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AB2463" s="47" t="e">
+      <c r="AB2462" s="49" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC2463" s="47" t="e">
+      <c r="AC2462" s="49" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AD2463" s="47" t="e">
-        <f>(W2463-W2222)/W2222</f>
+      <c r="AD2462" s="49" t="e">
+        <f>(W2462-W2221)/W2221</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AE2463" s="47" t="e">
-        <f>(X2463-X2222)/X2222</f>
+      <c r="AE2462" s="49" t="e">
+        <f>(X2462-X2221)/X2221</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF2463" s="47" t="e">
-        <f>(Y2463-Y2222)/Y2222</f>
+      <c r="AF2462" s="49" t="e">
+        <f>(Y2462-Y2221)/Y2221</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AG2463" s="47" t="e">
-        <f>(Z2463-Z2222)/Z2222</f>
+      <c r="AG2462" s="49" t="e">
+        <f>(Z2462-Z2221)/Z2221</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AH2463" s="47"/>
+      <c r="AH2462" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="16">
